--- a/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
+++ b/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="4">
@@ -89,16 +89,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1905</v>
+        <v>0.2143</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5001700</v>
+        <v>12327800</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>3.45</v>
+        <v>8.5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>75.03</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.416</v>
+        <v>0.417</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.412</v>
@@ -598,54 +598,62 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>EMA与SAR、Supertrend均呈多头排列，但RSI达75.03已入超买区，现价高于50日均线约21%，信号偏热。</t>
+          <t>EMA与SAR、Supertrend均呈多头排列，但RSI达76.29已超买，现价高于50日均线约24%，信号偏热。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7215</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>NIHSIN</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>31243000</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H3" t="n">
-        <v>78.19</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.0201</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>12634300</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>72.87</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>4.797</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>4.544</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>RSI达72.87，已进入超买区；现价5.08高于50日均线4.544约11.8%，短期均线多头排列，信号偏强但需留意超买风险。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,39 +663,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>0.0259</v>
+        <v>0.17</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>28067600</v>
+        <v>56445300</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.19</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="n">
-        <v>72.05</v>
-      </c>
-      <c r="I4" s="16" t="inlineStr">
+        <v>22.06</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.551</v>
+        <v>0.256</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.494</v>
+        <v>0.47</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -709,27 +717,27 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.235</v>
+        <v>0.25</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0</v>
+        <v>0.0638</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>3972000</v>
+        <v>55071900</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.2</v>
+        <v>2.83</v>
       </c>
       <c r="H5" t="n">
-        <v>52.63</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
+        <v>61.02</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.233</v>
+        <v>0.234</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0.233</v>
@@ -754,27 +762,27 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.19</v>
+        <v>0.195</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0</v>
+        <v>0.0263</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>3889100</v>
+        <v>13397200</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.08</v>
+        <v>0.27</v>
       </c>
       <c r="H6" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.154</v>
+        <v>0.155</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0.12</v>
@@ -790,39 +798,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E7" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>2151100</v>
+        <v>11350900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.09</v>
+        <v>0.44</v>
       </c>
       <c r="H7" t="n">
-        <v>26.04</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
+        <v>35.15</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.232</v>
+        <v>0.058</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.247</v>
+        <v>0.076</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,39 +843,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.175</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.09369999999999999</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>565200</v>
+        <v>9399600</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.04</v>
+        <v>0.4</v>
       </c>
       <c r="H8" t="n">
-        <v>48.13</v>
+        <v>42.45</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.773</v>
+        <v>0.179</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.774</v>
+        <v>0.215</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,45 +888,2461 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0152</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>DGB</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.002</v>
+        <v>0.04</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>532400</v>
+        <v>8831200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.03</v>
+        <v>127.15</v>
       </c>
       <c r="H9" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
+        <v>60.06</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>4.788</v>
+        <v>0.035</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>4.542</v>
+        <v>0.035</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>8482600</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H10" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>6418300</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H11" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7315</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AHB</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>5217700</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H12" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0468</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>UNIPAC</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>4958700</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>4587000</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>78.19</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>4534800</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H15" t="n">
+        <v>54.05</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>3671000</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H16" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>3513500</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H17" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0473</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Evocom Berhad</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>3404600</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>2676700</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H19" t="n">
+        <v>46.39</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>2638700</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>65.58</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>2.684</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>2.522</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0250</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>YXPM</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>-0.0444</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>2564500</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="H21" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>-0.008199999999999999</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>2380500</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H22" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>2371100</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>2312900</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>52.83</v>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>1965400</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H25" t="n">
+        <v>55.27</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>-0.006500000000000001</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>1925300</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H26" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>1911700</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>1745600</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H28" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0370</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>XPB</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>1531700</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>1493800</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H30" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>2.339</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>-0.0369</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>1367200</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H31" t="n">
+        <v>70.52</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>3.657</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>-0.0172</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>1295500</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H32" t="n">
+        <v>61.57</v>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>-0.0266</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>1293000</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H33" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>1281300</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H34" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>1239300</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>10.147</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>10.294</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0373</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VERDANT</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>1195100</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H36" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>1161100</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H37" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>1.366</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>1114800</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H38" t="n">
+        <v>53.23</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>7179</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>LAGENDA</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>1036300</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H39" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>1.582</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>1018700</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>1010100</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>2.791</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>2.649</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>1008700</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H42" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>2.511</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>911800</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H43" t="n">
+        <v>83.69</v>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>907100</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H44" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>893400</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H45" t="n">
+        <v>69.42</v>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>852000</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H46" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>1.745</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>831600</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H47" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>814400</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H48" t="n">
+        <v>60.43</v>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>786100</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H49" t="n">
+        <v>75.67</v>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>773000</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H50" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>7.801</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>7.741</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>767800</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H51" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>1.763</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>1.798</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>685900</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H52" t="n">
+        <v>80.33</v>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>3.709</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>3.283</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>683900</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H53" t="n">
+        <v>36.44</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>4.824</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>4.946</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>656300</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H54" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>637300</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H55" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>626800</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H56" t="n">
+        <v>66.08</v>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>625200</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H57" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>616400</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H58" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>611200</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H59" t="n">
+        <v>47.24</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>589800</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H60" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>580400</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H61" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="I61" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>-0.0157</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>524200</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H62" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>2.363</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>1.836</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>518700</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="I63" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
+++ b/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -92,11 +92,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.51</v>
+        <v>0.495</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.2143</v>
+        <v>0.1786</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>12327800</v>
+        <v>15661900</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>8.5</v>
+        <v>10.8</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>76.29000000000001</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.417</v>
+        <v>0.415</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.412</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>EMA与SAR、Supertrend均呈多头排列，但RSI达76.29已超买，现价高于50日均线约24%，信号偏热。</t>
+          <t>EMA与SAR、Supertrend均呈多头排列，RSI达74.35已入超买区，现价高于50日均线约20%，信号偏强但短线过热。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5.08</v>
+        <v>5.03</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0201</v>
+        <v>0.01</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>12634300</v>
+        <v>16796700</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>72.87</v>
+        <v>71.06</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>4.797</v>
+        <v>4.792</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>4.544</v>
+        <v>4.543</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>RSI达72.87，已进入超买区；现价5.08高于50日均线4.544约11.8%，短期均线多头排列，信号偏强但需留意超买风险。</t>
+          <t>RSI 71.06已超买，现价5.03高于50日均线4.543约10.7%，短期均线多头排列，信号偏强但需留意超买风险。</t>
         </is>
       </c>
     </row>
@@ -663,39 +663,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.0303</v>
+        <v>0.1064</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>56445300</v>
+        <v>78281000</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.1</v>
+        <v>4.02</v>
       </c>
       <c r="H4" t="n">
-        <v>22.06</v>
+        <v>65.14</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.256</v>
+        <v>0.235</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.47</v>
+        <v>0.233</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -708,39 +708,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.25</v>
+        <v>0.175</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.0638</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>55071900</v>
+        <v>76343200</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>2.83</v>
+        <v>0.13</v>
       </c>
       <c r="H5" t="n">
-        <v>61.02</v>
+        <v>23.59</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.234</v>
+        <v>0.256</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.233</v>
+        <v>0.47</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -753,39 +753,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.195</v>
+        <v>0.17</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.0263</v>
+        <v>0.0625</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>13397200</v>
+        <v>27800400</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.27</v>
+        <v>1.19</v>
       </c>
       <c r="H6" t="n">
-        <v>80.31999999999999</v>
+        <v>39.42</v>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.155</v>
+        <v>0.179</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.12</v>
+        <v>0.215</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -798,39 +798,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0051</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CUSCAPI</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.05</v>
+        <v>0.19</v>
       </c>
       <c r="E7" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>11350900</v>
+        <v>14203000</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="H7" t="n">
-        <v>35.15</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.058</v>
+        <v>0.154</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.076</v>
+        <v>0.12</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -843,39 +843,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.175</v>
+        <v>0.055</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.09369999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>9399600</v>
+        <v>11400900</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H8" t="n">
-        <v>42.45</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
+        <v>42.26</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.179</v>
+        <v>0.058</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.215</v>
+        <v>0.076</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -888,39 +888,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0152</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DGB</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.04</v>
+        <v>0.595</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>8831200</v>
+        <v>10771600</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>127.15</v>
+        <v>0.43</v>
       </c>
       <c r="H9" t="n">
-        <v>60.06</v>
+        <v>72.05</v>
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.035</v>
+        <v>0.555</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.035</v>
+        <v>0.495</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -933,39 +933,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0152</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>DGB</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.595</v>
+        <v>0.04</v>
       </c>
       <c r="E10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>8482600</v>
+        <v>9828100</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.34</v>
+        <v>141.5</v>
       </c>
       <c r="H10" t="n">
-        <v>72.05</v>
+        <v>60.06</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.555</v>
+        <v>0.035</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.495</v>
+        <v>0.035</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -978,39 +978,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.0417</v>
+        <v>0.05</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>6418300</v>
+        <v>9293800</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.22</v>
+        <v>0.93</v>
       </c>
       <c r="H11" t="n">
-        <v>36.22</v>
+        <v>48.92</v>
       </c>
       <c r="I11" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.271</v>
+        <v>0.052</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.322</v>
+        <v>0.044</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1023,39 +1023,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
+        <v>0.515</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-0.0721</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>5217700</v>
+        <v>7358200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.52</v>
+        <v>1.16</v>
       </c>
       <c r="H12" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
+        <v>46.92</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.052</v>
+        <v>0.524</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.044</v>
+        <v>0.532</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1068,33 +1068,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.265</v>
+        <v>0.245</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.0192</v>
+        <v>0.0208</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>4958700</v>
+        <v>6625700</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
+        <v>0.23</v>
+      </c>
+      <c r="H13" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0.322</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
     </row>
@@ -1106,39 +1113,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>0</v>
+        <v>0.21</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>4587000</v>
+        <v>6163500</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="H14" t="n">
-        <v>78.19</v>
+        <v>30.94</v>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.332</v>
+        <v>0.233</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.197</v>
+        <v>0.247</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1151,39 +1158,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>-0.036</v>
+        <v>1.82</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>4534800</v>
+        <v>5859500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="H15" t="n">
-        <v>54.05</v>
+        <v>39.82</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.526</v>
+        <v>1.886</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.533</v>
+        <v>1.959</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1196,40 +1203,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0.0196</v>
+        <v>0.26</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3671000</v>
+        <v>5764100</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H16" t="n">
-        <v>27.66</v>
+        <v>0.39</v>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>0.827</v>
-      </c>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
     </row>
@@ -1241,39 +1241,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0</v>
+        <v>0.475</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>3513500</v>
+        <v>5343800</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="H17" t="n">
-        <v>70.45</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
+        <v>52.83</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.377</v>
+        <v>0.469</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.372</v>
+        <v>0.472</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1286,33 +1286,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>-0.04</v>
+        <v>0.39</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>3404600</v>
+        <v>5192500</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
+      </c>
+      <c r="H18" t="n">
+        <v>78.19</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.197</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
     </row>
@@ -1324,39 +1331,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>-0.0122</v>
+        <v>0.345</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>2676700</v>
+        <v>5091600</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.24</v>
+        <v>0.67</v>
       </c>
       <c r="H19" t="n">
-        <v>46.39</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
+        <v>59.18</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.409</v>
+        <v>0.331</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.411</v>
+        <v>0.314</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1369,39 +1376,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>2.95</v>
+        <v>0.39</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>-0.0067</v>
+        <v>-0.0127</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>2638700</v>
+        <v>4812200</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="H20" t="n">
-        <v>65.58</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
+        <v>64.22</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2.684</v>
+        <v>0.377</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>2.522</v>
+        <v>0.372</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1414,39 +1421,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>YXPM</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.215</v>
+        <v>0.605</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>-0.0444</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2564500</v>
+        <v>4559700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>4.96</v>
+        <v>0.44</v>
       </c>
       <c r="H21" t="n">
-        <v>49.65</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
+        <v>48.44</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.216</v>
+        <v>0.607</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.214</v>
+        <v>0.606</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1459,39 +1466,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.52</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>2380500</v>
+        <v>4495500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="H22" t="n">
-        <v>48.44</v>
+        <v>27.66</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.607</v>
+        <v>0.612</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.606</v>
+        <v>0.827</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1504,39 +1511,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>0</v>
+        <v>0.155</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>2371100</v>
+        <v>4458500</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H23" t="n">
-        <v>26.04</v>
+        <v>50.05</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.232</v>
+        <v>0.157</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.247</v>
+        <v>0.148</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1549,39 +1556,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0.0106</v>
+        <v>0.11</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2312900</v>
+        <v>4237400</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.1</v>
+        <v>0.51</v>
       </c>
       <c r="H24" t="n">
-        <v>52.83</v>
+        <v>37.36</v>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.469</v>
+        <v>0.121</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.472</v>
+        <v>0.124</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1594,39 +1601,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0</v>
+        <v>0.1</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>-0.0476</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1965400</v>
+        <v>4188700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.08</v>
+        <v>0.67</v>
       </c>
       <c r="H25" t="n">
-        <v>55.27</v>
+        <v>74.37</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.203</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.186</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1639,39 +1646,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.445</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.0595</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1925300</v>
+        <v>4021000</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.14</v>
+        <v>2.01</v>
       </c>
       <c r="H26" t="n">
-        <v>48.13</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
+        <v>76.11</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.773</v>
+        <v>0.382</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.774</v>
+        <v>0.346</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1684,40 +1691,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.125</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>1911700</v>
+        <v>3956700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>46.81</v>
+        <v>0.09</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <v>0.87</v>
-      </c>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
     </row>
@@ -1729,39 +1729,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>2.49</v>
+        <v>0.77</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>-0.008</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1745600</v>
+        <v>3793200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.09</v>
+        <v>0.28</v>
       </c>
       <c r="H28" t="n">
-        <v>45.23</v>
+        <v>48.13</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>2.571</v>
+        <v>0.773</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>2.451</v>
+        <v>0.774</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1774,39 +1774,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0.0217</v>
+        <v>2.93</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1531700</v>
+        <v>3517600</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0.4</v>
       </c>
       <c r="H29" t="n">
-        <v>71.51000000000001</v>
-      </c>
-      <c r="I29" s="15" t="inlineStr">
+        <v>64.36</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.207</v>
+        <v>2.683</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.181</v>
+        <v>2.522</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1819,39 +1819,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>2.07</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>1493800</v>
+        <v>3442900</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="H30" t="n">
-        <v>48.57</v>
+        <v>44.75</v>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>2.339</v>
+        <v>2.117</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>2.251</v>
+        <v>2.066</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1864,39 +1864,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>-0.0369</v>
+        <v>0.365</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.0282</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1367200</v>
+        <v>3285700</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.11</v>
+        <v>0.46</v>
       </c>
       <c r="H31" t="n">
-        <v>70.52</v>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
+        <v>66.09</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>3.657</v>
+        <v>0.341</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>2.47</v>
+        <v>0.321</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1909,39 +1909,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.57</v>
+        <v>0.405</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>-0.0172</v>
+        <v>-0.0122</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>1295500</v>
+        <v>3015100</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.09</v>
+        <v>0.27</v>
       </c>
       <c r="H32" t="n">
-        <v>61.57</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
+        <v>46.39</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.533</v>
+        <v>0.409</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.485</v>
+        <v>0.411</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1954,39 +1954,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.915</v>
+        <v>0.575</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>-0.0266</v>
+        <v>-0.0086</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1293000</v>
+        <v>2968300</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="H33" t="n">
-        <v>61.37</v>
-      </c>
-      <c r="I33" s="15" t="inlineStr">
+        <v>63.01</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.891</v>
+        <v>0.533</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.853</v>
+        <v>0.485</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1999,39 +1999,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0.0128</v>
+        <v>4.06</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>-0.0645</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>1281300</v>
+        <v>2901000</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="H34" t="n">
-        <v>56.49</v>
+        <v>66.66</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.383</v>
+        <v>3.645</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.325</v>
+        <v>2.467</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2044,39 +2044,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>10.04</v>
+        <v>0.675</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0305</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1239300</v>
+        <v>2871900</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H35" t="n">
-        <v>40.82</v>
+        <v>61.53</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>10.147</v>
+        <v>0.638</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>10.294</v>
+        <v>0.581</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2089,39 +2089,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0.0185</v>
+        <v>0.39</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>1195100</v>
+        <v>2842300</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.42</v>
+        <v>0.13</v>
       </c>
       <c r="H36" t="n">
-        <v>76.7</v>
+        <v>55.3</v>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.233</v>
+        <v>0.383</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.211</v>
+        <v>0.325</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2134,39 +2134,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>1.34</v>
+        <v>0.225</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>-0.0074</v>
+        <v>-0.0217</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>1161100</v>
+        <v>2802700</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.09</v>
+        <v>0.74</v>
       </c>
       <c r="H37" t="n">
-        <v>48.32</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.366</v>
+        <v>0.206</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.297</v>
+        <v>0.181</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2179,39 +2179,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0.0068</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1114800</v>
+        <v>2800400</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
       <c r="H38" t="n">
-        <v>53.23</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
+        <v>50.19</v>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.736</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2224,39 +2224,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>1.56</v>
+        <v>0.865</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>-0.0127</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1036300</v>
+        <v>2684700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1.63</v>
+        <v>0.14</v>
       </c>
       <c r="H39" t="n">
-        <v>48.03</v>
+        <v>46.81</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>1.582</v>
+        <v>0.868</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>1.508</v>
+        <v>0.87</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2269,39 +2269,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.51</v>
       </c>
       <c r="E40" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1018700</v>
+        <v>2669800</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="H40" t="n">
-        <v>50.19</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
+        <v>46.6</v>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.573</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>2.452</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2314,39 +2314,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.2</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1010100</v>
+        <v>2647200</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H41" t="n">
-        <v>67.90000000000001</v>
+        <v>51.16</v>
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>2.791</v>
+        <v>0.202</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.649</v>
+        <v>0.186</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2359,39 +2359,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>YXPM</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.72</v>
+        <v>0.215</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>-0.0145</v>
+        <v>-0.0444</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1008700</v>
+        <v>2574500</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.21</v>
+        <v>4.98</v>
       </c>
       <c r="H42" t="n">
-        <v>77.31999999999999</v>
-      </c>
-      <c r="I42" s="15" t="inlineStr">
+        <v>49.65</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.511</v>
+        <v>0.216</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.16</v>
+        <v>0.214</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2404,39 +2404,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0.0726</v>
+        <v>1.71</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>-0.0116</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>911800</v>
+        <v>2465700</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="H43" t="n">
-        <v>83.69</v>
-      </c>
-      <c r="I43" s="15" t="inlineStr">
+        <v>42.32</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.089</v>
+        <v>1.762</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.913</v>
+        <v>1.798</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2449,39 +2449,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.39</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0.121</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>907100</v>
+        <v>2341400</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.27</v>
+        <v>0.85</v>
       </c>
       <c r="H44" t="n">
-        <v>56.82</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.634</v>
+        <v>1.095</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.596</v>
+        <v>0.914</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2494,39 +2494,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>-0.0175</v>
+        <v>10.1</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0.011</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>893400</v>
+        <v>2302600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="H45" t="n">
-        <v>69.42</v>
+        <v>44.9</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.491</v>
+        <v>10.152</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.41</v>
+        <v>10.295</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2539,39 +2539,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>852000</v>
+        <v>2108500</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="H46" t="n">
-        <v>58.11</v>
+        <v>60.5</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.745</v>
+        <v>0.453</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1.551</v>
+        <v>0.413</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2584,39 +2584,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="E47" s="17" t="n">
-        <v>-0.0175</v>
+        <v>-0.0296</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>831600</v>
+        <v>2080300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="H47" t="n">
-        <v>43.59</v>
+        <v>45.15</v>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.5639999999999999</v>
+        <v>1.363</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.593</v>
+        <v>1.296</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2629,39 +2629,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0</v>
+        <v>0.74</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>814400</v>
+        <v>1894300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.22</v>
+        <v>0.04</v>
       </c>
       <c r="H48" t="n">
-        <v>60.43</v>
+        <v>53.23</v>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.115</v>
+        <v>0.736</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.021</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2674,39 +2674,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>0</v>
+        <v>2.32</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0.0131</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>786100</v>
+        <v>1858100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H49" t="n">
-        <v>75.67</v>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
+        <v>49.33</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.625</v>
+        <v>2.251</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2719,39 +2719,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>7.78</v>
+        <v>0.57</v>
       </c>
       <c r="E50" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>773000</v>
+        <v>1838600</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="H50" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="I50" s="15" t="inlineStr">
+        <v>72.42</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>7.801</v>
+        <v>0.492</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>7.741</v>
+        <v>0.411</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2764,39 +2764,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>-0.0058</v>
+        <v>0.365</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>767800</v>
+        <v>1830000</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="H51" t="n">
-        <v>43.37</v>
-      </c>
-      <c r="I51" s="15" t="inlineStr">
+        <v>48.25</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.763</v>
+        <v>0.367</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.798</v>
+        <v>0.367</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2809,39 +2809,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>4.42</v>
+        <v>0.91</v>
       </c>
       <c r="E52" s="17" t="n">
-        <v>-0.0156</v>
+        <v>-0.0319</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>685900</v>
+        <v>1758400</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.11</v>
+        <v>0.37</v>
       </c>
       <c r="H52" t="n">
-        <v>80.33</v>
-      </c>
-      <c r="I52" s="15" t="inlineStr">
+        <v>59.42</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>3.709</v>
+        <v>0.891</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>3.283</v>
+        <v>0.853</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2854,39 +2854,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0.0042</v>
+        <v>0.265</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>683900</v>
+        <v>1520700</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.04</v>
+        <v>0.54</v>
       </c>
       <c r="H53" t="n">
-        <v>36.44</v>
+        <v>71.53</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>4.824</v>
+        <v>0.232</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>4.946</v>
+        <v>0.211</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2899,39 +2899,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0275</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>656300</v>
+        <v>1414300</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="H54" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="I54" s="15" t="inlineStr">
+        <v>77.19</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.323</v>
+        <v>1.022</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.43</v>
+        <v>0.861</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2944,39 +2944,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>-0.0076</v>
+        <v>1.8</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>637300</v>
+        <v>1401300</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="H55" t="n">
-        <v>63.19</v>
-      </c>
-      <c r="I55" s="15" t="inlineStr">
+        <v>58.81</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.605</v>
+        <v>1.746</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.61</v>
+        <v>1.551</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2989,39 +2989,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0.0118</v>
+        <v>1.57</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>626800</v>
+        <v>1352200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.2</v>
+        <v>2.13</v>
       </c>
       <c r="H56" t="n">
-        <v>66.08</v>
+        <v>50.09</v>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.582</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.73</v>
+        <v>1.508</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3034,39 +3034,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>0</v>
+        <v>2.75</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>625200</v>
+        <v>1350400</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="H57" t="n">
-        <v>76.75</v>
-      </c>
-      <c r="I57" s="15" t="inlineStr">
+        <v>81.63</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.994</v>
+        <v>2.514</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.821</v>
+        <v>2.16</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3079,39 +3079,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.21</v>
+        <v>0.305</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0167</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>616400</v>
+        <v>1278800</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>35.52</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
+        <v>53.62</v>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>1.261</v>
+        <v>0.303</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1.3</v>
+        <v>0.291</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3124,39 +3124,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.05</v>
+        <v>2.9</v>
       </c>
       <c r="E59" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>611200</v>
+        <v>1249600</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H59" t="n">
-        <v>47.24</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.075</v>
+        <v>2.79</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.025</v>
+        <v>2.648</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3169,39 +3169,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.765</v>
+        <v>4.72</v>
       </c>
       <c r="E60" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>589800</v>
+        <v>1231900</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
+        <v>33.24</v>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.772</v>
+        <v>4.823</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.772</v>
+        <v>4.945</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3214,39 +3214,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>0</v>
+        <v>3.16</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0.0032</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>580400</v>
+        <v>1186600</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.08</v>
+        <v>0.37</v>
       </c>
       <c r="H61" t="n">
-        <v>43.06</v>
+        <v>32.75</v>
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>1.17</v>
+        <v>3.274</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1.148</v>
+        <v>3.465</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3259,39 +3259,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>-0.0157</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>524200</v>
+        <v>1154400</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H62" t="n">
-        <v>88.18000000000001</v>
-      </c>
-      <c r="I62" s="15" t="inlineStr">
+        <v>52.07</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>2.363</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.836</v>
+        <v>0.665</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3304,45 +3304,1755 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>0</v>
+        <v>4.47</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>518700</v>
+        <v>1104800</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="H63" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="I63" s="15" t="inlineStr">
+        <v>83.18000000000001</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>3.714</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.665</v>
+        <v>3.284</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>1078300</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H64" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>7.803</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>7.741</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>1054300</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H65" t="n">
+        <v>60.43</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>1049700</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H66" t="n">
+        <v>64.37</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>1030400</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H67" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>1019900</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H68" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>1014500</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H69" t="n">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>1003200</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H70" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H71" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="14" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>964800</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H72" t="n">
+        <v>78.62</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>-0.0157</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>933300</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H73" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>2.363</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>1.836</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>927000</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H74" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>2.452</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>2.296</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>918700</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H75" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="I75" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="14" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>908900</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H76" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>888800</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H77" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="14" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>881900</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H78" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0263</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BETA</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>-0.0401</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>862000</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H79" t="n">
+        <v>42.94</v>
+      </c>
+      <c r="I79" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="14" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>829300</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H80" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>799700</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H81" t="n">
+        <v>35.72</v>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="14" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>-0.0092</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>796100</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H82" t="n">
+        <v>74</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>780000</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H83" t="n">
+        <v>64.83</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="14" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>775600</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H84" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>770700</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H85" t="n">
+        <v>32.34</v>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>7.905</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>8.233000000000001</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="14" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>724500</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H86" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>4.524</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>4.521</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>710000</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H87" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="14" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>709300</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H88" t="n">
+        <v>56.27</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>2.883</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>2.699</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>696200</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H89" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="14" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>638700</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>91.45</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>637800</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="I91" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="14" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>634500</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H92" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>5.703</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>5.191</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>625700</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H93" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>599400</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H94" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>5.717</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>5.754</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>585500</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H95" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>578100</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H96" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="I96" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>7.655</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>7.829</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>545700</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H97" t="n">
+        <v>40.29</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>13.148</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>13.739</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="14" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>530600</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H98" t="n">
+        <v>36.42</v>
+      </c>
+      <c r="I98" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>523600</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H99" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>506000</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H100" t="n">
+        <v>70.42</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>-0.0137</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>505400</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H101" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>2.217</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M63"/>
+  <autoFilter ref="A1:M101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
+++ b/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -92,11 +92,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.495</v>
+        <v>0.505</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1786</v>
+        <v>0.2024</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>15661900</v>
+        <v>16755000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>10.8</v>
+        <v>11.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>74.34999999999999</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.415</v>
+        <v>0.416</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.412</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>EMA与SAR、Supertrend均呈多头排列，RSI达74.35已入超买区，现价高于50日均线约20%，信号偏强但短线过热。</t>
+          <t>EMA与SAR、Supertrend均呈多头排列，但RSI达75.68已超买，现价高于50日均线约22.6%，信号偏热。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5.03</v>
+        <v>5.11</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0261</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>16796700</v>
+        <v>22170700</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.88</v>
+        <v>1.17</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>71.06</v>
+        <v>73.86</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>4.792</v>
+        <v>4.8</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>4.543</v>
+        <v>4.545</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>RSI 71.06已超买，现价5.03高于50日均线4.543约10.7%，短期均线多头排列，信号偏强但需留意超买风险。</t>
+          <t>RSI达73.86，已进入超买区；现价5.11高于50日均线4.545约12%，短期均线多头排列，信号偏强但需留意超买风险。</t>
         </is>
       </c>
     </row>
@@ -663,39 +663,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.26</v>
+        <v>0.175</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.1064</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>78281000</v>
+        <v>81898100</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>4.02</v>
+        <v>0.14</v>
       </c>
       <c r="H4" t="n">
-        <v>65.14</v>
+        <v>23.59</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.235</v>
+        <v>0.256</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.233</v>
+        <v>0.47</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -708,39 +708,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.175</v>
+        <v>0.255</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.0851</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>76343200</v>
+        <v>80405000</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.13</v>
+        <v>4.13</v>
       </c>
       <c r="H5" t="n">
-        <v>23.59</v>
+        <v>63.19</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.256</v>
+        <v>0.234</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.47</v>
+        <v>0.233</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -768,15 +768,15 @@
         <v>0.0625</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>27800400</v>
+        <v>27905100</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="H6" t="n">
         <v>39.42</v>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -807,27 +807,27 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0</v>
+        <v>0.195</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>14203000</v>
+        <v>14369300</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H7" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.154</v>
+        <v>0.155</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0.12</v>
@@ -843,39 +843,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0051</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CUSCAPI</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.1</v>
+        <v>0.595</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>11400900</v>
+        <v>12231000</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="H8" t="n">
-        <v>42.26</v>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
+        <v>72.05</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.058</v>
+        <v>0.555</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.076</v>
+        <v>0.495</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -888,39 +888,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0</v>
+        <v>0.055</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.1</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>10771600</v>
+        <v>11400900</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="H9" t="n">
-        <v>72.05</v>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
+        <v>42.26</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.555</v>
+        <v>0.058</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.495</v>
+        <v>0.076</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -956,7 +956,7 @@
       <c r="H10" t="n">
         <v>60.06</v>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -993,15 +993,15 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9293800</v>
+        <v>9393800</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.92</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.515</v>
+        <v>0.52</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>-0.0721</v>
+        <v>-0.06309999999999999</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>7358200</v>
+        <v>8185500</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="H12" t="n">
-        <v>46.92</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
+        <v>48.52</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1083,7 +1083,7 @@
         <v>0.0208</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6625700</v>
+        <v>6646700</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>0.23</v>
@@ -1091,7 +1091,7 @@
       <c r="H13" t="n">
         <v>33.57</v>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1122,21 +1122,21 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.21</v>
+        <v>0.215</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.0244</v>
+        <v>0.0488</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6163500</v>
+        <v>6478300</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H14" t="n">
-        <v>30.94</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
+        <v>35.23</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1158,39 +1158,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.06059999999999999</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>5859500</v>
+        <v>6339100</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="H15" t="n">
-        <v>39.82</v>
+        <v>60.92</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.886</v>
+        <v>0.332</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.959</v>
+        <v>0.314</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1203,33 +1203,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>0</v>
+        <v>1.83</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>5764100</v>
+        <v>5990200</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.39</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>41.23</v>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>1.887</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>1.959</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
     </row>
@@ -1241,40 +1248,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0.0106</v>
+        <v>0.26</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5343800</v>
+        <v>5816700</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H17" t="n">
-        <v>52.83</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>0.472</v>
-      </c>
+        <v>0.39</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
     </row>
@@ -1286,39 +1286,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0</v>
+        <v>0.475</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>5192500</v>
+        <v>5363700</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="H18" t="n">
-        <v>78.19</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
+        <v>52.83</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.332</v>
+        <v>0.469</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.197</v>
+        <v>0.472</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.39</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5091600</v>
+        <v>5198200</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.67</v>
+        <v>0.11</v>
       </c>
       <c r="H19" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
+        <v>78.19</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.314</v>
+        <v>0.197</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1376,39 +1376,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.39</v>
+        <v>0.11</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>-0.0127</v>
+        <v>-0.0435</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>4812200</v>
+        <v>5154200</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.45</v>
+        <v>0.62</v>
       </c>
       <c r="H20" t="n">
-        <v>64.22</v>
+        <v>37.36</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.377</v>
+        <v>0.121</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.372</v>
+        <v>0.124</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1421,39 +1421,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.395</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4559700</v>
+        <v>4862200</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H21" t="n">
-        <v>48.44</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
+        <v>70.45</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.607</v>
+        <v>0.377</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.606</v>
+        <v>0.372</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1466,39 +1466,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.52</v>
+        <v>0.435</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.0196</v>
+        <v>0.0357</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>4495500</v>
+        <v>4731400</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.12</v>
+        <v>2.37</v>
       </c>
       <c r="H22" t="n">
-        <v>27.66</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.612</v>
+        <v>0.381</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.827</v>
+        <v>0.346</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1511,39 +1511,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0.0333</v>
+        <v>0.605</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>4458500</v>
+        <v>4559700</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H23" t="n">
-        <v>50.05</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
+        <v>48.44</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.157</v>
+        <v>0.607</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.148</v>
+        <v>0.606</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1556,39 +1556,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>-0.0435</v>
+        <v>0.52</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>4237400</v>
+        <v>4527700</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.51</v>
+        <v>0.12</v>
       </c>
       <c r="H24" t="n">
-        <v>37.36</v>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
+        <v>27.66</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.121</v>
+        <v>0.612</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.124</v>
+        <v>0.827</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1601,39 +1601,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>-0.0476</v>
+        <v>0.155</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4188700</v>
+        <v>4525800</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.67</v>
+        <v>0.11</v>
       </c>
       <c r="H25" t="n">
-        <v>74.37</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
+        <v>50.05</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.157</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.148</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1646,40 +1646,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.0595</v>
+        <v>0.12</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4021000</v>
+        <v>4445600</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="H26" t="n">
-        <v>76.11</v>
+        <v>0.11</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>0.346</v>
-      </c>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
     </row>
@@ -1691,33 +1684,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>3956700</v>
+        <v>4235500</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.09</v>
+        <v>0.32</v>
+      </c>
+      <c r="H27" t="n">
+        <v>48.13</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="9" t="n"/>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.774</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
     </row>
@@ -1729,39 +1729,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.77</v>
+        <v>0.1</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.0476</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3793200</v>
+        <v>4188700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.28</v>
+        <v>0.67</v>
       </c>
       <c r="H28" t="n">
-        <v>48.13</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
+        <v>74.37</v>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.773</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.774</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1774,39 +1774,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>-0.0135</v>
+        <v>0.47</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>3517600</v>
+        <v>4011700</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H29" t="n">
-        <v>64.36</v>
+        <v>58.22</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>2.683</v>
+        <v>0.452</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2.522</v>
+        <v>0.413</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1819,39 +1819,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>-0.0048</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3442900</v>
+        <v>3660400</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H30" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
+        <v>50.19</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>2.117</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>2.066</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1864,39 +1864,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0.0282</v>
+        <v>2.95</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>-0.0067</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3285700</v>
+        <v>3633800</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="H31" t="n">
-        <v>66.09</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
+        <v>65.58</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.341</v>
+        <v>2.684</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.321</v>
+        <v>2.522</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1909,39 +1909,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.405</v>
+        <v>0.575</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>-0.0122</v>
+        <v>-0.0086</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3015100</v>
+        <v>3597200</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="H32" t="n">
-        <v>46.39</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
+        <v>63.01</v>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.409</v>
+        <v>0.533</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.411</v>
+        <v>0.485</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1954,39 +1954,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.575</v>
+        <v>2.07</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>-0.0086</v>
+        <v>-0.0048</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>2968300</v>
+        <v>3510500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H33" t="n">
-        <v>63.01</v>
+        <v>44.75</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.533</v>
+        <v>2.117</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.485</v>
+        <v>2.066</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1999,39 +1999,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>-0.0645</v>
+        <v>0.365</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0.0282</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>2901000</v>
+        <v>3484700</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.24</v>
+        <v>0.49</v>
       </c>
       <c r="H34" t="n">
-        <v>66.66</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
+        <v>66.09</v>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>3.645</v>
+        <v>0.341</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>2.467</v>
+        <v>0.321</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2044,39 +2044,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0.0305</v>
+        <v>4.08</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>-0.0599</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2871900</v>
+        <v>3467800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="H35" t="n">
-        <v>61.53</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
+        <v>67.28</v>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.638</v>
+        <v>3.647</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.581</v>
+        <v>2.468</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2089,39 +2089,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>2842300</v>
+        <v>3351700</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H36" t="n">
-        <v>55.3</v>
+        <v>46.81</v>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.383</v>
+        <v>0.868</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.325</v>
+        <v>0.87</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2134,39 +2134,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.225</v>
+        <v>0.405</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>-0.0217</v>
+        <v>-0.0122</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2802700</v>
+        <v>3189600</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.74</v>
+        <v>0.29</v>
       </c>
       <c r="H37" t="n">
-        <v>65.48999999999999</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
+        <v>46.39</v>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.206</v>
+        <v>0.409</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.181</v>
+        <v>0.411</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2179,39 +2179,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.0382</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2800400</v>
+        <v>2994100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.19</v>
+        <v>0.31</v>
       </c>
       <c r="H38" t="n">
-        <v>50.19</v>
+        <v>62.34</v>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.638</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.581</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2224,39 +2224,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.39</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2684700</v>
+        <v>2885500</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H39" t="n">
-        <v>46.81</v>
+        <v>55.3</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.868</v>
+        <v>0.383</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.87</v>
+        <v>0.325</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2269,39 +2269,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2669800</v>
+        <v>2855600</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.13</v>
+        <v>0.75</v>
       </c>
       <c r="H40" t="n">
-        <v>46.6</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.573</v>
+        <v>0.206</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.452</v>
+        <v>0.181</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2314,39 +2314,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>-0.0244</v>
+        <v>2.51</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2647200</v>
+        <v>2693500</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="H41" t="n">
-        <v>51.16</v>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
+        <v>46.6</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.202</v>
+        <v>2.573</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.186</v>
+        <v>2.452</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2359,39 +2359,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YXPM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>-0.0444</v>
+        <v>0.205</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2574500</v>
+        <v>2680900</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>4.98</v>
+        <v>0.11</v>
       </c>
       <c r="H42" t="n">
-        <v>49.65</v>
+        <v>55.27</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.216</v>
+        <v>0.203</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.214</v>
+        <v>0.186</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2404,39 +2404,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>-0.0116</v>
+        <v>0.305</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2465700</v>
+        <v>2673800</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="H43" t="n">
-        <v>42.32</v>
+        <v>53.62</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.762</v>
+        <v>0.303</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.798</v>
+        <v>0.291</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2449,39 +2449,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.39</v>
+        <v>10.1</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>0.121</v>
+        <v>0.011</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2341400</v>
+        <v>2637200</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.85</v>
+        <v>0.21</v>
       </c>
       <c r="H44" t="n">
-        <v>85.59999999999999</v>
+        <v>44.9</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>1.095</v>
+        <v>10.152</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.914</v>
+        <v>10.295</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2494,39 +2494,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>YXPM</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0.011</v>
+        <v>0.215</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>-0.0444</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2302600</v>
+        <v>2574500</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.18</v>
+        <v>4.98</v>
       </c>
       <c r="H45" t="n">
-        <v>44.9</v>
+        <v>49.65</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>10.152</v>
+        <v>0.216</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>10.295</v>
+        <v>0.214</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2539,39 +2539,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.48</v>
+        <v>1.37</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.0213</v>
+        <v>0.1048</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2108500</v>
+        <v>2564000</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.21</v>
+        <v>0.93</v>
       </c>
       <c r="H46" t="n">
-        <v>60.5</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.453</v>
+        <v>1.093</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.413</v>
+        <v>0.914</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2584,39 +2584,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1.31</v>
+        <v>1.72</v>
       </c>
       <c r="E47" s="17" t="n">
-        <v>-0.0296</v>
+        <v>-0.0058</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2080300</v>
+        <v>2491700</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="H47" t="n">
-        <v>45.15</v>
+        <v>43.37</v>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.363</v>
+        <v>1.763</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>1.296</v>
+        <v>1.798</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2638,21 +2638,21 @@
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0.0068</v>
+        <v>0.735</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1894300</v>
+        <v>2302500</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H48" t="n">
-        <v>53.23</v>
-      </c>
-      <c r="I48" s="15" t="inlineStr">
+        <v>52.16</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2674,39 +2674,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0.0131</v>
+        <v>1.31</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>-0.0296</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1858100</v>
+        <v>2260700</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="H49" t="n">
-        <v>49.33</v>
+        <v>45.15</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>2.34</v>
+        <v>1.363</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>2.251</v>
+        <v>1.296</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2734,15 +2734,15 @@
         <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1838600</v>
+        <v>2044100</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H50" t="n">
         <v>72.42</v>
       </c>
-      <c r="I50" s="13" t="inlineStr">
+      <c r="I50" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -2764,39 +2764,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>0</v>
+        <v>2.31</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1830000</v>
+        <v>2029500</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.29</v>
+        <v>0.12</v>
       </c>
       <c r="H51" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
+        <v>48.57</v>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.367</v>
+        <v>2.339</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.367</v>
+        <v>2.251</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2809,39 +2809,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>-0.0319</v>
+        <v>0.365</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1758400</v>
+        <v>2016400</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="H52" t="n">
-        <v>59.42</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
+        <v>48.25</v>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.891</v>
+        <v>0.367</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.853</v>
+        <v>0.367</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2854,39 +2854,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.265</v>
+        <v>0.905</v>
       </c>
       <c r="E53" s="17" t="n">
-        <v>-0.0185</v>
+        <v>-0.0372</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1520700</v>
+        <v>1858200</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
       <c r="H53" t="n">
-        <v>71.53</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
+        <v>57.59</v>
+      </c>
+      <c r="I53" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.232</v>
+        <v>0.89</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.211</v>
+        <v>0.853</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2899,39 +2899,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.0275</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1414300</v>
+        <v>1685600</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>77.19</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
+        <v>58.81</v>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.022</v>
+        <v>1.746</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.861</v>
+        <v>1.551</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2944,39 +2944,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.005600000000000001</v>
+        <v>2.88</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1401300</v>
+        <v>1619900</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="H55" t="n">
-        <v>58.81</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.746</v>
+        <v>2.789</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>1.551</v>
+        <v>2.648</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2989,39 +2989,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.57</v>
+        <v>1.03</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>-0.0063</v>
+        <v>-0.019</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1352200</v>
+        <v>1605000</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>2.13</v>
+        <v>0.14</v>
       </c>
       <c r="H56" t="n">
-        <v>50.09</v>
-      </c>
-      <c r="I56" s="15" t="inlineStr">
+        <v>44.39</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>1.582</v>
+        <v>1.074</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.508</v>
+        <v>1.025</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3043,30 +3043,30 @@
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>-0.0036</v>
+        <v>2.76</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1350400</v>
+        <v>1543600</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="H57" t="n">
-        <v>81.63</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
+        <v>83.18000000000001</v>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.514</v>
+        <v>2.515</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.16</v>
+        <v>2.161</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3079,39 +3079,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0.0167</v>
+        <v>0.265</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1278800</v>
+        <v>1538200</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H58" t="n">
-        <v>53.62</v>
+        <v>71.53</v>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.303</v>
+        <v>0.232</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.291</v>
+        <v>0.211</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3124,39 +3124,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>0</v>
+        <v>1.54</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>-0.0253</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1249600</v>
+        <v>1486000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.08</v>
+        <v>2.34</v>
       </c>
       <c r="H59" t="n">
-        <v>67.18000000000001</v>
+        <v>44.38</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>2.79</v>
+        <v>1.58</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2.648</v>
+        <v>1.507</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3169,39 +3169,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>4.72</v>
+        <v>1.12</v>
       </c>
       <c r="E60" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1231900</v>
+        <v>1459400</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="H60" t="n">
-        <v>33.24</v>
+        <v>43.06</v>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>4.823</v>
+        <v>1.17</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>4.945</v>
+        <v>1.148</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3214,39 +3214,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>3.16</v>
+        <v>1.12</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>0.0032</v>
+        <v>0.0275</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1186600</v>
+        <v>1441300</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="H61" t="n">
-        <v>32.75</v>
+        <v>77.19</v>
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>3.274</v>
+        <v>1.022</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>3.465</v>
+        <v>0.861</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3259,39 +3259,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.72</v>
       </c>
       <c r="E62" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1154400</v>
+        <v>1406500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="H62" t="n">
-        <v>52.07</v>
+        <v>33.24</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>4.823</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.665</v>
+        <v>4.945</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3304,39 +3304,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="E63" s="17" t="n">
-        <v>-0.004500000000000001</v>
+        <v>1.16</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1104800</v>
+        <v>1392000</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="H63" t="n">
-        <v>83.18000000000001</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
+        <v>61.75</v>
+      </c>
+      <c r="I63" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>3.714</v>
+        <v>1.116</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>3.284</v>
+        <v>1.021</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3358,27 +3358,27 @@
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>7.8</v>
+        <v>7.79</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0013</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1078300</v>
+        <v>1375000</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H64" t="n">
-        <v>50.83</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
+        <v>50.34</v>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>7.803</v>
+        <v>7.802</v>
       </c>
       <c r="K64" s="9" t="n">
         <v>7.741</v>
@@ -3394,39 +3394,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E65" s="16" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1054300</v>
+        <v>1326300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.28</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>60.43</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
+        <v>61.78</v>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.115</v>
+        <v>0.506</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.021</v>
+        <v>0.413</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3439,39 +3439,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.79</v>
+        <v>4.51</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>0.0064</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1049700</v>
+        <v>1299400</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H66" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.768</v>
+        <v>3.718</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.754</v>
+        <v>3.285</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3484,39 +3484,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>-0.0076</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1030400</v>
+        <v>1283500</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.35</v>
+        <v>0.16</v>
       </c>
       <c r="H67" t="n">
-        <v>63.19</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
+        <v>52.07</v>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.605</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.61</v>
+        <v>0.665</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3529,39 +3529,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E68" s="16" t="n">
-        <v>0</v>
+        <v>0.79</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1019900</v>
+        <v>1266800</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="H68" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
+        <v>64.37</v>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.768</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.73</v>
+        <v>0.754</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3574,39 +3574,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>-0.0064</v>
+        <v>3.16</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0.0032</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1014500</v>
+        <v>1232500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="H69" t="n">
-        <v>73.98999999999999</v>
+        <v>32.75</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.274</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.625</v>
+        <v>3.465</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3619,39 +3619,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.65</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1003200</v>
+        <v>1081700</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="H70" t="n">
-        <v>44.53</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
+        <v>61.67</v>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>1.171</v>
+        <v>0.604</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1.148</v>
+        <v>0.61</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3664,39 +3664,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>-0.0175</v>
+        <v>0.845</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1000000</v>
+        <v>1067400</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="H71" t="n">
-        <v>43.59</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.593</v>
+        <v>0.73</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3724,15 +3724,15 @@
         <v>0.0189</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>964800</v>
+        <v>1065800</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H72" t="n">
         <v>78.62</v>
       </c>
-      <c r="I72" s="13" t="inlineStr">
+      <c r="I72" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3754,39 +3754,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>-0.0157</v>
+        <v>1.2</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>933300</v>
+        <v>1057800</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="H73" t="n">
-        <v>88.18000000000001</v>
+        <v>32.5</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>2.363</v>
+        <v>1.26</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>1.836</v>
+        <v>1.299</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3799,39 +3799,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0263</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0.004</v>
+        <v>0.67</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>-0.0401</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>927000</v>
+        <v>1055000</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.06</v>
+        <v>1.97</v>
       </c>
       <c r="H74" t="n">
-        <v>62.3</v>
+        <v>42.94</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>2.452</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>2.296</v>
+        <v>0.711</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3844,39 +3844,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>3</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0.0033</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>918700</v>
+        <v>1022300</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H75" t="n">
-        <v>56.82</v>
+        <v>57.29</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.634</v>
+        <v>2.885</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.596</v>
+        <v>2.699</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3889,39 +3889,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>908900</v>
+        <v>1017400</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H76" t="n">
-        <v>32.5</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>1.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1.299</v>
+        <v>0.625</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3934,39 +3934,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1.03</v>
+        <v>3.16</v>
       </c>
       <c r="E77" s="17" t="n">
-        <v>-0.019</v>
+        <v>-0.0063</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>888800</v>
+        <v>1010000</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.08</v>
+        <v>0.34</v>
       </c>
       <c r="H77" t="n">
-        <v>44.39</v>
+        <v>90.31</v>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>1.074</v>
+        <v>2.366</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.025</v>
+        <v>1.837</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3979,39 +3979,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0.0159</v>
+        <v>1.28</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>881900</v>
+        <v>1002900</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="H78" t="n">
-        <v>57.06</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
+        <v>93.38</v>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.622</v>
+        <v>0.952</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.586</v>
+        <v>0.758</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4024,39 +4024,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0263</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E79" s="17" t="n">
-        <v>-0.0401</v>
+        <v>-0.0175</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>862000</v>
+        <v>1001500</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.61</v>
+        <v>0.27</v>
       </c>
       <c r="H79" t="n">
-        <v>42.94</v>
+        <v>43.59</v>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.711</v>
+        <v>0.593</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4069,39 +4069,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>829300</v>
+        <v>993800</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.27</v>
+        <v>0.09</v>
       </c>
       <c r="H80" t="n">
-        <v>50.34</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
+        <v>63.64</v>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.569</v>
+        <v>0.727</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.575</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4114,39 +4114,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.64</v>
+        <v>2.51</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.004</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>799700</v>
+        <v>947100</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="H81" t="n">
-        <v>35.72</v>
+        <v>62.3</v>
       </c>
       <c r="I81" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.714</v>
+        <v>2.452</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.831</v>
+        <v>2.296</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4159,39 +4159,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E82" s="17" t="n">
-        <v>-0.0092</v>
+        <v>0.64</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>796100</v>
+        <v>935600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="H82" t="n">
-        <v>74</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
+        <v>57.06</v>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.993</v>
+        <v>0.622</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.821</v>
+        <v>0.586</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4204,39 +4204,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.75</v>
+        <v>7.61</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>780000</v>
+        <v>928700</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="H83" t="n">
-        <v>64.83</v>
+        <v>31.71</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>7.904</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.62</v>
+        <v>8.233000000000001</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4249,39 +4249,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>775600</v>
+        <v>918700</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="H84" t="n">
-        <v>35.76</v>
-      </c>
-      <c r="I84" s="15" t="inlineStr">
+        <v>56.82</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.556</v>
+        <v>0.634</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.587</v>
+        <v>0.596</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>7.62</v>
+        <v>1.64</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>0.0106</v>
+        <v>0.0123</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>770700</v>
+        <v>840000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="H85" t="n">
-        <v>32.34</v>
-      </c>
-      <c r="I85" s="15" t="inlineStr">
+        <v>35.72</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>7.905</v>
+        <v>1.714</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>8.233000000000001</v>
+        <v>1.831</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4339,39 +4339,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>-0.014</v>
+        <v>0.57</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>724500</v>
+        <v>834400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.09</v>
+        <v>0.27</v>
       </c>
       <c r="H86" t="n">
-        <v>39.78</v>
+        <v>50.34</v>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>4.524</v>
+        <v>0.569</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>4.521</v>
+        <v>0.575</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4384,39 +4384,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>831000</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H87" t="n">
+        <v>64.18000000000001</v>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="K87" s="9" t="n">
         <v>0.62</v>
-      </c>
-      <c r="E87" s="17" t="n">
-        <v>-0.0159</v>
-      </c>
-      <c r="F87" s="11" t="n">
-        <v>710000</v>
-      </c>
-      <c r="G87" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H87" t="n">
-        <v>36.72</v>
-      </c>
-      <c r="I87" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J87" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K87" s="9" t="n">
-        <v>0.636</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4429,39 +4429,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="E88" s="17" t="n">
-        <v>-0.0033</v>
+        <v>1.09</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>709300</v>
+        <v>819700</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="H88" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
+        <v>76.75</v>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.883</v>
+        <v>0.994</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>2.699</v>
+        <v>0.821</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4474,39 +4474,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>4.27</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>696200</v>
+        <v>793300</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H89" t="n">
-        <v>38.26</v>
+        <v>40.83</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.323</v>
+        <v>4.528</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.43</v>
+        <v>4.522</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4519,39 +4519,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>1.27</v>
+        <v>0.53</v>
       </c>
       <c r="E90" s="17" t="n">
-        <v>-0.0155</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>638700</v>
+        <v>782100</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H90" t="n">
-        <v>91.45</v>
+        <v>34.14</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.951</v>
+        <v>0.555</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.757</v>
+        <v>0.586</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4564,39 +4564,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>0</v>
+        <v>12.98</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>637800</v>
+        <v>751500</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H91" t="n">
-        <v>46.13</v>
+        <v>39.49</v>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.772</v>
+        <v>13.146</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.772</v>
+        <v>13.739</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4624,15 +4624,15 @@
         <v>-0.0069</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>634500</v>
+        <v>724400</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H92" t="n">
         <v>57.12</v>
       </c>
-      <c r="I92" s="13" t="inlineStr">
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -4654,39 +4654,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.915</v>
+        <v>0.62</v>
       </c>
       <c r="E93" s="17" t="n">
-        <v>-0.0054</v>
+        <v>-0.0159</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>625700</v>
+        <v>710000</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.27</v>
+        <v>0.7</v>
       </c>
       <c r="H93" t="n">
-        <v>39.72</v>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
+        <v>36.72</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.929</v>
+        <v>0.63</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.947</v>
+        <v>0.636</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4699,39 +4699,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="E94" s="17" t="n">
-        <v>-0.005600000000000001</v>
+        <v>1.3</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>599400</v>
+        <v>699900</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="H94" t="n">
-        <v>39.6</v>
+        <v>40.64</v>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>5.717</v>
+        <v>1.323</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>5.754</v>
+        <v>1.43</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4744,39 +4744,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>0</v>
+        <v>7.53</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0.0107</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>585500</v>
+        <v>697300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.42</v>
+        <v>0.1</v>
       </c>
       <c r="H95" t="n">
-        <v>52.65</v>
+        <v>42.08</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.634</v>
+        <v>7.654</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.629</v>
+        <v>7.828</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4789,39 +4789,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0.0121</v>
+        <v>0.91</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>578100</v>
+        <v>682500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.08</v>
+        <v>0.3</v>
       </c>
       <c r="H96" t="n">
-        <v>42.58</v>
-      </c>
-      <c r="I96" s="15" t="inlineStr">
+        <v>37.66</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>7.655</v>
+        <v>0.929</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>7.829</v>
+        <v>0.947</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4834,39 +4834,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0.022</v>
+        <v>5.34</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>545700</v>
+        <v>675600</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="H97" t="n">
-        <v>40.29</v>
+        <v>39.18</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>13.148</v>
+        <v>5.715</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>13.739</v>
+        <v>5.754</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4879,39 +4879,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.765</v>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>530600</v>
+        <v>637800</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H98" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="I98" s="15" t="inlineStr">
+        <v>46.13</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.375</v>
+        <v>0.772</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.317</v>
+        <v>0.772</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>-0.0123</v>
+        <v>1.45</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>523600</v>
+        <v>609500</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="H99" t="n">
-        <v>63.64</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
+        <v>42.53</v>
+      </c>
+      <c r="I99" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.727</v>
+        <v>1.473</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4969,39 +4969,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0.03</v>
+        <v>2.16</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>506000</v>
+        <v>588200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.89</v>
+        <v>0.08</v>
       </c>
       <c r="H100" t="n">
-        <v>70.42</v>
+        <v>47.14</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.988</v>
+        <v>2.217</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.976</v>
+        <v>2.109</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5014,45 +5014,180 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E101" s="17" t="n">
-        <v>-0.0137</v>
+        <v>0.635</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>505400</v>
+        <v>585500</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="H101" t="n">
-        <v>47.14</v>
+        <v>52.65</v>
       </c>
       <c r="I101" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>2.217</v>
+        <v>0.634</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>2.109</v>
+        <v>0.629</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>568000</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H102" t="n">
+        <v>36.42</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>508300</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H103" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>506000</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H104" t="n">
+        <v>70.42</v>
+      </c>
+      <c r="I104" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M101"/>
+  <autoFilter ref="A1:M104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
+++ b/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.505</v>
+        <v>0.515</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.2024</v>
+        <v>0.2262</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>16755000</v>
+        <v>17872500</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>11.56</v>
+        <v>12.33</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>75.68000000000001</v>
+        <v>76.87</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.416</v>
+        <v>0.417</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.412</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>EMA与SAR、Supertrend均呈多头排列，但RSI达75.68已超买，现价高于50日均线约22.6%，信号偏热。</t>
+          <t>EMA与SAR、Supertrend均呈多头排列，但RSI达76.87已入超买区，现价高于50日均线约25%，信号偏热。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0261</v>
+        <v>0.0241</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>22170700</v>
+        <v>25633800</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>73.86</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>4.8</v>
+        <v>4.799</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>4.545</v>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>RSI达73.86，已进入超买区；现价5.11高于50日均线4.545约12%，短期均线多头排列，信号偏强但需留意超买风险。</t>
+          <t>RSI达73.54，已进入超买区；现价5.1高于50日均线4.545约12%，短期均线多头排列，信号偏强但需留意超买风险。</t>
         </is>
       </c>
     </row>
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.175</v>
+        <v>0.17</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.0303</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>81898100</v>
+        <v>110629500</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="H4" t="n">
-        <v>23.59</v>
+        <v>22.06</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         <v>0.0851</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>80405000</v>
+        <v>86171200</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>4.13</v>
+        <v>4.43</v>
       </c>
       <c r="H5" t="n">
         <v>63.19</v>
@@ -768,10 +768,10 @@
         <v>0.0625</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>27905100</v>
+        <v>28129300</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="H6" t="n">
         <v>39.42</v>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0.0263</v>
+        <v>0.19</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>14369300</v>
+        <v>14938600</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H7" t="n">
-        <v>80.31999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0.12</v>
@@ -852,19 +852,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>12231000</v>
+        <v>13563700</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="H8" t="n">
-        <v>72.05</v>
+        <v>69.39</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>0.1</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>11400900</v>
+        <v>11460900</v>
       </c>
       <c r="G9" s="12" t="n">
         <v>0.45</v>
@@ -948,10 +948,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>9828100</v>
+        <v>9843300</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>141.5</v>
+        <v>141.72</v>
       </c>
       <c r="H10" t="n">
         <v>60.06</v>
@@ -993,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9393800</v>
+        <v>9413800</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="H11" t="n">
         <v>48.92</v>
@@ -1038,10 +1038,10 @@
         <v>-0.06309999999999999</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>8185500</v>
+        <v>9011800</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="H12" t="n">
         <v>48.52</v>
@@ -1068,28 +1068,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.245</v>
+        <v>0.355</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.0208</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6646700</v>
+        <v>7836700</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.23</v>
+        <v>1.03</v>
       </c>
       <c r="H13" t="n">
-        <v>33.57</v>
+        <v>62.52</v>
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.27</v>
+        <v>0.332</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.322</v>
+        <v>0.314</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1113,39 +1113,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.215</v>
+        <v>0.25</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.0488</v>
+        <v>0.0417</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6478300</v>
+        <v>6939900</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="H14" t="n">
-        <v>35.23</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.22</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.233</v>
+        <v>0.271</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.247</v>
+        <v>0.322</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1158,39 +1158,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.455</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>-0.0319</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>6339100</v>
+        <v>6869600</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.84</v>
+        <v>0.7</v>
       </c>
       <c r="H15" t="n">
-        <v>60.92</v>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.57</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.332</v>
+        <v>0.45</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.314</v>
+        <v>0.413</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1203,28 +1203,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1.83</v>
+        <v>0.215</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0488</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>5990200</v>
+        <v>6810400</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="H16" t="n">
-        <v>41.23</v>
+        <v>35.23</v>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.887</v>
+        <v>0.233</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1.959</v>
+        <v>0.247</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1248,33 +1248,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0</v>
+        <v>0.11</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5816700</v>
+        <v>6192100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
+        <v>0.75</v>
+      </c>
+      <c r="H17" t="n">
+        <v>37.36</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.124</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
     </row>
@@ -1286,39 +1293,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.475</v>
+        <v>1.83</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>0.0106</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>5363700</v>
+        <v>6047400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.22</v>
+        <v>0.82</v>
       </c>
       <c r="H18" t="n">
-        <v>52.83</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.23</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.469</v>
+        <v>1.887</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.472</v>
+        <v>1.959</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1331,40 +1338,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0</v>
+        <v>0.255</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5198200</v>
+        <v>5917500</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H19" t="n">
-        <v>78.19</v>
+        <v>0.4</v>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J19" s="9" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>0.197</v>
-      </c>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
     </row>
@@ -1376,28 +1376,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>-0.0435</v>
+        <v>0.52</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>5154200</v>
+        <v>5436000</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.62</v>
+        <v>0.14</v>
       </c>
       <c r="H20" t="n">
-        <v>37.36</v>
+        <v>27.66</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.121</v>
+        <v>0.612</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.124</v>
+        <v>0.827</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1421,28 +1421,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0</v>
+        <v>0.475</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4862200</v>
+        <v>5363700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.45</v>
+        <v>0.22</v>
       </c>
       <c r="H21" t="n">
-        <v>70.45</v>
+        <v>52.83</v>
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.377</v>
+        <v>0.469</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.372</v>
+        <v>0.472</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1466,28 +1466,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0.0357</v>
+        <v>0.39</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>4731400</v>
+        <v>5198200</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>2.37</v>
+        <v>0.11</v>
       </c>
       <c r="H22" t="n">
-        <v>74.40000000000001</v>
+        <v>78.19</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.381</v>
+        <v>0.332</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.346</v>
+        <v>0.197</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1511,28 +1511,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.605</v>
+        <v>0.77</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>4559700</v>
+        <v>5115800</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="H23" t="n">
-        <v>48.44</v>
+        <v>48.13</v>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.607</v>
+        <v>0.773</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.606</v>
+        <v>0.774</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1556,39 +1556,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.0196</v>
+        <v>0.0127</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>4527700</v>
+        <v>5096500</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.12</v>
+        <v>1.18</v>
       </c>
       <c r="H24" t="n">
-        <v>27.66</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.74</v>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.612</v>
+        <v>0.802</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.827</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1601,28 +1601,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.155</v>
+        <v>0.44</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0.0333</v>
+        <v>0.0476</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4525800</v>
+        <v>4977400</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.11</v>
+        <v>2.49</v>
       </c>
       <c r="H25" t="n">
-        <v>50.05</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.157</v>
+        <v>0.381</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.148</v>
+        <v>0.346</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1646,33 +1646,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.12</v>
+        <v>0.39</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>-0.04</v>
+        <v>-0.0127</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4445600</v>
+        <v>4865500</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
+        <v>0.45</v>
+      </c>
+      <c r="H26" t="n">
+        <v>64.22</v>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.372</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
     </row>
@@ -1684,28 +1691,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.77</v>
+        <v>0.605</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4235500</v>
+        <v>4792700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
       <c r="H27" t="n">
-        <v>48.13</v>
+        <v>48.44</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
@@ -1713,10 +1720,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.773</v>
+        <v>0.607</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.774</v>
+        <v>0.606</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1729,39 +1736,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>-0.0476</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4188700</v>
+        <v>4692400</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="H28" t="n">
-        <v>74.37</v>
-      </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.19</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1774,39 +1781,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>0</v>
+        <v>0.155</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4011700</v>
+        <v>4627000</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.41</v>
+        <v>0.11</v>
       </c>
       <c r="H29" t="n">
-        <v>58.22</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.05</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.452</v>
+        <v>0.157</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.413</v>
+        <v>0.148</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1819,40 +1826,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>0</v>
+        <v>0.12</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3660400</v>
+        <v>4554800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H30" t="n">
-        <v>50.19</v>
+        <v>0.11</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J30" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>0.8070000000000001</v>
-      </c>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
     </row>
@@ -1864,28 +1864,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2.95</v>
+        <v>0.865</v>
       </c>
       <c r="E31" s="17" t="n">
-        <v>-0.0067</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3633800</v>
+        <v>4313200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="H31" t="n">
-        <v>65.58</v>
+        <v>46.81</v>
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>2.684</v>
+        <v>0.868</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>2.522</v>
+        <v>0.87</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1909,39 +1909,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>-0.0086</v>
+        <v>0.305</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3597200</v>
+        <v>4179800</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="H32" t="n">
-        <v>63.01</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.62</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.533</v>
+        <v>0.303</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.485</v>
+        <v>0.291</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1954,39 +1954,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2.07</v>
+        <v>0.575</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>-0.0048</v>
+        <v>-0.0086</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3510500</v>
+        <v>4088000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="H33" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.01</v>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>2.117</v>
+        <v>0.533</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>2.066</v>
+        <v>0.485</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         <v>0.0282</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3484700</v>
+        <v>4019300</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H34" t="n">
         <v>66.09</v>
@@ -2044,28 +2044,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>4.08</v>
+        <v>2.93</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>-0.0599</v>
+        <v>-0.0135</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3467800</v>
+        <v>3865500</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
       <c r="H35" t="n">
-        <v>67.28</v>
+        <v>64.36</v>
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>3.647</v>
+        <v>2.683</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>2.468</v>
+        <v>2.522</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2089,28 +2089,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.865</v>
+        <v>4.05</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0668</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3351700</v>
+        <v>3740800</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
       <c r="H36" t="n">
-        <v>46.81</v>
+        <v>66.36</v>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.868</v>
+        <v>3.645</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.87</v>
+        <v>2.467</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2134,39 +2134,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.405</v>
+        <v>2.07</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>-0.0122</v>
+        <v>-0.0048</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3189600</v>
+        <v>3711600</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="H37" t="n">
-        <v>46.39</v>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.75</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.409</v>
+        <v>2.117</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.411</v>
+        <v>2.066</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         <v>0.0382</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2994100</v>
+        <v>3414400</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="H38" t="n">
         <v>62.34</v>
@@ -2224,39 +2224,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2885500</v>
+        <v>3311100</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="H39" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.39</v>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.383</v>
+        <v>0.409</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.325</v>
+        <v>0.411</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2269,39 +2269,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.225</v>
+        <v>1.55</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>-0.0217</v>
+        <v>-0.0064</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2855600</v>
+        <v>3252400</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.75</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>65.48999999999999</v>
-      </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.52</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.206</v>
+        <v>1.578</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.181</v>
+        <v>1.642</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2314,28 +2314,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>0</v>
+        <v>10.08</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2693500</v>
+        <v>3201000</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="H41" t="n">
-        <v>46.6</v>
+        <v>43.61</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>2.573</v>
+        <v>10.15</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.452</v>
+        <v>10.294</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2359,28 +2359,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.205</v>
+        <v>2.51</v>
       </c>
       <c r="E42" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2680900</v>
+        <v>3194000</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="H42" t="n">
-        <v>55.27</v>
+        <v>46.6</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.203</v>
+        <v>2.573</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.186</v>
+        <v>2.452</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2404,39 +2404,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0.0167</v>
+        <v>0.365</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2673800</v>
+        <v>3030100</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.14</v>
+        <v>0.48</v>
       </c>
       <c r="H43" t="n">
-        <v>53.62</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.25</v>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.303</v>
+        <v>0.367</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.291</v>
+        <v>0.367</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2449,39 +2449,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.011</v>
+        <v>1.71</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>-0.0116</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2637200</v>
+        <v>2930900</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.21</v>
+        <v>0.52</v>
       </c>
       <c r="H44" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.32</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>10.152</v>
+        <v>1.762</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>10.295</v>
+        <v>1.798</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2494,28 +2494,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YXPM</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.215</v>
+        <v>0.225</v>
       </c>
       <c r="E45" s="17" t="n">
-        <v>-0.0444</v>
+        <v>-0.0217</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2574500</v>
+        <v>2907300</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>4.98</v>
+        <v>0.77</v>
       </c>
       <c r="H45" t="n">
-        <v>49.65</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.216</v>
+        <v>0.206</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.214</v>
+        <v>0.181</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2539,39 +2539,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0.1048</v>
+        <v>1.3</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2564000</v>
+        <v>2895400</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.93</v>
+        <v>0.23</v>
       </c>
       <c r="H46" t="n">
-        <v>85.01000000000001</v>
-      </c>
-      <c r="I46" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.18</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.093</v>
+        <v>1.362</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.914</v>
+        <v>1.296</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2584,39 +2584,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>-0.0058</v>
+        <v>0.39</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2491700</v>
+        <v>2895200</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.45</v>
+        <v>0.13</v>
       </c>
       <c r="H47" t="n">
-        <v>43.37</v>
-      </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.3</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.763</v>
+        <v>0.383</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>1.798</v>
+        <v>0.325</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2629,28 +2629,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.735</v>
+        <v>0.205</v>
       </c>
       <c r="E48" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2302500</v>
+        <v>2794200</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="H48" t="n">
-        <v>52.16</v>
+        <v>55.27</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.736</v>
+        <v>0.203</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.186</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2674,39 +2674,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>-0.0296</v>
+        <v>1.37</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0.1048</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2260700</v>
+        <v>2764900</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.18</v>
+        <v>1.01</v>
       </c>
       <c r="H49" t="n">
-        <v>45.15</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.01000000000001</v>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>1.363</v>
+        <v>1.093</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>1.296</v>
+        <v>0.914</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2719,28 +2719,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>YXPM</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>-0.0444</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2044100</v>
+        <v>2574500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.13</v>
+        <v>4.98</v>
       </c>
       <c r="H50" t="n">
-        <v>72.42</v>
+        <v>49.65</v>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.492</v>
+        <v>0.216</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.411</v>
+        <v>0.214</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2764,28 +2764,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>1.78</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2029500</v>
+        <v>2485300</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H51" t="n">
-        <v>48.57</v>
+        <v>57.12</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>2.339</v>
+        <v>1.744</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2.251</v>
+        <v>1.55</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2809,39 +2809,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.365</v>
+        <v>0.735</v>
       </c>
       <c r="E52" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2016400</v>
+        <v>2386000</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.32</v>
+        <v>0.05</v>
       </c>
       <c r="H52" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.16</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.367</v>
+        <v>0.736</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.367</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2854,28 +2854,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>-0.0372</v>
+        <v>0.57</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1858200</v>
+        <v>2283700</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.39</v>
+        <v>0.15</v>
       </c>
       <c r="H53" t="n">
-        <v>57.59</v>
+        <v>72.42</v>
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
@@ -2883,10 +2883,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.89</v>
+        <v>0.492</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.853</v>
+        <v>0.411</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2899,28 +2899,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.8</v>
+        <v>1.13</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.0367</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1685600</v>
+        <v>2223400</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="H54" t="n">
-        <v>58.81</v>
+        <v>78.03</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.746</v>
+        <v>1.023</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.551</v>
+        <v>0.861</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2944,28 +2944,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>-0.0069</v>
+        <v>2.31</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1619900</v>
+        <v>2100100</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H55" t="n">
-        <v>64.29000000000001</v>
+        <v>48.57</v>
       </c>
       <c r="I55" s="15" t="inlineStr">
         <is>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>2.789</v>
+        <v>2.339</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>2.648</v>
+        <v>2.251</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2989,39 +2989,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.03</v>
+        <v>0.905</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>-0.019</v>
+        <v>-0.0372</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1605000</v>
+        <v>2093800</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="H56" t="n">
-        <v>44.39</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.59</v>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>1.074</v>
+        <v>0.89</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.025</v>
+        <v>0.853</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3034,28 +3034,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>0</v>
+        <v>3.05</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0.0201</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1543600</v>
+        <v>1995500</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.32</v>
+        <v>0.55</v>
       </c>
       <c r="H57" t="n">
-        <v>83.18000000000001</v>
+        <v>59.37</v>
       </c>
       <c r="I57" s="15" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.515</v>
+        <v>2.89</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.161</v>
+        <v>2.7</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3079,39 +3079,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>-0.0185</v>
+        <v>1.23</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0.025</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1538200</v>
+        <v>1972600</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.55</v>
+        <v>0.37</v>
       </c>
       <c r="H58" t="n">
-        <v>71.53</v>
-      </c>
-      <c r="I58" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.8</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.232</v>
+        <v>1.263</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.211</v>
+        <v>1.3</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3133,19 +3133,19 @@
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>-0.0253</v>
+        <v>-0.019</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1486000</v>
+        <v>1955800</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>2.34</v>
+        <v>3.08</v>
       </c>
       <c r="H59" t="n">
-        <v>44.38</v>
+        <v>46.13</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.58</v>
+        <v>1.581</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>1.507</v>
@@ -3169,39 +3169,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1.12</v>
+        <v>4.72</v>
       </c>
       <c r="E60" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1459400</v>
+        <v>1927900</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="H60" t="n">
-        <v>43.06</v>
-      </c>
-      <c r="I60" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.24</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>1.17</v>
+        <v>4.823</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1.148</v>
+        <v>4.945</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3214,28 +3214,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0.0275</v>
+        <v>2.9</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1441300</v>
+        <v>1877800</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H61" t="n">
-        <v>77.19</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>1.022</v>
+        <v>2.79</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.861</v>
+        <v>2.648</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3259,39 +3259,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>0</v>
+        <v>7.81</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1406500</v>
+        <v>1787400</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="H62" t="n">
-        <v>33.24</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.3</v>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>4.823</v>
+        <v>7.804</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>4.945</v>
+        <v>7.742</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3304,39 +3304,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.16</v>
+        <v>7.59</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0066</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1392000</v>
+        <v>1760500</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.38</v>
+        <v>0.16</v>
       </c>
       <c r="H63" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="I63" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.4</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.116</v>
+        <v>7.902</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1.021</v>
+        <v>8.233000000000001</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3349,39 +3349,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0.0013</v>
+        <v>1.03</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1375000</v>
+        <v>1748500</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="H64" t="n">
-        <v>50.34</v>
-      </c>
-      <c r="I64" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.39</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>7.802</v>
+        <v>1.074</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>7.741</v>
+        <v>1.025</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3394,28 +3394,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0.009300000000000001</v>
+        <v>2.74</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1326300</v>
+        <v>1597800</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="H65" t="n">
-        <v>61.78</v>
+        <v>80.14</v>
       </c>
       <c r="I65" s="15" t="inlineStr">
         <is>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.506</v>
+        <v>2.513</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.413</v>
+        <v>2.16</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3439,28 +3439,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.265</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1299400</v>
+        <v>1583600</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>84.59999999999999</v>
+        <v>71.53</v>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>3.718</v>
+        <v>0.232</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>3.285</v>
+        <v>0.211</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3484,28 +3484,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>0</v>
+        <v>1.16</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1283500</v>
+        <v>1572000</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.16</v>
+        <v>0.42</v>
       </c>
       <c r="H67" t="n">
-        <v>52.07</v>
+        <v>61.75</v>
       </c>
       <c r="I67" s="15" t="inlineStr">
         <is>
@@ -3513,10 +3513,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.116</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.665</v>
+        <v>1.021</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3529,28 +3529,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.79</v>
+        <v>1.13</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>0.0064</v>
+        <v>0.0089</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1266800</v>
+        <v>1531400</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H68" t="n">
-        <v>64.37</v>
+        <v>44.53</v>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.768</v>
+        <v>1.171</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.754</v>
+        <v>1.148</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3574,39 +3574,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0.0032</v>
+        <v>4.49</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1232500</v>
+        <v>1472900</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="H69" t="n">
-        <v>32.75</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.38</v>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>3.274</v>
+        <v>3.716</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>3.465</v>
+        <v>3.284</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3619,28 +3619,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.65</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>-0.0152</v>
+        <v>-0.0072</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1081700</v>
+        <v>1462400</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.36</v>
+        <v>0.19</v>
       </c>
       <c r="H70" t="n">
-        <v>61.67</v>
+        <v>51.06</v>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.604</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.61</v>
+        <v>0.665</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3673,19 +3673,19 @@
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>0</v>
+        <v>0.835</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1067400</v>
+        <v>1440200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="H71" t="n">
-        <v>64.40000000000001</v>
+        <v>61.35</v>
       </c>
       <c r="I71" s="15" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.73</v>
+        <v>0.729</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3709,39 +3709,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.08</v>
+        <v>3.16</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>0.0189</v>
+        <v>0.0032</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1065800</v>
+        <v>1395600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="H72" t="n">
-        <v>78.62</v>
-      </c>
-      <c r="I72" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.75</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.924</v>
+        <v>3.274</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.775</v>
+        <v>3.465</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3754,39 +3754,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>0</v>
+        <v>0.345</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1057800</v>
+        <v>1394200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="H73" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.26</v>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>1.26</v>
+        <v>0.34</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>1.299</v>
+        <v>0.334</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3799,39 +3799,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0263</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>-0.0401</v>
+        <v>0.545</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1055000</v>
+        <v>1329700</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>1.97</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>42.94</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.78</v>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.506</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.711</v>
+        <v>0.413</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3844,28 +3844,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>3</v>
+        <v>0.295</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0172</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1022300</v>
+        <v>1301600</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="H75" t="n">
-        <v>57.29</v>
+        <v>44.81</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.885</v>
+        <v>0.297</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.699</v>
+        <v>0.311</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3889,28 +3889,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>-0.0064</v>
+        <v>0.635</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1017400</v>
+        <v>1273800</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="H76" t="n">
-        <v>73.98999999999999</v>
+        <v>55.91</v>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.621</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.625</v>
+        <v>0.585</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3934,28 +3934,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="E77" s="17" t="n">
-        <v>-0.0063</v>
+        <v>0.79</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1010000</v>
+        <v>1266800</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H77" t="n">
-        <v>90.31</v>
+        <v>64.37</v>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.366</v>
+        <v>0.768</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.837</v>
+        <v>0.754</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3979,28 +3979,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E78" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.78</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1002900</v>
+        <v>1252300</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H78" t="n">
-        <v>93.38</v>
+        <v>75.67</v>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.952</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.758</v>
+        <v>0.625</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4024,28 +4024,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="E79" s="17" t="n">
-        <v>-0.0175</v>
+        <v>-0.0152</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1001500</v>
+        <v>1193300</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="H79" t="n">
-        <v>43.59</v>
+        <v>61.67</v>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.604</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.593</v>
+        <v>0.61</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4069,28 +4069,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.8</v>
+        <v>3.13</v>
       </c>
       <c r="E80" s="17" t="n">
-        <v>-0.0123</v>
+        <v>-0.0157</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>993800</v>
+        <v>1164000</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.09</v>
+        <v>0.4</v>
       </c>
       <c r="H80" t="n">
-        <v>63.64</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.727</v>
+        <v>2.363</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>1.836</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4114,39 +4114,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0263</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>0.004</v>
+        <v>0.675</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>-0.033</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>947100</v>
+        <v>1115300</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.06</v>
+        <v>2.08</v>
       </c>
       <c r="H81" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="I81" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.17</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>2.452</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>2.296</v>
+        <v>0.711</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4159,39 +4159,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>0.0159</v>
+        <v>0.865</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>935600</v>
+        <v>1097600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="H82" t="n">
-        <v>57.06</v>
-      </c>
-      <c r="I82" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.68</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.622</v>
+        <v>0.861</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.586</v>
+        <v>0.856</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4204,39 +4204,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.795</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>928700</v>
+        <v>1071200</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H83" t="n">
-        <v>31.71</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.67</v>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>7.904</v>
+        <v>0.727</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>8.233000000000001</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4249,39 +4249,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.09</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0.0283</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>918700</v>
+        <v>1069600</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="H84" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.19</v>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.634</v>
+        <v>0.925</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.596</v>
+        <v>0.775</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0.0123</v>
+        <v>5.78</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>840000</v>
+        <v>1057300</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>35.72</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.6</v>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.714</v>
+        <v>5.704</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.831</v>
+        <v>5.191</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4339,39 +4339,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>834400</v>
+        <v>1020900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="H86" t="n">
-        <v>50.34</v>
-      </c>
-      <c r="I86" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.45</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.569</v>
+        <v>0.35</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.575</v>
+        <v>0.35</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4384,28 +4384,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0.0068</v>
+        <v>1.28</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>831000</v>
+        <v>1014300</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H87" t="n">
-        <v>64.18000000000001</v>
+        <v>93.38</v>
       </c>
       <c r="I87" s="15" t="inlineStr">
         <is>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.952</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.62</v>
+        <v>0.758</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4429,28 +4429,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>819700</v>
+        <v>1008300</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="H88" t="n">
-        <v>76.75</v>
+        <v>43.59</v>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.994</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.821</v>
+        <v>0.593</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4474,39 +4474,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>4.27</v>
+        <v>0.25</v>
       </c>
       <c r="E89" s="17" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.0196</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>793300</v>
+        <v>1005600</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H89" t="n">
-        <v>40.83</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.16</v>
+      </c>
+      <c r="I89" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>4.528</v>
+        <v>0.268</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>4.522</v>
+        <v>0.311</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4519,39 +4519,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>782100</v>
+        <v>1005400</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H90" t="n">
-        <v>34.14</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.27</v>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.555</v>
+        <v>0.278</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.586</v>
+        <v>0.271</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4564,28 +4564,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>12.98</v>
+        <v>2.51</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.004</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>751500</v>
+        <v>1001300</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H91" t="n">
-        <v>39.49</v>
+        <v>62.3</v>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>13.146</v>
+        <v>2.452</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>13.739</v>
+        <v>2.296</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4609,39 +4609,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>-0.0069</v>
+        <v>1.26</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>724400</v>
+        <v>983600</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.05</v>
+        <v>0.34</v>
       </c>
       <c r="H92" t="n">
-        <v>57.12</v>
-      </c>
-      <c r="I92" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.77</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>5.703</v>
+        <v>1.374</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>5.191</v>
+        <v>1.317</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4654,39 +4654,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.62</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E93" s="17" t="n">
-        <v>-0.0159</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>710000</v>
+        <v>963200</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.7</v>
+        <v>0.32</v>
       </c>
       <c r="H93" t="n">
-        <v>36.72</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.95</v>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.63</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.636</v>
+        <v>0.575</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4699,39 +4699,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0123</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>699900</v>
+        <v>939800</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="H94" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="I94" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.72</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.323</v>
+        <v>1.714</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.43</v>
+        <v>1.831</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4744,28 +4744,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>0.0107</v>
+        <v>0.635</v>
+      </c>
+      <c r="E95" s="17" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>697300</v>
+        <v>918800</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="H95" t="n">
-        <v>42.08</v>
+        <v>56.82</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>7.654</v>
+        <v>0.634</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>7.828</v>
+        <v>0.596</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4789,39 +4789,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>-0.0109</v>
+        <v>13</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0.022</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>682500</v>
+        <v>905400</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.3</v>
+        <v>0.11</v>
       </c>
       <c r="H96" t="n">
-        <v>37.66</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.29</v>
+      </c>
+      <c r="I96" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.929</v>
+        <v>13.148</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.947</v>
+        <v>13.739</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4834,39 +4834,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>-0.009300000000000001</v>
+        <v>1.09</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>675600</v>
+        <v>901000</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="H97" t="n">
-        <v>39.18</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.75</v>
+      </c>
+      <c r="I97" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>5.715</v>
+        <v>0.994</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>5.754</v>
+        <v>0.821</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4879,28 +4879,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E98" s="16" t="n">
-        <v>0</v>
+        <v>4.28</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>-0.0023</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>637800</v>
+        <v>880900</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H98" t="n">
-        <v>46.13</v>
+        <v>41.1</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.772</v>
+        <v>4.529</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.772</v>
+        <v>4.522</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4924,28 +4924,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E99" s="16" t="n">
-        <v>0</v>
+        <v>0.745</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>609500</v>
+        <v>876700</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="H99" t="n">
-        <v>42.53</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="I99" s="15" t="inlineStr">
         <is>
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.473</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.52</v>
+        <v>0.62</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4969,39 +4969,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>-0.0137</v>
+        <v>0.92</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>588200</v>
+        <v>848600</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="H100" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.85</v>
+      </c>
+      <c r="I100" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>2.217</v>
+        <v>0.926</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>2.109</v>
+        <v>0.969</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5014,39 +5014,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>0</v>
+        <v>5.32</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>585500</v>
+        <v>840100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="H101" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="I101" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.77</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.634</v>
+        <v>5.714</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.629</v>
+        <v>5.754</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5059,28 +5059,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.765</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>568000</v>
+        <v>827800</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="H102" t="n">
-        <v>36.42</v>
+        <v>46.13</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.375</v>
+        <v>0.772</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.317</v>
+        <v>0.772</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5104,28 +5104,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>0</v>
+        <v>0.53</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>508300</v>
+        <v>800200</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H103" t="n">
-        <v>33.4</v>
+        <v>34.14</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.629</v>
+        <v>0.555</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.656</v>
+        <v>0.586</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5149,28 +5149,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>0.03</v>
+        <v>0.0156</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>506000</v>
+        <v>799400</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.89</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H104" t="n">
-        <v>70.42</v>
+        <v>40.64</v>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
@@ -5178,16 +5178,781 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.988</v>
+        <v>1.323</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.976</v>
+        <v>1.43</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>782200</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H105" t="n">
+        <v>37.66</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>771300</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H106" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>4.664</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>4.959</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>-0.0357</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>730100</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H107" t="n">
+        <v>53.57</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>711900</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H108" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>7.654</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>7.828</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>710000</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H109" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>655000</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H110" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>641700</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H111" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="I111" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>623300</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H112" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>2.218</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>621900</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H113" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="I113" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>1.521</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>7174</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>614600</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H114" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="I114" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>585500</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H115" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="I115" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>568700</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H116" t="n">
+        <v>42.94</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>561100</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H117" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>536300</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H118" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>3.693</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>530100</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H119" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>506000</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H120" t="n">
+        <v>70.42</v>
+      </c>
+      <c r="I120" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>7095</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PIE</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>505300</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H121" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="I121" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>1.716</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>1.627</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M104"/>
+  <autoFilter ref="A1:M121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
+++ b/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
   </fonts>
   <fills count="4">
@@ -89,16 +89,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.515</v>
+        <v>0.52</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.2262</v>
+        <v>0.2381</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>17872500</v>
+        <v>22526400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>12.33</v>
+        <v>15.54</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>76.87</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.417</v>
+        <v>0.418</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.412</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
+          <t>🎯 EMA</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>EMA与SAR、Supertrend均呈多头排列，但RSI达76.87已入超买区，现价高于50日均线约25%，信号偏热。</t>
+          <t>现价0.52高于50日均线0.412，EMA信号偏多；但RSI达77.43，已处超买区，短线动能强但回调风险上升。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5.1</v>
+        <v>5.13</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0241</v>
+        <v>0.0301</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>25633800</v>
+        <v>27885300</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>73.54000000000001</v>
+        <v>74.47</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>4.799</v>
+        <v>4.802</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>4.545</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
+          <t>🎯 EMA</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>RSI达73.54，已进入超买区；现价5.1高于50日均线4.545约12%，短期均线多头排列，信号偏强但需留意超买风险。</t>
+          <t>现价RM5.13高于50日均线RM4.545约12.9%，RSI达74.47，处于超买区间，EMA信号可靠性偏弱。</t>
         </is>
       </c>
     </row>
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.0303</v>
+        <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>110629500</v>
+        <v>140401500</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H4" t="n">
-        <v>22.06</v>
+        <v>20.46</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.256</v>
+        <v>0.255</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.47</v>
@@ -719,19 +719,19 @@
       <c r="D5" s="9" t="n">
         <v>0.255</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="15" t="n">
         <v>0.0851</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>86171200</v>
+        <v>89934200</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>4.43</v>
+        <v>4.62</v>
       </c>
       <c r="H5" t="n">
         <v>63.19</v>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -764,14 +764,14 @@
       <c r="D6" s="9" t="n">
         <v>0.17</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="15" t="n">
         <v>0.0625</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>28129300</v>
+        <v>28927400</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="H6" t="n">
         <v>39.42</v>
@@ -798,39 +798,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E7" s="16" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>14938600</v>
+        <v>16728700</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.3</v>
+        <v>0.67</v>
       </c>
       <c r="H7" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>72.05</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.154</v>
+        <v>0.555</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.12</v>
+        <v>0.495</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -843,39 +843,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.19</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>13563700</v>
+        <v>15330000</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.54</v>
+        <v>0.31</v>
       </c>
       <c r="H8" t="n">
-        <v>69.39</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.555</v>
+        <v>0.154</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.495</v>
+        <v>0.12</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -888,39 +888,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0051</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CUSCAPI</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0.1</v>
+        <v>2.51</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.004</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>11460900</v>
+        <v>12926300</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.45</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>42.26</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.3</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.058</v>
+        <v>2.452</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.076</v>
+        <v>2.296</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -933,39 +933,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0152</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DGB</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0</v>
+        <v>0.055</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.1</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>9843300</v>
+        <v>12010900</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>141.72</v>
+        <v>0.47</v>
       </c>
       <c r="H10" t="n">
-        <v>60.06</v>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.26</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.035</v>
+        <v>0.058</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.035</v>
+        <v>0.076</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -978,39 +978,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>0152</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>DGB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E11" s="16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9413800</v>
+        <v>11110500</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.95</v>
+        <v>159.97</v>
       </c>
       <c r="H11" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.06</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.052</v>
+        <v>0.035</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.044</v>
+        <v>0.035</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1023,28 +1023,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>-0.06309999999999999</v>
+        <v>0.75</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>9011800</v>
+        <v>9945400</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.42</v>
+        <v>0.22</v>
       </c>
       <c r="H12" t="n">
-        <v>48.52</v>
+        <v>55.23</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.524</v>
+        <v>0.737</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.532</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1068,39 +1068,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.355</v>
+        <v>0.05</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.07580000000000001</v>
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7836700</v>
+        <v>9413800</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.03</v>
+        <v>0.95</v>
       </c>
       <c r="H13" t="n">
-        <v>62.52</v>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.92</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.332</v>
+        <v>0.052</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.314</v>
+        <v>0.044</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1113,39 +1113,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0.0417</v>
+        <v>0.515</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.0721</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6939900</v>
+        <v>9389000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.24</v>
+        <v>1.48</v>
       </c>
       <c r="H14" t="n">
-        <v>36.22</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.92</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.271</v>
+        <v>0.524</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.322</v>
+        <v>0.532</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1158,39 +1158,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>-0.0319</v>
+        <v>0.35</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.06059999999999999</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>6869600</v>
+        <v>8984500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.7</v>
+        <v>1.19</v>
       </c>
       <c r="H15" t="n">
-        <v>53.57</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.92</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.45</v>
+        <v>0.332</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.413</v>
+        <v>0.314</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1203,39 +1203,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.215</v>
+        <v>0.155</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.0488</v>
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>6810400</v>
+        <v>8200100</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="H16" t="n">
-        <v>35.23</v>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.233</v>
+        <v>0.156</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.247</v>
+        <v>0.159</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1248,28 +1248,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.11</v>
+        <v>0.46</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>-0.0435</v>
+        <v>-0.0213</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6192100</v>
+        <v>7892600</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H17" t="n">
-        <v>37.36</v>
+        <v>55.03</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.121</v>
+        <v>0.451</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.124</v>
+        <v>0.413</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1293,28 +1293,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.215</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.0488</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>6047400</v>
+        <v>7375900</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.82</v>
+        <v>0.3</v>
       </c>
       <c r="H18" t="n">
-        <v>41.23</v>
+        <v>35.23</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1.887</v>
+        <v>0.233</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1.959</v>
+        <v>0.247</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1338,33 +1338,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>-0.0192</v>
+        <v>0.245</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5917500</v>
+        <v>7138700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
+        <v>0.25</v>
+      </c>
+      <c r="H19" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.322</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
     </row>
@@ -1376,28 +1383,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0.0196</v>
+        <v>0.305</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>5436000</v>
+        <v>7009800</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="H20" t="n">
-        <v>27.66</v>
+        <v>53.62</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1405,10 +1412,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.612</v>
+        <v>0.303</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.827</v>
+        <v>0.291</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1421,39 +1428,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0.0106</v>
+        <v>0.52</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>5363700</v>
+        <v>6900100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="H21" t="n">
-        <v>52.83</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.66</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.469</v>
+        <v>0.612</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.472</v>
+        <v>0.827</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1466,39 +1473,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>0</v>
+        <v>0.11</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5198200</v>
+        <v>6855100</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.11</v>
+        <v>0.82</v>
       </c>
       <c r="H22" t="n">
-        <v>78.19</v>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.36</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.332</v>
+        <v>0.121</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.197</v>
+        <v>0.124</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1526,15 +1533,15 @@
         <v>-0.006500000000000001</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5115800</v>
+        <v>6627000</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="H23" t="n">
         <v>48.13</v>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -1556,39 +1563,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.4</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>5096500</v>
+        <v>6366900</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1.18</v>
+        <v>0.57</v>
       </c>
       <c r="H24" t="n">
-        <v>48.74</v>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.46</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.802</v>
+        <v>0.408</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.411</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1601,40 +1608,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4977400</v>
+        <v>6364200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="H25" t="n">
-        <v>75.29000000000001</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="K25" s="9" t="n">
-        <v>0.346</v>
-      </c>
+        <v>0.43</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
     </row>
@@ -1646,39 +1646,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>-0.0127</v>
+        <v>0.21</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4865500</v>
+        <v>6312400</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="H26" t="n">
-        <v>64.22</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.61</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.377</v>
+        <v>0.203</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.372</v>
+        <v>0.186</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1691,39 +1691,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.605</v>
+        <v>0.865</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4792700</v>
+        <v>6199000</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="H27" t="n">
-        <v>48.44</v>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
+        <v>46.81</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.607</v>
+        <v>0.868</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.606</v>
+        <v>0.87</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1736,28 +1736,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>0</v>
+        <v>1.84</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.011</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4692400</v>
+        <v>6146900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.33</v>
+        <v>0.83</v>
       </c>
       <c r="H28" t="n">
-        <v>50.19</v>
+        <v>42.58</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.887</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>1.959</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1781,39 +1781,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.155</v>
+        <v>0.035</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.0333</v>
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4627000</v>
+        <v>6100700</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.11</v>
+        <v>0.73</v>
       </c>
       <c r="H29" t="n">
-        <v>50.05</v>
-      </c>
-      <c r="I29" s="15" t="inlineStr">
+        <v>53.89</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.157</v>
+        <v>0.033</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.148</v>
+        <v>0.032</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1826,33 +1826,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.12</v>
+        <v>0.805</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>-0.04</v>
+        <v>-0.0062</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4554800</v>
+        <v>6007800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.11</v>
+        <v>0.42</v>
+      </c>
+      <c r="H30" t="n">
+        <v>47.5</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
+      <c r="J30" s="9" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.8070000000000001</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
     </row>
@@ -1864,39 +1871,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.865</v>
+        <v>0.39</v>
       </c>
       <c r="E31" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0127</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4313200</v>
+        <v>5846400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.23</v>
+        <v>0.54</v>
       </c>
       <c r="H31" t="n">
-        <v>46.81</v>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
+        <v>64.22</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.868</v>
+        <v>0.377</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.87</v>
+        <v>0.372</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1909,39 +1916,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0.0167</v>
+        <v>0.475</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>4179800</v>
+        <v>5815900</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="H32" t="n">
-        <v>53.62</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.83</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.303</v>
+        <v>0.469</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.291</v>
+        <v>0.472</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1954,40 +1961,33 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.575</v>
+        <v>0.12</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>-0.0086</v>
+        <v>-0.04</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4088000</v>
+        <v>5568500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H33" t="n">
-        <v>63.01</v>
-      </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>0.485</v>
-      </c>
+        <v>0.13</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
     </row>
@@ -1999,39 +1999,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.365</v>
+        <v>0.79</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.0282</v>
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4019300</v>
+        <v>5406400</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="H34" t="n">
-        <v>66.09</v>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
+        <v>45.55</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.341</v>
+        <v>0.801</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.321</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2044,39 +2044,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>-0.0135</v>
+        <v>0.39</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3865500</v>
+        <v>5358200</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.44</v>
+        <v>0.11</v>
       </c>
       <c r="H35" t="n">
-        <v>64.36</v>
-      </c>
-      <c r="I35" s="15" t="inlineStr">
+        <v>78.19</v>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>2.683</v>
+        <v>0.332</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>2.522</v>
+        <v>0.197</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2089,39 +2089,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>-0.0668</v>
+        <v>0.44</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3740800</v>
+        <v>5341700</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.31</v>
+        <v>2.67</v>
       </c>
       <c r="H36" t="n">
-        <v>66.36</v>
-      </c>
-      <c r="I36" s="15" t="inlineStr">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>3.645</v>
+        <v>0.381</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>2.467</v>
+        <v>0.346</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2134,39 +2134,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0118</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>TRIVE</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>-0.0048</v>
+        <v>0.02</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.3333</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3711600</v>
+        <v>5248200</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.22</v>
+        <v>53.65</v>
       </c>
       <c r="H37" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.93</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.117</v>
+        <v>0.016</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.066</v>
+        <v>0.017</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2179,39 +2179,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0.0382</v>
+        <v>2.5</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>-0.004</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3414400</v>
+        <v>5240200</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.36</v>
+        <v>0.26</v>
       </c>
       <c r="H38" t="n">
-        <v>62.34</v>
-      </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.9</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.638</v>
+        <v>2.572</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.581</v>
+        <v>2.452</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2224,39 +2224,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.405</v>
+        <v>2.07</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>-0.0122</v>
+        <v>-0.0048</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3311100</v>
+        <v>5226300</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H39" t="n">
-        <v>46.39</v>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.75</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.409</v>
+        <v>2.117</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.411</v>
+        <v>2.066</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2269,28 +2269,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>TFP</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>-0.0064</v>
+        <v>0.055</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3252400</v>
+        <v>5209300</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="H40" t="n">
-        <v>40.52</v>
+        <v>38.54</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>1.578</v>
+        <v>0.062</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1.642</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2314,28 +2314,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.4</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3201000</v>
+        <v>5088700</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="H41" t="n">
-        <v>43.61</v>
+        <v>57.61</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>10.15</v>
+        <v>0.384</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>10.294</v>
+        <v>0.325</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2359,39 +2359,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3194000</v>
+        <v>5000100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.16</v>
+        <v>0.48</v>
       </c>
       <c r="H42" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.01</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.573</v>
+        <v>0.607</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.452</v>
+        <v>0.606</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2404,39 +2404,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>0</v>
+        <v>3.94</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>-0.0922</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3030100</v>
+        <v>4812600</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="H43" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="I43" s="15" t="inlineStr">
+        <v>63.21</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.367</v>
+        <v>3.634</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.367</v>
+        <v>2.465</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2449,39 +2449,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.71</v>
+        <v>0.575</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>-0.0116</v>
+        <v>-0.0086</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2930900</v>
+        <v>4649000</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.52</v>
+        <v>0.31</v>
       </c>
       <c r="H44" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="I44" s="15" t="inlineStr">
+        <v>63.01</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>1.762</v>
+        <v>0.533</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1.798</v>
+        <v>0.485</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2494,39 +2494,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>-0.0217</v>
+        <v>0.155</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2907300</v>
+        <v>4640800</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.77</v>
+        <v>0.11</v>
       </c>
       <c r="H45" t="n">
-        <v>65.48999999999999</v>
-      </c>
-      <c r="I45" s="15" t="inlineStr">
+        <v>50.05</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.206</v>
+        <v>0.157</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.181</v>
+        <v>0.148</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2539,39 +2539,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.365</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0.0282</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2895400</v>
+        <v>4437600</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.23</v>
+        <v>0.62</v>
       </c>
       <c r="H46" t="n">
-        <v>44.18</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.09</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.362</v>
+        <v>0.341</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1.296</v>
+        <v>0.321</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2584,39 +2584,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>0</v>
+        <v>2.92</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2895200</v>
+        <v>4380600</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.76</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.383</v>
+        <v>2.682</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.325</v>
+        <v>2.522</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2629,39 +2629,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.0382</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2794200</v>
+        <v>3978400</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.12</v>
+        <v>0.41</v>
       </c>
       <c r="H48" t="n">
-        <v>55.27</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.34</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.203</v>
+        <v>0.638</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.186</v>
+        <v>0.581</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2674,39 +2674,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0.1048</v>
+        <v>10.06</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2764900</v>
+        <v>3804200</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1.01</v>
+        <v>0.3</v>
       </c>
       <c r="H49" t="n">
-        <v>85.01000000000001</v>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.25</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>1.093</v>
+        <v>10.149</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.914</v>
+        <v>10.294</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2719,39 +2719,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YXPM</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>-0.0444</v>
+        <v>1.56</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2574500</v>
+        <v>3374800</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>4.98</v>
+        <v>0.98</v>
       </c>
       <c r="H50" t="n">
-        <v>49.65</v>
-      </c>
-      <c r="I50" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.35</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.216</v>
+        <v>1.579</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.214</v>
+        <v>1.642</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2764,39 +2764,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="E51" s="17" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2485300</v>
+        <v>3308600</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="H51" t="n">
-        <v>57.12</v>
-      </c>
-      <c r="I51" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.18</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.744</v>
+        <v>1.362</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.55</v>
+        <v>1.296</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2809,39 +2809,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E52" s="16" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2386000</v>
+        <v>3250100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.05</v>
+        <v>0.51</v>
       </c>
       <c r="H52" t="n">
-        <v>52.16</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.25</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.736</v>
+        <v>0.367</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.367</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2854,39 +2854,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>0</v>
+        <v>1.34</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.0806</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2283700</v>
+        <v>3178300</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.15</v>
+        <v>1.16</v>
       </c>
       <c r="H53" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
+        <v>84.04000000000001</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.492</v>
+        <v>1.09</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.411</v>
+        <v>0.913</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2899,39 +2899,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.0367</v>
+        <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2223400</v>
+        <v>3102900</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="H54" t="n">
-        <v>78.03</v>
-      </c>
-      <c r="I54" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.24</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.023</v>
+        <v>1.075</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.861</v>
+        <v>1.025</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2944,39 +2944,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>2.31</v>
+        <v>0.295</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2100100</v>
+        <v>3081200</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="H55" t="n">
-        <v>48.57</v>
-      </c>
-      <c r="I55" s="15" t="inlineStr">
+        <v>66.27</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>2.339</v>
+        <v>0.278</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>2.251</v>
+        <v>0.271</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2989,39 +2989,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E56" s="17" t="n">
-        <v>-0.0372</v>
+        <v>7.8</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0.0026</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2093800</v>
+        <v>3079600</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.44</v>
+        <v>0.24</v>
       </c>
       <c r="H56" t="n">
-        <v>57.59</v>
-      </c>
-      <c r="I56" s="15" t="inlineStr">
+        <v>50.83</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.89</v>
+        <v>7.803</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.853</v>
+        <v>7.741</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3034,39 +3034,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0.0201</v>
+        <v>1.7</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>-0.0173</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1995500</v>
+        <v>3006000</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="H57" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="I57" s="15" t="inlineStr">
+        <v>41.33</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.89</v>
+        <v>1.761</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.7</v>
+        <v>1.797</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3079,39 +3079,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0.025</v>
+        <v>0.225</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1972600</v>
+        <v>2908400</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.37</v>
+        <v>0.77</v>
       </c>
       <c r="H58" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.48999999999999</v>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>1.263</v>
+        <v>0.206</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1.3</v>
+        <v>0.181</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3124,28 +3124,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>-0.019</v>
+        <v>1.22</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1955800</v>
+        <v>2709100</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>3.08</v>
+        <v>0.5</v>
       </c>
       <c r="H59" t="n">
-        <v>46.13</v>
+        <v>38.27</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.581</v>
+        <v>1.262</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.507</v>
+        <v>1.3</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3169,39 +3169,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>0</v>
+        <v>1.77</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1927900</v>
+        <v>2676500</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>0.11</v>
       </c>
       <c r="H60" t="n">
-        <v>33.24</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.17</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>4.823</v>
+        <v>1.743</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>4.945</v>
+        <v>1.55</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3214,39 +3214,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>0</v>
+        <v>0.895</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>-0.0479</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1877800</v>
+        <v>2629800</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.13</v>
+        <v>0.55</v>
       </c>
       <c r="H61" t="n">
-        <v>67.18000000000001</v>
-      </c>
-      <c r="I61" s="15" t="inlineStr">
+        <v>54.24</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>2.79</v>
+        <v>0.89</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>2.648</v>
+        <v>0.852</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3259,39 +3259,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0.0039</v>
+        <v>2.31</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1787400</v>
+        <v>2613000</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H62" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="I62" s="15" t="inlineStr">
+        <v>48.57</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>7.804</v>
+        <v>2.339</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>7.742</v>
+        <v>2.251</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3304,39 +3304,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>YXPM</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>7.59</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>0.0066</v>
+        <v>0.215</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>-0.0444</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1760500</v>
+        <v>2574500</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.16</v>
+        <v>4.98</v>
       </c>
       <c r="H63" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.65</v>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>7.902</v>
+        <v>0.216</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>8.233000000000001</v>
+        <v>0.214</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3349,39 +3349,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>-0.019</v>
+        <v>1.11</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0.0183</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1748500</v>
+        <v>2570800</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H64" t="n">
-        <v>44.39</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.28</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.074</v>
+        <v>1.021</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1.025</v>
+        <v>0.861</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3394,39 +3394,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>-0.0072</v>
+        <v>4.72</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1597800</v>
+        <v>2419300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.33</v>
+        <v>0.13</v>
       </c>
       <c r="H65" t="n">
-        <v>80.14</v>
-      </c>
-      <c r="I65" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.24</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.513</v>
+        <v>4.823</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.16</v>
+        <v>4.945</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3439,39 +3439,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>-0.0185</v>
+        <v>0.57</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1583600</v>
+        <v>2308800</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="H66" t="n">
-        <v>71.53</v>
-      </c>
-      <c r="I66" s="15" t="inlineStr">
+        <v>72.42</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.232</v>
+        <v>0.492</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.211</v>
+        <v>0.411</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3484,39 +3484,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>3.03</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>0.0134</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1572000</v>
+        <v>2291300</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.42</v>
+        <v>0.64</v>
       </c>
       <c r="H67" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="I67" s="15" t="inlineStr">
+        <v>58.56</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>1.116</v>
+        <v>2.888</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1.021</v>
+        <v>2.7</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3529,39 +3529,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0.0089</v>
+        <v>1.66</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1531400</v>
+        <v>2218800</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="H68" t="n">
-        <v>44.53</v>
-      </c>
-      <c r="I68" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.93</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>1.171</v>
+        <v>1.716</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1.148</v>
+        <v>1.832</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3574,39 +3574,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="E69" s="16" t="n">
-        <v>0</v>
+        <v>7.57</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.004</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1472900</v>
+        <v>2206300</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="H69" t="n">
-        <v>84.38</v>
-      </c>
-      <c r="I69" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.05</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>3.716</v>
+        <v>7.9</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>3.284</v>
+        <v>8.231999999999999</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3619,39 +3619,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>-0.0072</v>
+        <v>2.77</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1462400</v>
+        <v>2098900</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.19</v>
+        <v>0.44</v>
       </c>
       <c r="H70" t="n">
-        <v>51.06</v>
-      </c>
-      <c r="I70" s="15" t="inlineStr">
+        <v>83.48999999999999</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>2.516</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.665</v>
+        <v>2.161</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3664,39 +3664,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>-0.0118</v>
+        <v>4.5</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>0.0022</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1440200</v>
+        <v>2079900</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.47</v>
+        <v>0.34</v>
       </c>
       <c r="H71" t="n">
-        <v>61.35</v>
-      </c>
-      <c r="I71" s="15" t="inlineStr">
+        <v>84.48999999999999</v>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>3.717</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.729</v>
+        <v>3.284</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3709,28 +3709,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0.0032</v>
+        <v>1.55</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1395600</v>
+        <v>2038800</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.44</v>
+        <v>3.21</v>
       </c>
       <c r="H72" t="n">
-        <v>32.75</v>
+        <v>46.13</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>3.274</v>
+        <v>1.581</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>3.465</v>
+        <v>1.507</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3754,39 +3754,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.345</v>
+        <v>3.09</v>
       </c>
       <c r="E73" s="17" t="n">
-        <v>-0.0143</v>
+        <v>-0.0283</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1394200</v>
+        <v>1977500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.29</v>
+        <v>0.67</v>
       </c>
       <c r="H73" t="n">
-        <v>55.26</v>
-      </c>
-      <c r="I73" s="15" t="inlineStr">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.34</v>
+        <v>2.359</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.334</v>
+        <v>1.835</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3799,39 +3799,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.545</v>
+        <v>3.15</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>0.009300000000000001</v>
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1329700</v>
+        <v>1975500</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="H74" t="n">
-        <v>61.78</v>
-      </c>
-      <c r="I74" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.3</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.506</v>
+        <v>3.273</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.413</v>
+        <v>3.465</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3844,39 +3844,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>0.0172</v>
+        <v>2.88</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1301600</v>
+        <v>1917900</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="H75" t="n">
-        <v>44.81</v>
-      </c>
-      <c r="I75" s="15" t="inlineStr">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.297</v>
+        <v>2.789</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.311</v>
+        <v>2.648</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3889,39 +3889,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.79</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1273800</v>
+        <v>1847700</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="H76" t="n">
-        <v>55.91</v>
-      </c>
-      <c r="I76" s="15" t="inlineStr">
+        <v>64.37</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.621</v>
+        <v>0.768</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.585</v>
+        <v>0.754</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3934,39 +3934,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0.0064</v>
+        <v>0.64</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1266800</v>
+        <v>1833100</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="H77" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="I77" s="15" t="inlineStr">
+        <v>57.06</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.768</v>
+        <v>0.622</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.754</v>
+        <v>0.586</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3979,39 +3979,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E78" s="16" t="n">
-        <v>0</v>
+        <v>1.07</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1252300</v>
+        <v>1801500</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H78" t="n">
-        <v>75.67</v>
-      </c>
-      <c r="I78" s="15" t="inlineStr">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.923</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.625</v>
+        <v>0.775</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4024,39 +4024,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.65</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E79" s="17" t="n">
-        <v>-0.0152</v>
+        <v>-0.0072</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1193300</v>
+        <v>1741900</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="H79" t="n">
-        <v>61.67</v>
-      </c>
-      <c r="I79" s="15" t="inlineStr">
+        <v>51.06</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.604</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.61</v>
+        <v>0.665</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4069,39 +4069,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>-0.0157</v>
+        <v>1.16</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1164000</v>
+        <v>1740900</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="H80" t="n">
-        <v>88.18000000000001</v>
-      </c>
-      <c r="I80" s="15" t="inlineStr">
+        <v>61.75</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>2.363</v>
+        <v>1.116</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1.836</v>
+        <v>1.021</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4114,39 +4114,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0263</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E81" s="17" t="n">
-        <v>-0.033</v>
+        <v>1.13</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1115300</v>
+        <v>1732700</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>2.08</v>
+        <v>0.25</v>
       </c>
       <c r="H81" t="n">
-        <v>44.17</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.53</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>1.171</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.711</v>
+        <v>1.148</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4159,39 +4159,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.865</v>
+        <v>0.265</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0185</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1097600</v>
+        <v>1707300</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.35</v>
+        <v>0.61</v>
       </c>
       <c r="H82" t="n">
-        <v>56.68</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.53</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.861</v>
+        <v>0.232</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.856</v>
+        <v>0.211</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4204,39 +4204,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.795</v>
+        <v>0.865</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>-0.0185</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1071200</v>
+        <v>1638600</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.1</v>
+        <v>0.52</v>
       </c>
       <c r="H83" t="n">
-        <v>62.67</v>
-      </c>
-      <c r="I83" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.68</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.727</v>
+        <v>0.861</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.856</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4249,39 +4249,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>0.0283</v>
+        <v>13.02</v>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>0.0236</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1069600</v>
+        <v>1636900</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="H84" t="n">
-        <v>79.19</v>
-      </c>
-      <c r="I84" s="15" t="inlineStr">
+        <v>41.08</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.925</v>
+        <v>13.15</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.775</v>
+        <v>13.74</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>5.78</v>
+        <v>0.835</v>
       </c>
       <c r="E85" s="17" t="n">
-        <v>-0.0052</v>
+        <v>-0.0118</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1057300</v>
+        <v>1588900</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="H85" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="I85" s="15" t="inlineStr">
+        <v>61.35</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>5.704</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>5.191</v>
+        <v>0.729</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4339,28 +4339,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.34</v>
+        <v>0.905</v>
       </c>
       <c r="E86" s="17" t="n">
-        <v>-0.0145</v>
+        <v>-0.0163</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1020900</v>
+        <v>1516900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.15</v>
+        <v>0.66</v>
       </c>
       <c r="H86" t="n">
-        <v>38.45</v>
+        <v>35.81</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.35</v>
+        <v>0.928</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.35</v>
+        <v>0.947</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4384,39 +4384,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E87" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1014300</v>
+        <v>1498900</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H87" t="n">
-        <v>93.38</v>
-      </c>
-      <c r="I87" s="15" t="inlineStr">
+        <v>44.81</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.952</v>
+        <v>0.297</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.758</v>
+        <v>0.311</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4429,39 +4429,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>-0.0175</v>
+        <v>-0.0286</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1008300</v>
+        <v>1433100</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="H88" t="n">
-        <v>43.59</v>
-      </c>
-      <c r="I88" s="15" t="inlineStr">
+        <v>51.39</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.339</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.593</v>
+        <v>0.333</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4474,39 +4474,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>-0.0196</v>
+        <v>4.46</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1005600</v>
+        <v>1403100</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.09</v>
+        <v>0.28</v>
       </c>
       <c r="H89" t="n">
-        <v>37.16</v>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.85</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.268</v>
+        <v>4.668</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.311</v>
+        <v>4.959</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4519,39 +4519,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E90" s="16" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E90" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1005400</v>
+        <v>1402300</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="H90" t="n">
-        <v>66.27</v>
-      </c>
-      <c r="I90" s="15" t="inlineStr">
+        <v>75.67</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.278</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.271</v>
+        <v>0.625</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4564,39 +4564,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0.004</v>
+        <v>5.77</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1001300</v>
+        <v>1355500</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H91" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="I91" s="15" t="inlineStr">
+        <v>57.12</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>2.452</v>
+        <v>5.703</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>2.296</v>
+        <v>5.191</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4609,39 +4609,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>983600</v>
+        <v>1351100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.34</v>
+        <v>0.71</v>
       </c>
       <c r="H92" t="n">
-        <v>34.77</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.78</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>1.374</v>
+        <v>0.506</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1.317</v>
+        <v>0.413</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4654,39 +4654,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.805</v>
       </c>
       <c r="E93" s="17" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0062</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>963200</v>
+        <v>1274000</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.32</v>
+        <v>0.11</v>
       </c>
       <c r="H93" t="n">
-        <v>48.95</v>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
+        <v>64.63</v>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.728</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.575</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4699,28 +4699,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>0.0123</v>
+        <v>4.75</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>939800</v>
+        <v>1271200</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>0.14</v>
       </c>
       <c r="H94" t="n">
-        <v>35.72</v>
+        <v>53.64</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.714</v>
+        <v>4.739</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.831</v>
+        <v>4.597</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4744,28 +4744,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0263</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.635</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E95" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0115</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>918800</v>
+        <v>1240800</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.27</v>
+        <v>2.32</v>
       </c>
       <c r="H95" t="n">
-        <v>56.82</v>
+        <v>48.3</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.634</v>
+        <v>0.694</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.596</v>
+        <v>0.711</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4789,39 +4789,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0.022</v>
+        <v>1.28</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>905400</v>
+        <v>1217000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.11</v>
+        <v>0.42</v>
       </c>
       <c r="H96" t="n">
-        <v>40.29</v>
-      </c>
-      <c r="I96" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.98</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>13.148</v>
+        <v>1.376</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>13.739</v>
+        <v>1.318</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4834,39 +4834,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>0</v>
+        <v>0.65</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>901000</v>
+        <v>1213000</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="H97" t="n">
-        <v>76.75</v>
-      </c>
-      <c r="I97" s="15" t="inlineStr">
+        <v>61.67</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.994</v>
+        <v>0.604</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.821</v>
+        <v>0.61</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4879,39 +4879,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>-0.0023</v>
+        <v>0.49</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>880900</v>
+        <v>1180600</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.11</v>
+        <v>0.39</v>
       </c>
       <c r="H98" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.12</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>4.529</v>
+        <v>0.454</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>4.522</v>
+        <v>0.409</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.745</v>
+        <v>0.765</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>876700</v>
+        <v>1166100</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="H99" t="n">
-        <v>64.18000000000001</v>
-      </c>
-      <c r="I99" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.772</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.62</v>
+        <v>0.772</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4969,39 +4969,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E100" s="16" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E100" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>848600</v>
+        <v>1154200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="H100" t="n">
-        <v>43.85</v>
-      </c>
-      <c r="I100" s="15" t="inlineStr">
+        <v>50.34</v>
+      </c>
+      <c r="I100" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.926</v>
+        <v>0.569</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.969</v>
+        <v>0.575</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5014,28 +5014,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5.32</v>
+        <v>0.755</v>
       </c>
       <c r="E101" s="17" t="n">
-        <v>-0.013</v>
+        <v>-0.0066</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>840100</v>
+        <v>1143900</v>
       </c>
       <c r="G101" s="12" t="n">
         <v>0.26</v>
       </c>
       <c r="H101" t="n">
-        <v>38.77</v>
+        <v>35.05</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>5.714</v>
+        <v>0.789</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>5.754</v>
+        <v>0.842</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5059,39 +5059,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E102" s="16" t="n">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>0.0092</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>827800</v>
+        <v>1140300</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="H102" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.58</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.772</v>
+        <v>0.995</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.772</v>
+        <v>0.821</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5104,40 +5104,36 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E103" s="17" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.275</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>800200</v>
+        <v>1140000</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="H103" t="n">
-        <v>34.14</v>
+        <v>16.56</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J103" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="K103" s="9" t="n">
-        <v>0.586</v>
-      </c>
+      <c r="J103" s="9" t="n"/>
+      <c r="K103" s="9" t="n"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
     </row>
@@ -5149,39 +5145,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>0.0156</v>
+        <v>1.27</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>799400</v>
+        <v>1089600</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="H104" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="I104" s="15" t="inlineStr">
+        <v>91.45</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>1.323</v>
+        <v>0.951</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1.43</v>
+        <v>0.757</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5194,39 +5190,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.91</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E105" s="17" t="n">
-        <v>-0.0109</v>
+        <v>-0.0175</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>782200</v>
+        <v>1056600</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="H105" t="n">
-        <v>37.66</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.59</v>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.929</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.947</v>
+        <v>0.593</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5239,28 +5235,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0.0068</v>
+        <v>4.27</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>771300</v>
+        <v>1046900</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H106" t="n">
-        <v>30.81</v>
+        <v>40.83</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5268,10 +5264,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>4.664</v>
+        <v>4.528</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>4.959</v>
+        <v>4.522</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5284,28 +5280,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E107" s="17" t="n">
-        <v>-0.0357</v>
+        <v>0.345</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>730100</v>
+        <v>1046900</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="H107" t="n">
-        <v>53.57</v>
+        <v>42.85</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5313,10 +5309,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.348</v>
+        <v>0.351</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1.169</v>
+        <v>0.35</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5329,39 +5325,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>7.53</v>
+        <v>0.74</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>0.0107</v>
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>711900</v>
+        <v>1044400</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="H108" t="n">
-        <v>42.08</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.5</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>7.654</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>7.828</v>
+        <v>0.62</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5374,39 +5370,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>-0.0159</v>
+        <v>0.92</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>710000</v>
+        <v>1030300</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.7</v>
+        <v>0.28</v>
       </c>
       <c r="H109" t="n">
-        <v>36.72</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.85</v>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.63</v>
+        <v>0.926</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.636</v>
+        <v>0.969</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5419,39 +5415,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E110" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E110" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>655000</v>
+        <v>1029600</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="H110" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.45</v>
+      </c>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.629</v>
+        <v>0.287</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.656</v>
+        <v>0.278</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5464,39 +5460,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.91</v>
+        <v>5.31</v>
       </c>
       <c r="E111" s="17" t="n">
-        <v>-0.0109</v>
+        <v>-0.0148</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>641700</v>
+        <v>1016900</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H111" t="n">
-        <v>53.95</v>
-      </c>
-      <c r="I111" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.57</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.908</v>
+        <v>5.713</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.795</v>
+        <v>5.753</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5509,39 +5505,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>2.17</v>
+        <v>0.25</v>
       </c>
       <c r="E112" s="17" t="n">
-        <v>-0.0091</v>
+        <v>-0.0196</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>623300</v>
+        <v>1007200</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H112" t="n">
-        <v>47.81</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.16</v>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>2.218</v>
+        <v>0.268</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.11</v>
+        <v>0.311</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5554,39 +5550,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>0.0069</v>
+        <v>0.305</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>621900</v>
+        <v>1004000</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="H113" t="n">
-        <v>44.92</v>
-      </c>
-      <c r="I113" s="15" t="inlineStr">
+        <v>41.46</v>
+      </c>
+      <c r="I113" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>1.474</v>
+        <v>0.318</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.521</v>
+        <v>0.337</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5599,39 +5595,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.53</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>614600</v>
+        <v>961200</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.95</v>
+        <v>0.15</v>
       </c>
       <c r="H114" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="I114" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.14</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.536</v>
+        <v>0.555</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.528</v>
+        <v>0.586</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5644,39 +5640,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E115" s="16" t="n">
-        <v>0</v>
+        <v>0.57</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0.0364</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>585500</v>
+        <v>937200</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.42</v>
+        <v>1.44</v>
       </c>
       <c r="H115" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="I115" s="15" t="inlineStr">
+        <v>75.72</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.634</v>
+        <v>0.535</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.629</v>
+        <v>0.528</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5689,28 +5685,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0.0052</v>
+        <v>7.5</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>0.0067</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>568700</v>
+        <v>925600</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.3</v>
+        <v>0.13</v>
       </c>
       <c r="H116" t="n">
-        <v>42.94</v>
+        <v>40.52</v>
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
@@ -5718,10 +5714,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.991</v>
+        <v>7.651</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>1.008</v>
+        <v>7.828</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5734,28 +5730,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.635</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>561100</v>
+        <v>918800</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="H117" t="n">
-        <v>49.28</v>
+        <v>56.82</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
@@ -5763,10 +5759,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>1.028</v>
+        <v>0.634</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>1.013</v>
+        <v>0.596</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5779,39 +5775,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>0.0059</v>
+        <v>7.91</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>536300</v>
+        <v>911200</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="H118" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="I118" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.03</v>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>3.58</v>
+        <v>7.894</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>3.693</v>
+        <v>8.074</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5824,28 +5820,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E119" s="10" t="n">
-        <v>0.0051</v>
+        <v>1.78</v>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>530100</v>
+        <v>874400</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.11</v>
+        <v>0.68</v>
       </c>
       <c r="H119" t="n">
-        <v>32.37</v>
+        <v>30.01</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5853,10 +5849,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.036</v>
+        <v>1.887</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.075</v>
+        <v>1.956</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5869,39 +5865,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>0.03</v>
+        <v>1.13</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>506000</v>
+        <v>868900</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.89</v>
+        <v>0.09</v>
       </c>
       <c r="H120" t="n">
-        <v>70.42</v>
-      </c>
-      <c r="I120" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.49</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.988</v>
+        <v>1.157</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.976</v>
+        <v>1.103</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5914,45 +5910,1305 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0.0238</v>
+        <v>2.68</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>-0.0037</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>505300</v>
+        <v>867400</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.52</v>
+        <v>0.1</v>
       </c>
       <c r="H121" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="I121" s="15" t="inlineStr">
+        <v>47.39</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.716</v>
+        <v>2.674</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.627</v>
+        <v>2.853</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>863700</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H122" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>4.366</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>-0.0286</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>852800</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H123" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>1.349</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>845600</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H124" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>3.039</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>845000</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>824400</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H126" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>822800</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H127" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>3.579</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>3.693</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>753000</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>2.218</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>749900</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H129" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>712600</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H130" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>710000</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H131" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>7095</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PIE</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>684700</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H132" t="n">
+        <v>51.07</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>1.715</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>1.627</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>668700</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H133" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>660500</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H134" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2488</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ABMB</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>658800</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H135" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>4.829</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>4.834</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>654800</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H136" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>1.943</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>2.067</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>643600</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H137" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>633200</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H138" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>616400</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H139" t="n">
+        <v>70.84</v>
+      </c>
+      <c r="I139" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>1.363</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>615500</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H140" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>1.547</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>1.662</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5139</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AEONCR</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>-0.0231</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>580900</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H141" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>5.366</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>5.548</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>573000</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H142" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="I142" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>6599</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>AEON</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>552900</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H143" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E144" s="15" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>545700</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H144" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E145" s="17" t="n">
+        <v>-0.0153</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>524700</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H145" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>512000</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H146" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>1.976</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>1.972</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>510200</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H147" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>1.178</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>506000</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H148" t="n">
+        <v>70.42</v>
+      </c>
+      <c r="I148" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E149" s="15" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>505800</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H149" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>1.146</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M121"/>
+  <autoFilter ref="A1:M149"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
+++ b/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M149"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -557,28 +557,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0118</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>TRIVE</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.52</v>
+        <v>0.025</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.2381</v>
+        <v>0.6667000000000001</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>22526400</v>
+        <v>5262400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>15.54</v>
+        <v>53.79</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>77.43000000000001</v>
+        <v>66.81</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.418</v>
+        <v>0.017</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.412</v>
+        <v>0.017</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.52高于50日均线0.412，EMA信号偏多；但RSI达77.43，已处超买区，短线动能强但回调风险上升。</t>
+          <t>现价0.025高于50日均线0.017，EMA信号偏多；RSI 66.81接近超买区，可靠性中等。</t>
         </is>
       </c>
     </row>
@@ -610,28 +610,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5.13</v>
+        <v>0.45</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0301</v>
+        <v>0.0227</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>27885300</v>
+        <v>1082700</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.47</v>
+        <v>0.32</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>74.47</v>
+        <v>53.82</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>4.802</v>
+        <v>0.44</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>4.545</v>
+        <v>0.436</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -651,54 +651,62 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价RM5.13高于50日均线RM4.545约12.9%，RSI达74.47，处于超买区间，EMA信号可靠性偏弱。</t>
+          <t>现价0.45略高于50日均线0.436，RSI 53.82处中性区间，无超买迹象，EMA信号可靠性偏中性。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>140401500</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H4" t="n">
-        <v>20.46</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" s="14" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.06059999999999999</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>10042400</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>现价0.35高于50日均线0.314，EMA信号偏多；RSI 60.92未超买，仍有上行空间，信号可靠性中等偏强。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -708,39 +716,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>148015600</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H5" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
         <v>0.255</v>
       </c>
-      <c r="E5" s="15" t="n">
-        <v>0.0851</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>89934200</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="H5" t="n">
-        <v>63.19</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0.234</v>
-      </c>
       <c r="K5" s="9" t="n">
-        <v>0.233</v>
+        <v>0.47</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -753,39 +761,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.17</v>
+        <v>0.255</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.0625</v>
+        <v>0.0851</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>28927400</v>
+        <v>102619500</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.24</v>
+        <v>5.27</v>
       </c>
       <c r="H6" t="n">
-        <v>39.42</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.19</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.179</v>
+        <v>0.234</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.215</v>
+        <v>0.233</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -798,39 +806,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0</v>
+        <v>5.18</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.04019999999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>16728700</v>
+        <v>37215700</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.67</v>
+        <v>1.96</v>
       </c>
       <c r="H7" t="n">
-        <v>72.05</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.89</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.555</v>
+        <v>4.807</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.495</v>
+        <v>4.546</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -843,39 +851,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>0.17</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>15330000</v>
+        <v>30341600</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.31</v>
+        <v>1.3</v>
       </c>
       <c r="H8" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.42</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.154</v>
+        <v>0.179</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.12</v>
+        <v>0.215</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -888,28 +896,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2.51</v>
+        <v>0.195</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.004</v>
+        <v>0.0263</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>12926300</v>
+        <v>27915100</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>62.3</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
@@ -917,10 +925,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2.452</v>
+        <v>0.155</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2.296</v>
+        <v>0.12</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -933,39 +941,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0051</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CUSCAPI</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.055</v>
+        <v>0.505</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.1</v>
+        <v>0.2024</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>12010900</v>
+        <v>25736200</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.47</v>
+        <v>17.75</v>
       </c>
       <c r="H10" t="n">
-        <v>42.26</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.68000000000001</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.058</v>
+        <v>0.416</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.076</v>
+        <v>0.412</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -978,28 +986,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0152</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DGB</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>11110500</v>
+        <v>22408300</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>159.97</v>
+        <v>0.89</v>
       </c>
       <c r="H11" t="n">
-        <v>60.06</v>
+        <v>69.39</v>
       </c>
       <c r="I11" s="16" t="inlineStr">
         <is>
@@ -1007,10 +1015,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.035</v>
+        <v>0.555</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.035</v>
+        <v>0.495</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1032,19 +1040,19 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>0.0204</v>
+        <v>0.0068</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>9945400</v>
+        <v>14634800</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="H12" t="n">
-        <v>55.23</v>
+        <v>53.23</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1052,7 +1060,7 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.737</v>
+        <v>0.736</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0.6860000000000001</v>
@@ -1068,39 +1076,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>2.49</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>-0.004</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>9413800</v>
+        <v>14531300</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H13" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.66</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.052</v>
+        <v>2.45</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.044</v>
+        <v>2.295</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1113,28 +1121,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.515</v>
+        <v>3.68</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>-0.0721</v>
+        <v>-0.1521</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>9389000</v>
+        <v>12821200</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.48</v>
+        <v>1.06</v>
       </c>
       <c r="H14" t="n">
-        <v>46.92</v>
+        <v>56.82</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1142,10 +1150,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.524</v>
+        <v>3.609</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.532</v>
+        <v>2.46</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1158,39 +1166,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.51</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>-0.08109999999999999</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>8984500</v>
+        <v>12716100</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>60.92</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.42</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.332</v>
+        <v>0.523</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.314</v>
+        <v>0.532</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1203,39 +1211,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.155</v>
+        <v>2.08</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>8200100</v>
+        <v>12346800</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.34</v>
+        <v>0.73</v>
       </c>
       <c r="H16" t="n">
-        <v>44.73</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.92</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.156</v>
+        <v>2.118</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.159</v>
+        <v>2.067</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1248,39 +1256,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>-0.0213</v>
+        <v>0.155</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>7892600</v>
+        <v>12341300</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.8</v>
+        <v>0.52</v>
       </c>
       <c r="H17" t="n">
-        <v>55.03</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.451</v>
+        <v>0.156</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.413</v>
+        <v>0.159</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1293,28 +1301,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.215</v>
+        <v>0.055</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>0.0488</v>
+        <v>0.1</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>7375900</v>
+        <v>12060900</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.3</v>
+        <v>0.47</v>
       </c>
       <c r="H18" t="n">
-        <v>35.23</v>
+        <v>42.26</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
@@ -1322,10 +1330,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.233</v>
+        <v>0.058</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.247</v>
+        <v>0.076</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1338,28 +1346,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0152</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>DGB</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.0208</v>
+        <v>0.04</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7138700</v>
+        <v>11111700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.25</v>
+        <v>159.98</v>
       </c>
       <c r="H19" t="n">
-        <v>33.57</v>
+        <v>60.06</v>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
@@ -1367,10 +1375,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.27</v>
+        <v>0.035</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.322</v>
+        <v>0.035</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1383,28 +1391,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.455</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>-0.0319</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>7009800</v>
+        <v>10673200</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.36</v>
+        <v>1.08</v>
       </c>
       <c r="H20" t="n">
-        <v>53.62</v>
+        <v>53.57</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1412,10 +1420,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.303</v>
+        <v>0.45</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.291</v>
+        <v>0.413</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1428,28 +1436,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.52</v>
+        <v>0.305</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>0.0196</v>
+        <v>0.0167</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>6900100</v>
+        <v>9985300</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="H21" t="n">
-        <v>27.66</v>
+        <v>53.62</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1457,10 +1465,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.612</v>
+        <v>0.303</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.827</v>
+        <v>0.291</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1473,28 +1481,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>-0.0435</v>
+        <v>0.215</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.0488</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>6855100</v>
+        <v>9603700</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.82</v>
+        <v>0.39</v>
       </c>
       <c r="H22" t="n">
-        <v>37.36</v>
+        <v>35.23</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -1502,10 +1510,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.121</v>
+        <v>0.233</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.124</v>
+        <v>0.247</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1518,39 +1526,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.77</v>
+        <v>0.045</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6627000</v>
+        <v>9460800</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="H23" t="n">
-        <v>48.13</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.47</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.773</v>
+        <v>0.052</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.774</v>
+        <v>0.044</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1563,39 +1571,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>-0.0244</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>6366900</v>
+        <v>9164600</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>42.46</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.13</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.408</v>
+        <v>0.773</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.411</v>
+        <v>0.774</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1608,33 +1616,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6364200</v>
+        <v>9028400</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
+      </c>
+      <c r="H25" t="n">
+        <v>46.81</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
+      <c r="J25" s="9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0.87</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
     </row>
@@ -1655,19 +1670,19 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0.0244</v>
+        <v>0.205</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6312400</v>
+        <v>8984000</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="H26" t="n">
-        <v>58.61</v>
+        <v>55.27</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1691,28 +1706,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.865</v>
+        <v>0.78</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0127</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6199000</v>
+        <v>8922000</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.33</v>
+        <v>2.06</v>
       </c>
       <c r="H27" t="n">
-        <v>46.81</v>
+        <v>42.88</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1720,10 +1735,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.868</v>
+        <v>0.8</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.87</v>
+        <v>0.806</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1736,39 +1751,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>1.84</v>
+        <v>0.245</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0.011</v>
+        <v>0.0208</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6146900</v>
+        <v>8899300</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.83</v>
+        <v>0.31</v>
       </c>
       <c r="H28" t="n">
-        <v>42.58</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.57</v>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1.887</v>
+        <v>0.27</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>1.959</v>
+        <v>0.322</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1781,39 +1796,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0007</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PUC</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
+        <v>0.53</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6100700</v>
+        <v>8465100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.73</v>
+        <v>0.22</v>
       </c>
       <c r="H29" t="n">
-        <v>53.89</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.77</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.033</v>
+        <v>0.613</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.032</v>
+        <v>0.827</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1835,19 +1850,19 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>-0.0062</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6007800</v>
+        <v>8025000</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>47.5</v>
+        <v>50.19</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1855,7 +1870,7 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0.8070000000000001</v>
@@ -1871,28 +1886,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>-0.0127</v>
+        <v>0.475</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5846400</v>
+        <v>7888000</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.54</v>
+        <v>0.33</v>
       </c>
       <c r="H31" t="n">
-        <v>64.22</v>
+        <v>52.83</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1900,10 +1915,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.377</v>
+        <v>0.469</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.372</v>
+        <v>0.472</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1916,39 +1931,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>0.0106</v>
+        <v>2.48</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5815900</v>
+        <v>7435800</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="H32" t="n">
-        <v>52.83</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.57</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.469</v>
+        <v>2.57</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.472</v>
+        <v>2.451</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1961,33 +1976,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>-0.04</v>
+        <v>0.395</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.0128</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5568500</v>
+        <v>7391400</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
+      </c>
+      <c r="H33" t="n">
+        <v>56.49</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
+      <c r="J33" s="9" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0.325</v>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
     </row>
@@ -1999,39 +2021,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5406400</v>
+        <v>7091500</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.25</v>
+        <v>0.63</v>
       </c>
       <c r="H34" t="n">
-        <v>45.55</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.46</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.801</v>
+        <v>0.408</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.411</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2044,39 +2066,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
+        <v>0.11</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5358200</v>
+        <v>7012600</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.11</v>
+        <v>0.84</v>
       </c>
       <c r="H35" t="n">
-        <v>78.19</v>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.36</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.332</v>
+        <v>0.121</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.197</v>
+        <v>0.124</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2089,28 +2111,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.0476</v>
+        <v>0.39</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5341700</v>
+        <v>6649200</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>2.67</v>
+        <v>0.14</v>
       </c>
       <c r="H36" t="n">
-        <v>75.29000000000001</v>
+        <v>78.19</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
@@ -2118,10 +2140,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.381</v>
+        <v>0.332</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.346</v>
+        <v>0.197</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2134,28 +2156,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0118</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TRIVE</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>0.3333</v>
+        <v>0.385</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>-0.0253</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5248200</v>
+        <v>6639900</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>53.65</v>
+        <v>0.62</v>
       </c>
       <c r="H37" t="n">
-        <v>58.93</v>
+        <v>59.01</v>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
@@ -2163,10 +2185,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.016</v>
+        <v>0.376</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.017</v>
+        <v>0.372</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2179,28 +2201,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>-0.004</v>
+        <v>1.84</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.011</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5240200</v>
+        <v>6516300</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.26</v>
+        <v>0.88</v>
       </c>
       <c r="H38" t="n">
-        <v>45.9</v>
+        <v>42.58</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2208,10 +2230,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>2.572</v>
+        <v>1.887</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>2.452</v>
+        <v>1.959</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2224,40 +2246,33 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>-0.0048</v>
+        <v>0.265</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5226300</v>
+        <v>6455800</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H39" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>2.117</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>2.066</v>
-      </c>
+        <v>0.43</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
     </row>
@@ -2269,39 +2284,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0145</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TFP</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0</v>
+        <v>2.93</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5209300</v>
+        <v>6281000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1.4</v>
+        <v>0.72</v>
       </c>
       <c r="H40" t="n">
-        <v>38.54</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.36</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.062</v>
+        <v>2.683</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>2.522</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2314,39 +2329,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.0256</v>
+        <v>1.75</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>-0.0223</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5088700</v>
+        <v>6102100</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H41" t="n">
-        <v>57.61</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.37</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.384</v>
+        <v>1.741</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.325</v>
+        <v>1.55</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2359,28 +2374,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>-0.0164</v>
+        <v>0.035</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5000100</v>
+        <v>6100700</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.48</v>
+        <v>0.73</v>
       </c>
       <c r="H42" t="n">
-        <v>46.01</v>
+        <v>53.89</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
@@ -2388,10 +2403,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.607</v>
+        <v>0.033</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.606</v>
+        <v>0.032</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2404,40 +2419,33 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>3.94</v>
+        <v>0.12</v>
       </c>
       <c r="E43" s="17" t="n">
-        <v>-0.0922</v>
+        <v>-0.04</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4812600</v>
+        <v>5739100</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H43" t="n">
-        <v>63.21</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J43" s="9" t="n">
-        <v>3.634</v>
-      </c>
-      <c r="K43" s="9" t="n">
-        <v>2.465</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
     </row>
@@ -2449,28 +2457,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>-0.0086</v>
+        <v>0.44</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4649000</v>
+        <v>5670500</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.31</v>
+        <v>2.84</v>
       </c>
       <c r="H44" t="n">
-        <v>63.01</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="I44" s="16" t="inlineStr">
         <is>
@@ -2478,10 +2486,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.533</v>
+        <v>0.381</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.485</v>
+        <v>0.346</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2494,39 +2502,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0.0333</v>
+        <v>0.01</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4640800</v>
+        <v>5632200</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.11</v>
+        <v>7.84</v>
       </c>
       <c r="H45" t="n">
-        <v>50.05</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.43</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.157</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.148</v>
+        <v>0.007</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2539,39 +2547,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>TFP</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0.0282</v>
+        <v>0.055</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>4437600</v>
+        <v>5209300</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.62</v>
+        <v>1.4</v>
       </c>
       <c r="H46" t="n">
-        <v>66.09</v>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.54</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.341</v>
+        <v>0.062</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.321</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2584,28 +2592,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>-0.0168</v>
+        <v>0.66</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0.0076</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>4380600</v>
+        <v>5078900</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="H47" t="n">
-        <v>63.76</v>
+        <v>58.87</v>
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
@@ -2613,10 +2621,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>2.682</v>
+        <v>0.636</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>2.522</v>
+        <v>0.58</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2629,28 +2637,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>0.0382</v>
+        <v>0.57</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3978400</v>
+        <v>5069900</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="H48" t="n">
-        <v>62.34</v>
+        <v>61.57</v>
       </c>
       <c r="I48" s="16" t="inlineStr">
         <is>
@@ -2658,10 +2666,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.638</v>
+        <v>0.533</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.581</v>
+        <v>0.485</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2683,19 +2691,19 @@
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>10.06</v>
+        <v>10.04</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3804200</v>
+        <v>5038100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H49" t="n">
-        <v>42.25</v>
+        <v>40.82</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2703,7 +2711,7 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>10.149</v>
+        <v>10.147</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>10.294</v>
@@ -2719,39 +2727,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3374800</v>
+        <v>5000300</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.98</v>
+        <v>0.48</v>
       </c>
       <c r="H50" t="n">
-        <v>42.35</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.01</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>1.579</v>
+        <v>0.607</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>1.642</v>
+        <v>0.606</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2764,39 +2772,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.155</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3308600</v>
+        <v>4944300</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.27</v>
+        <v>0.12</v>
       </c>
       <c r="H51" t="n">
-        <v>44.18</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.05</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.362</v>
+        <v>0.157</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.296</v>
+        <v>0.148</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2809,39 +2817,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>-0.0444</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3250100</v>
+        <v>4613100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.51</v>
+        <v>0.37</v>
       </c>
       <c r="H52" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.26</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.367</v>
+        <v>1.361</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.367</v>
+        <v>1.296</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2854,28 +2862,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>1.34</v>
+        <v>7.8</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>0.0806</v>
+        <v>0.0026</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3178300</v>
+        <v>4545400</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.16</v>
+        <v>0.35</v>
       </c>
       <c r="H53" t="n">
-        <v>84.04000000000001</v>
+        <v>50.83</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
@@ -2883,10 +2891,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>1.09</v>
+        <v>7.803</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.913</v>
+        <v>7.741</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2899,39 +2907,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0</v>
+        <v>0.365</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0282</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3102900</v>
+        <v>4526900</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.28</v>
+        <v>0.64</v>
       </c>
       <c r="H54" t="n">
-        <v>47.24</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.09</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.075</v>
+        <v>0.341</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.025</v>
+        <v>0.321</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2944,39 +2952,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3081200</v>
+        <v>4473000</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.47</v>
+        <v>0.71</v>
       </c>
       <c r="H55" t="n">
-        <v>66.27</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.04</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.278</v>
+        <v>0.77</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.271</v>
+        <v>0.772</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2989,39 +2997,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>0.0026</v>
+        <v>1.03</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3079600</v>
+        <v>4376800</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.24</v>
+        <v>0.39</v>
       </c>
       <c r="H56" t="n">
-        <v>50.83</v>
-      </c>
-      <c r="I56" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.39</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>7.803</v>
+        <v>1.074</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>7.741</v>
+        <v>1.025</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3043,19 +3051,19 @@
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="E57" s="17" t="n">
-        <v>-0.0173</v>
+        <v>-0.0058</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3006000</v>
+        <v>4318900</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.54</v>
+        <v>0.77</v>
       </c>
       <c r="H57" t="n">
-        <v>41.33</v>
+        <v>43.37</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3063,10 +3071,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>1.761</v>
+        <v>1.763</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1.797</v>
+        <v>1.798</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3079,39 +3087,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.225</v>
+        <v>0.36</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>-0.0217</v>
+        <v>-0.0137</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2908400</v>
+        <v>3934800</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
       <c r="H58" t="n">
-        <v>65.48999999999999</v>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.44</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.206</v>
+        <v>0.366</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.181</v>
+        <v>0.367</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3124,39 +3132,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.295</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2709100</v>
+        <v>3696300</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="H59" t="n">
-        <v>38.27</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.27</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.262</v>
+        <v>0.278</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.3</v>
+        <v>0.271</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3169,28 +3177,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>-0.0112</v>
+        <v>1.34</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0.0806</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2676500</v>
+        <v>3609700</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.11</v>
+        <v>1.31</v>
       </c>
       <c r="H60" t="n">
-        <v>56.17</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
@@ -3198,10 +3206,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>1.743</v>
+        <v>1.09</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1.55</v>
+        <v>0.913</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3214,28 +3222,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.895</v>
+        <v>0.79</v>
       </c>
       <c r="E61" s="17" t="n">
-        <v>-0.0479</v>
+        <v>-0.0247</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2629800</v>
+        <v>3434200</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.55</v>
+        <v>0.31</v>
       </c>
       <c r="H61" t="n">
-        <v>54.24</v>
+        <v>61.74</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3243,10 +3251,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.89</v>
+        <v>0.727</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.852</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3259,39 +3267,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>1.55</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2613000</v>
+        <v>3431800</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.15</v>
+        <v>0.99</v>
       </c>
       <c r="H62" t="n">
-        <v>48.57</v>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.52</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>2.339</v>
+        <v>1.578</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>2.251</v>
+        <v>1.642</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3304,28 +3312,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>YXPM</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.215</v>
+        <v>0.25</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>-0.0444</v>
+        <v>-0.0196</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2574500</v>
+        <v>3383600</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>4.98</v>
+        <v>0.29</v>
       </c>
       <c r="H63" t="n">
-        <v>49.65</v>
+        <v>37.16</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
@@ -3333,10 +3341,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.216</v>
+        <v>0.268</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.214</v>
+        <v>0.311</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3349,28 +3357,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>0.0183</v>
+        <v>4.42</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2570800</v>
+        <v>3363500</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.21</v>
+        <v>0.55</v>
       </c>
       <c r="H64" t="n">
-        <v>76.28</v>
+        <v>80.33</v>
       </c>
       <c r="I64" s="16" t="inlineStr">
         <is>
@@ -3378,10 +3386,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.021</v>
+        <v>3.709</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.861</v>
+        <v>3.283</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3394,28 +3402,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0</v>
+        <v>1.22</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2419300</v>
+        <v>3359600</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="H65" t="n">
-        <v>33.24</v>
+        <v>38.27</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3423,10 +3431,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>4.823</v>
+        <v>1.262</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>4.945</v>
+        <v>1.3</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3439,39 +3447,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0</v>
+        <v>4.71</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>-0.0021</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2308800</v>
+        <v>3293700</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H66" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.42</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.492</v>
+        <v>4.822</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.411</v>
+        <v>4.945</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3484,28 +3492,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>0.0134</v>
+        <v>0.885</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>-0.0585</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2291300</v>
+        <v>3272000</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H67" t="n">
-        <v>58.56</v>
+        <v>51.27</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3513,10 +3521,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>2.888</v>
+        <v>0.889</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.7</v>
+        <v>0.852</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3538,19 +3546,19 @@
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>0.0247</v>
+        <v>0.0309</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2218800</v>
+        <v>3237600</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.34</v>
+        <v>0.49</v>
       </c>
       <c r="H68" t="n">
-        <v>38.93</v>
+        <v>40.42</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3558,7 +3566,7 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>1.716</v>
+        <v>1.717</v>
       </c>
       <c r="K68" s="9" t="n">
         <v>1.832</v>
@@ -3574,39 +3582,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>7.57</v>
+        <v>2.31</v>
       </c>
       <c r="E69" s="15" t="n">
-        <v>0.004</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2206300</v>
+        <v>3214100</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="H69" t="n">
-        <v>29.05</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.57</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>7.9</v>
+        <v>2.339</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>8.231999999999999</v>
+        <v>2.251</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3619,28 +3627,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>0.0036</v>
+        <v>1.12</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2098900</v>
+        <v>3107200</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H70" t="n">
-        <v>83.48999999999999</v>
+        <v>43.06</v>
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
@@ -3648,10 +3656,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>2.516</v>
+        <v>1.17</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.161</v>
+        <v>1.148</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3664,28 +3672,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>0.0022</v>
+        <v>0.0092</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2079900</v>
+        <v>3080900</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="H71" t="n">
-        <v>84.48999999999999</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3693,10 +3701,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>3.717</v>
+        <v>1.02</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>3.284</v>
+        <v>0.861</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3709,28 +3717,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E72" s="17" t="n">
-        <v>-0.019</v>
+        <v>7.56</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.0027</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2038800</v>
+        <v>2971000</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>3.21</v>
+        <v>0.26</v>
       </c>
       <c r="H72" t="n">
-        <v>46.13</v>
+        <v>28.35</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3738,10 +3746,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1.581</v>
+        <v>7.899</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>1.507</v>
+        <v>8.231999999999999</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3754,28 +3762,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3.09</v>
+        <v>0.225</v>
       </c>
       <c r="E73" s="17" t="n">
-        <v>-0.0283</v>
+        <v>-0.0217</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1977500</v>
+        <v>2954500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="H73" t="n">
-        <v>85.48999999999999</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
@@ -3783,10 +3791,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>2.359</v>
+        <v>0.206</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>1.835</v>
+        <v>0.181</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3799,39 +3807,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0</v>
+        <v>2.92</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1975500</v>
+        <v>2950300</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.62</v>
+        <v>0.2</v>
       </c>
       <c r="H74" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.58</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>3.273</v>
+        <v>2.792</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>3.465</v>
+        <v>2.649</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3844,28 +3852,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.88</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E75" s="17" t="n">
-        <v>-0.0069</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1917900</v>
+        <v>2878100</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H75" t="n">
-        <v>64.29000000000001</v>
+        <v>70.89</v>
       </c>
       <c r="I75" s="16" t="inlineStr">
         <is>
@@ -3873,10 +3881,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.789</v>
+        <v>0.492</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.648</v>
+        <v>0.41</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3889,39 +3897,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>0.0064</v>
+        <v>3.15</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1847700</v>
+        <v>2789500</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.3</v>
+        <v>0.88</v>
       </c>
       <c r="H76" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="I76" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.3</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.768</v>
+        <v>3.273</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.754</v>
+        <v>3.465</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3934,28 +3942,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.64</v>
+        <v>13.04</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>0.0159</v>
+        <v>0.0252</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1833100</v>
+        <v>2775200</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="H77" t="n">
-        <v>57.06</v>
+        <v>41.84</v>
       </c>
       <c r="I77" s="16" t="inlineStr">
         <is>
@@ -3963,10 +3971,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.622</v>
+        <v>13.152</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.586</v>
+        <v>13.74</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3979,28 +3987,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.07</v>
+        <v>3.7</v>
       </c>
       <c r="E78" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0054</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1801500</v>
+        <v>2725500</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.22</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>78.01000000000001</v>
+        <v>77.33</v>
       </c>
       <c r="I78" s="16" t="inlineStr">
         <is>
@@ -4008,10 +4016,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.923</v>
+        <v>3.381</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.775</v>
+        <v>2.938</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4024,28 +4032,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>-0.0072</v>
+        <v>0.79</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1741900</v>
+        <v>2701600</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.22</v>
+        <v>0.43</v>
       </c>
       <c r="H79" t="n">
-        <v>51.06</v>
+        <v>64.37</v>
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
@@ -4053,10 +4061,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.768</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.665</v>
+        <v>0.754</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4069,39 +4077,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>1.52</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>-0.038</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1740900</v>
+        <v>2695900</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.47</v>
+        <v>4.24</v>
       </c>
       <c r="H80" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="I80" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.25</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>1.116</v>
+        <v>1.578</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1.021</v>
+        <v>1.507</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4114,28 +4122,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.13</v>
+        <v>2.77</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>0.0089</v>
+        <v>0.0036</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1732700</v>
+        <v>2600300</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.25</v>
+        <v>0.54</v>
       </c>
       <c r="H81" t="n">
-        <v>44.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4143,10 +4151,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.171</v>
+        <v>2.516</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.148</v>
+        <v>2.161</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4159,28 +4167,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>YXPM</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.265</v>
+        <v>0.215</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>-0.0185</v>
+        <v>-0.0444</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1707300</v>
+        <v>2574500</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.61</v>
+        <v>4.98</v>
       </c>
       <c r="H82" t="n">
-        <v>71.53</v>
+        <v>49.65</v>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
@@ -4188,10 +4196,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.232</v>
+        <v>0.216</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.211</v>
+        <v>0.214</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4204,39 +4212,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.865</v>
+        <v>3.06</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0377</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1638600</v>
+        <v>2566700</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.52</v>
+        <v>0.87</v>
       </c>
       <c r="H83" t="n">
-        <v>56.68</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.58</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.861</v>
+        <v>2.356</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.856</v>
+        <v>1.835</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4249,28 +4257,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>13.02</v>
+        <v>3.05</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.0236</v>
+        <v>0.0201</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1636900</v>
+        <v>2525600</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="H84" t="n">
-        <v>41.08</v>
+        <v>59.37</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4278,10 +4286,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>13.15</v>
+        <v>2.89</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>13.74</v>
+        <v>2.7</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4294,28 +4302,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.835</v>
+        <v>1.05</v>
       </c>
       <c r="E85" s="17" t="n">
-        <v>-0.0118</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1588900</v>
+        <v>2524800</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.52</v>
+        <v>0.31</v>
       </c>
       <c r="H85" t="n">
-        <v>61.35</v>
+        <v>75.19</v>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
@@ -4323,10 +4331,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.921</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.729</v>
+        <v>0.775</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4339,39 +4347,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.905</v>
+        <v>0.675</v>
       </c>
       <c r="E86" s="17" t="n">
-        <v>-0.0163</v>
+        <v>-0.0217</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1516900</v>
+        <v>2514300</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.66</v>
+        <v>0.32</v>
       </c>
       <c r="H86" t="n">
-        <v>35.81</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.14</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.928</v>
+        <v>0.681</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.947</v>
+        <v>0.665</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4384,28 +4392,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0.0172</v>
+        <v>0.265</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1498900</v>
+        <v>2504700</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.21</v>
+        <v>0.89</v>
       </c>
       <c r="H87" t="n">
-        <v>44.81</v>
+        <v>71.53</v>
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
@@ -4413,10 +4421,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.297</v>
+        <v>0.232</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.311</v>
+        <v>0.211</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4429,39 +4437,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E88" s="17" t="n">
-        <v>-0.0286</v>
+        <v>0.295</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1433100</v>
+        <v>2322000</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.3</v>
+        <v>1.11</v>
       </c>
       <c r="H88" t="n">
-        <v>51.39</v>
-      </c>
-      <c r="I88" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.339</v>
+        <v>0.295</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.333</v>
+        <v>0.296</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4474,39 +4482,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>4.46</v>
+        <v>2.06</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>0.0159</v>
+        <v>0.0049</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1403100</v>
+        <v>2211300</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.28</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H89" t="n">
-        <v>33.85</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.99</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>4.668</v>
+        <v>2.062</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>4.959</v>
+        <v>2.102</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4519,28 +4527,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.78</v>
+        <v>0.29</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1402300</v>
+        <v>2199300</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="H90" t="n">
-        <v>75.67</v>
+        <v>39.08</v>
       </c>
       <c r="I90" s="16" t="inlineStr">
         <is>
@@ -4548,10 +4556,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.296</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.625</v>
+        <v>0.311</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4564,39 +4572,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>-0.0069</v>
+        <v>4.5</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.0251</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1355500</v>
+        <v>2178300</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.09</v>
+        <v>0.44</v>
       </c>
       <c r="H91" t="n">
-        <v>57.12</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.64</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>5.703</v>
+        <v>4.672</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>5.191</v>
+        <v>4.96</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4609,28 +4617,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.545</v>
+        <v>0.645</v>
       </c>
       <c r="E92" s="15" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0238</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1351100</v>
+        <v>2148000</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="H92" t="n">
-        <v>61.78</v>
+        <v>58.16</v>
       </c>
       <c r="I92" s="16" t="inlineStr">
         <is>
@@ -4638,10 +4646,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.506</v>
+        <v>0.622</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.413</v>
+        <v>0.586</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4654,28 +4662,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.805</v>
+        <v>0.83</v>
       </c>
       <c r="E93" s="17" t="n">
-        <v>-0.0062</v>
+        <v>-0.0178</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1274000</v>
+        <v>2141100</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>64.63</v>
+        <v>59.93</v>
       </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
@@ -4683,10 +4691,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.728</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.729</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4699,39 +4707,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>4.75</v>
+        <v>7.91</v>
       </c>
       <c r="E94" s="15" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1271200</v>
+        <v>2119500</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="H94" t="n">
-        <v>53.64</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.03</v>
+      </c>
+      <c r="I94" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>4.739</v>
+        <v>7.894</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>4.597</v>
+        <v>8.074</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4744,39 +4752,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0263</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E95" s="17" t="n">
-        <v>-0.0115</v>
+        <v>1.16</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1240800</v>
+        <v>2074300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>2.32</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.75</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.694</v>
+        <v>1.116</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.711</v>
+        <v>1.021</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4789,28 +4797,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v>0.0159</v>
+        <v>0.865</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1217000</v>
+        <v>2022300</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="H96" t="n">
-        <v>37.98</v>
+        <v>56.68</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4818,10 +4826,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>1.376</v>
+        <v>0.861</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>1.318</v>
+        <v>0.856</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4834,39 +4842,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>-0.0152</v>
+        <v>1.95</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1213000</v>
+        <v>1946200</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="H97" t="n">
-        <v>61.67</v>
-      </c>
-      <c r="I97" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.43</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.604</v>
+        <v>1.977</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.61</v>
+        <v>1.972</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4879,28 +4887,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1180600</v>
+        <v>1907000</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="H98" t="n">
-        <v>71.12</v>
+        <v>72.39</v>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
@@ -4908,10 +4916,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.454</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.409</v>
+        <v>0.625</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4924,39 +4932,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1166100</v>
+        <v>1902300</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="H99" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.64</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.772</v>
+        <v>1.323</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.772</v>
+        <v>1.43</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4969,39 +4977,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0</v>
+        <v>0.905</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>-0.0163</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1154200</v>
+        <v>1833300</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="H100" t="n">
-        <v>50.34</v>
-      </c>
-      <c r="I100" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.81</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.569</v>
+        <v>0.928</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.575</v>
+        <v>0.947</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5014,28 +5022,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E101" s="17" t="n">
-        <v>-0.0066</v>
+        <v>1.27</v>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1143900</v>
+        <v>1819100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.26</v>
+        <v>0.63</v>
       </c>
       <c r="H101" t="n">
-        <v>35.05</v>
+        <v>36.42</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5043,10 +5051,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.789</v>
+        <v>1.375</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.842</v>
+        <v>1.317</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5059,28 +5067,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v>0.0092</v>
+        <v>5.76</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1140300</v>
+        <v>1810600</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="H102" t="n">
-        <v>77.58</v>
+        <v>56.65</v>
       </c>
       <c r="I102" s="16" t="inlineStr">
         <is>
@@ -5088,10 +5096,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.995</v>
+        <v>5.702</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.821</v>
+        <v>5.191</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5104,36 +5112,40 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>0</v>
+        <v>0.645</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1140000</v>
+        <v>1771800</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.06</v>
+        <v>0.59</v>
       </c>
       <c r="H103" t="n">
-        <v>16.56</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J103" s="9" t="n"/>
-      <c r="K103" s="9" t="n"/>
+        <v>60.21</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>0.61</v>
+      </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
     </row>
@@ -5145,28 +5157,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>-0.0155</v>
+        <v>-0.0092</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1089600</v>
+        <v>1737200</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="H104" t="n">
-        <v>91.45</v>
+        <v>74</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5174,10 +5186,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.951</v>
+        <v>0.993</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.757</v>
+        <v>0.821</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5190,39 +5202,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.585</v>
       </c>
       <c r="E105" s="17" t="n">
-        <v>-0.0175</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1056600</v>
+        <v>1674200</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="H105" t="n">
-        <v>43.59</v>
-      </c>
-      <c r="I105" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.29</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.628</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.593</v>
+        <v>0.656</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5235,28 +5247,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>4.27</v>
+        <v>0.25</v>
       </c>
       <c r="E106" s="17" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.1228</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1046900</v>
+        <v>1666000</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H106" t="n">
-        <v>40.83</v>
+        <v>48.47</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5264,10 +5276,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>4.528</v>
+        <v>0.264</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>4.522</v>
+        <v>0.223</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5289,19 +5301,19 @@
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1046900</v>
+        <v>1654600</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="H107" t="n">
-        <v>42.85</v>
+        <v>38.45</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5309,7 +5321,7 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>0.35</v>
@@ -5325,39 +5337,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
+        <v>5.3</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1044400</v>
+        <v>1613900</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.17</v>
+        <v>0.49</v>
       </c>
       <c r="H108" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="I108" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.37</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>5.712</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.62</v>
+        <v>5.753</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5370,28 +5382,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1030300</v>
+        <v>1603600</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.28</v>
+        <v>0.51</v>
       </c>
       <c r="H109" t="n">
-        <v>43.85</v>
+        <v>54.28</v>
       </c>
       <c r="I109" s="16" t="inlineStr">
         <is>
@@ -5399,10 +5411,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.926</v>
+        <v>0.437</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.969</v>
+        <v>0.452</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5415,39 +5427,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>0</v>
+        <v>4.23</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>-0.014</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1029600</v>
+        <v>1602900</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
       </c>
       <c r="H110" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="I110" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.78</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.287</v>
+        <v>4.524</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.278</v>
+        <v>4.521</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5460,28 +5472,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>-0.0148</v>
+        <v>4.74</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1016900</v>
+        <v>1587900</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="H111" t="n">
-        <v>38.57</v>
+        <v>52.79</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5489,10 +5501,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>5.713</v>
+        <v>4.738</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>5.753</v>
+        <v>4.597</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5505,28 +5517,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E112" s="17" t="n">
-        <v>-0.0196</v>
+        <v>0.57</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0.0364</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1007200</v>
+        <v>1585100</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.09</v>
+        <v>2.44</v>
       </c>
       <c r="H112" t="n">
-        <v>37.16</v>
+        <v>75.72</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5534,10 +5546,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.268</v>
+        <v>0.535</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.311</v>
+        <v>0.528</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5550,39 +5562,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>-0.0161</v>
+        <v>7.5</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>0.0067</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1004000</v>
+        <v>1580900</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="H113" t="n">
-        <v>41.46</v>
-      </c>
-      <c r="I113" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.52</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.318</v>
+        <v>7.651</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.337</v>
+        <v>7.828</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5595,28 +5607,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.53</v>
+        <v>4.12</v>
       </c>
       <c r="E114" s="17" t="n">
-        <v>-0.009300000000000001</v>
+        <v>-0.026</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>961200</v>
+        <v>1563300</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.15</v>
+        <v>0.62</v>
       </c>
       <c r="H114" t="n">
-        <v>34.14</v>
+        <v>41.59</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5624,10 +5636,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.555</v>
+        <v>4.366</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.586</v>
+        <v>4.41</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5640,39 +5652,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E115" s="15" t="n">
-        <v>0.0364</v>
+        <v>1.11</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>-0.0089</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>937200</v>
+        <v>1551300</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>1.44</v>
+        <v>0.17</v>
       </c>
       <c r="H115" t="n">
-        <v>75.72</v>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.66</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.535</v>
+        <v>1.155</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.528</v>
+        <v>1.103</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5685,39 +5697,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v>0.0067</v>
+        <v>0.41</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>925600</v>
+        <v>1529900</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="H116" t="n">
-        <v>40.52</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.12</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>7.651</v>
+        <v>0.403</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>7.828</v>
+        <v>0.403</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5730,39 +5742,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.635</v>
+        <v>0.345</v>
       </c>
       <c r="E117" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0143</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>918800</v>
+        <v>1528900</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="H117" t="n">
-        <v>56.82</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.26</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.634</v>
+        <v>0.34</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.596</v>
+        <v>0.334</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5775,28 +5787,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v>0.0051</v>
+        <v>2.69</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>911200</v>
+        <v>1508200</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="H118" t="n">
-        <v>49.03</v>
+        <v>48.27</v>
       </c>
       <c r="I118" s="16" t="inlineStr">
         <is>
@@ -5804,10 +5816,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>7.894</v>
+        <v>2.675</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>8.074</v>
+        <v>2.853</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5820,39 +5832,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.78</v>
+        <v>1.26</v>
       </c>
       <c r="E119" s="17" t="n">
-        <v>-0.0111</v>
+        <v>-0.0233</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>874400</v>
+        <v>1501200</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.68</v>
+        <v>0.24</v>
       </c>
       <c r="H119" t="n">
-        <v>30.01</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.59999999999999</v>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.887</v>
+        <v>0.95</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.956</v>
+        <v>0.757</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5865,39 +5877,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E120" s="15" t="n">
-        <v>0.0089</v>
+        <v>0.485</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>-0.0102</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>868900</v>
+        <v>1475600</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.09</v>
+        <v>0.48</v>
       </c>
       <c r="H120" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.22</v>
+      </c>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.157</v>
+        <v>0.454</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.103</v>
+        <v>0.409</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5910,39 +5922,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>-0.0037</v>
+        <v>3.43</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>0.0059</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>867400</v>
+        <v>1426400</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="H121" t="n">
-        <v>47.39</v>
-      </c>
-      <c r="I121" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.72</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>2.674</v>
+        <v>3.58</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>2.853</v>
+        <v>3.693</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5955,28 +5967,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>4.12</v>
+        <v>2.9</v>
       </c>
       <c r="E122" s="17" t="n">
-        <v>-0.026</v>
+        <v>-0.0102</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>863700</v>
+        <v>1422400</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="H122" t="n">
-        <v>41.59</v>
+        <v>40.39</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5984,10 +5996,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>4.366</v>
+        <v>2.989</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>4.41</v>
+        <v>3.039</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6000,28 +6012,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>1.36</v>
+        <v>0.83</v>
       </c>
       <c r="E123" s="17" t="n">
-        <v>-0.0286</v>
+        <v>-0.006</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>852800</v>
+        <v>1404200</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.26</v>
+        <v>0.92</v>
       </c>
       <c r="H123" t="n">
-        <v>54.62</v>
+        <v>29.7</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6029,10 +6041,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>1.349</v>
+        <v>0.875</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>1.169</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6045,39 +6057,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E124" s="17" t="n">
-        <v>-0.0068</v>
+        <v>0.745</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>845600</v>
+        <v>1401900</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="H124" t="n">
-        <v>41.15</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.18000000000001</v>
+      </c>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>2.99</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>3.039</v>
+        <v>0.62</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6090,39 +6102,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E125" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>1.87</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>845000</v>
+        <v>1400200</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="H125" t="n">
-        <v>38.26</v>
-      </c>
-      <c r="I125" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.89</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>1.323</v>
+        <v>1.942</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>1.43</v>
+        <v>2.066</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6135,28 +6147,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>-0.0217</v>
+        <v>0.54</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>824400</v>
+        <v>1390500</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.45</v>
+        <v>0.73</v>
       </c>
       <c r="H126" t="n">
-        <v>52.3</v>
+        <v>61.03</v>
       </c>
       <c r="I126" s="16" t="inlineStr">
         <is>
@@ -6164,10 +6176,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.907</v>
+        <v>0.506</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.795</v>
+        <v>0.413</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6180,39 +6192,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="E127" s="15" t="n">
-        <v>0.0029</v>
+        <v>0.915</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>822800</v>
+        <v>1384700</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.15</v>
+        <v>0.38</v>
       </c>
       <c r="H127" t="n">
-        <v>33.69</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.27</v>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>3.579</v>
+        <v>0.925</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>3.693</v>
+        <v>0.969</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6225,39 +6237,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="E128" s="17" t="n">
-        <v>-0.0091</v>
+        <v>0.31</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>753000</v>
+        <v>1354400</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="H128" t="n">
-        <v>47.81</v>
-      </c>
-      <c r="I128" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.6</v>
+      </c>
+      <c r="I128" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>2.218</v>
+        <v>0.318</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>2.11</v>
+        <v>0.337</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6270,39 +6282,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>749900</v>
+        <v>1347100</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="H129" t="n">
-        <v>41.02</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.95</v>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.99</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.008</v>
+        <v>0.575</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6315,28 +6327,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>712600</v>
+        <v>1323600</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.14</v>
+        <v>0.46</v>
       </c>
       <c r="H130" t="n">
-        <v>33.4</v>
+        <v>52.42</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -6344,10 +6356,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.629</v>
+        <v>0.464</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.656</v>
+        <v>0.461</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6360,28 +6372,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E131" s="17" t="n">
-        <v>-0.0159</v>
+        <v>1.04</v>
+      </c>
+      <c r="E131" s="15" t="n">
+        <v>0.0297</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>710000</v>
+        <v>1259500</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H131" t="n">
-        <v>36.72</v>
+        <v>52.53</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6389,10 +6401,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.63</v>
+        <v>1.029</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.636</v>
+        <v>1.013</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6405,28 +6417,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>1.71</v>
+        <v>0.68</v>
       </c>
       <c r="E132" s="15" t="n">
-        <v>0.0179</v>
+        <v>0.0149</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>684700</v>
+        <v>1254700</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="H132" t="n">
-        <v>51.07</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="I132" s="16" t="inlineStr">
         <is>
@@ -6434,10 +6446,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>1.715</v>
+        <v>0.581</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1.627</v>
+        <v>0.501</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6450,28 +6462,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E133" s="10" t="n">
-        <v>0</v>
+        <v>0.245</v>
+      </c>
+      <c r="E133" s="17" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>668700</v>
+        <v>1251900</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.14</v>
+        <v>1.14</v>
       </c>
       <c r="H133" t="n">
-        <v>30.66</v>
+        <v>43.9</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6479,10 +6491,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>1.036</v>
+        <v>0.254</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>1.075</v>
+        <v>0.252</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6495,39 +6507,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0263</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>660500</v>
+        <v>1247800</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.48</v>
+        <v>2.33</v>
       </c>
       <c r="H134" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="I134" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.3</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.634</v>
+        <v>0.694</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.629</v>
+        <v>0.711</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6540,28 +6552,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ABMB</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>4.67</v>
+        <v>2.14</v>
       </c>
       <c r="E135" s="17" t="n">
-        <v>-0.0106</v>
+        <v>-0.0228</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>658800</v>
+        <v>1246100</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.5</v>
+        <v>0.16</v>
       </c>
       <c r="H135" t="n">
-        <v>32.68</v>
+        <v>45.85</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6569,10 +6581,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>4.829</v>
+        <v>2.215</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>4.834</v>
+        <v>2.109</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6585,28 +6597,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="E136" s="17" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>654800</v>
+        <v>1236800</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.14</v>
+        <v>6.47</v>
       </c>
       <c r="H136" t="n">
-        <v>35.9</v>
+        <v>38.76</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6614,10 +6626,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.943</v>
+        <v>0.308</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>2.067</v>
+        <v>0.319</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6630,40 +6642,36 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.45</v>
+        <v>0.275</v>
       </c>
       <c r="E137" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>643600</v>
+        <v>1225200</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>42.53</v>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J137" s="9" t="n">
-        <v>1.473</v>
-      </c>
-      <c r="K137" s="9" t="n">
-        <v>1.52</v>
-      </c>
+        <v>16.56</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n"/>
+      <c r="K137" s="9" t="n"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
     </row>
@@ -6675,28 +6683,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E138" s="15" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.76</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>633200</v>
+        <v>1209600</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="H138" t="n">
-        <v>49.28</v>
+        <v>36.15</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6704,10 +6712,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>1.028</v>
+        <v>0.789</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>1.013</v>
+        <v>0.842</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6720,39 +6728,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0</v>
+        <v>0.33</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>616400</v>
+        <v>1203500</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.31</v>
+        <v>0.62</v>
       </c>
       <c r="H139" t="n">
-        <v>70.84</v>
-      </c>
-      <c r="I139" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.85</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.363</v>
+        <v>0.35</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.328</v>
+        <v>0.321</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6765,28 +6773,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>-0.0067</v>
+        <v>0.23</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>615500</v>
+        <v>1199300</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H140" t="n">
-        <v>29.13</v>
+        <v>41.61</v>
       </c>
       <c r="I140" s="13" t="inlineStr">
         <is>
@@ -6794,10 +6802,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>1.547</v>
+        <v>0.239</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>1.662</v>
+        <v>0.243</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6810,39 +6818,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>AEONCR</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="E141" s="17" t="n">
-        <v>-0.0231</v>
+        <v>0.92</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>580900</v>
+        <v>1171300</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>1.64</v>
+        <v>0.63</v>
       </c>
       <c r="H141" t="n">
-        <v>26.31</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.71</v>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>5.366</v>
+        <v>0.909</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>5.548</v>
+        <v>0.795</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6855,28 +6863,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>TEKSENG</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E142" s="10" t="n">
-        <v>0</v>
+        <v>0.27</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>573000</v>
+        <v>1160700</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.33</v>
+        <v>1.53</v>
       </c>
       <c r="H142" t="n">
-        <v>78.84999999999999</v>
+        <v>56.39</v>
       </c>
       <c r="I142" s="16" t="inlineStr">
         <is>
@@ -6884,10 +6892,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.58</v>
+        <v>0.262</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.5</v>
+        <v>0.243</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6900,39 +6908,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E143" s="17" t="n">
-        <v>-0.0052</v>
+        <v>1.4</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>552900</v>
+        <v>1139200</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H143" t="n">
-        <v>29.04</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.84</v>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.973</v>
+        <v>1.363</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>1.007</v>
+        <v>1.328</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6945,39 +6953,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>HLBANK</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.715</v>
+        <v>23.4</v>
       </c>
       <c r="E144" s="15" t="n">
-        <v>0.0142</v>
+        <v>0.0052</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>545700</v>
+        <v>1119200</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.32</v>
+        <v>1.67</v>
       </c>
       <c r="H144" t="n">
-        <v>40.98</v>
-      </c>
-      <c r="I144" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.45</v>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.731</v>
+        <v>23.234</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.751</v>
+        <v>22.902</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6990,39 +6998,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E145" s="17" t="n">
-        <v>-0.0153</v>
+        <v>0.425</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>524700</v>
+        <v>1101600</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.13</v>
+        <v>0.95</v>
       </c>
       <c r="H145" t="n">
-        <v>57.01</v>
-      </c>
-      <c r="I145" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.37</v>
+      </c>
+      <c r="I145" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>1.249</v>
+        <v>0.43</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>1.151</v>
+        <v>0.451</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7035,39 +7043,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>1.94</v>
+        <v>0.295</v>
       </c>
       <c r="E146" s="17" t="n">
-        <v>-0.0051</v>
+        <v>-0.0167</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>512000</v>
+        <v>1097700</v>
       </c>
       <c r="G146" s="12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H146" t="n">
-        <v>44.03</v>
-      </c>
-      <c r="I146" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.45</v>
+      </c>
+      <c r="I146" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.976</v>
+        <v>0.286</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.972</v>
+        <v>0.278</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7080,39 +7088,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E147" s="17" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>510200</v>
+        <v>1079900</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.44</v>
+        <v>0.29</v>
       </c>
       <c r="H147" t="n">
-        <v>32.52</v>
-      </c>
-      <c r="I147" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.59</v>
+      </c>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.141</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>1.178</v>
+        <v>0.593</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7125,39 +7133,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E148" s="15" t="n">
-        <v>0.03</v>
+        <v>1.35</v>
+      </c>
+      <c r="E148" s="17" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>506000</v>
+        <v>1040200</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.89</v>
+        <v>0.32</v>
       </c>
       <c r="H148" t="n">
-        <v>70.42</v>
-      </c>
-      <c r="I148" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.57</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.988</v>
+        <v>1.348</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.976</v>
+        <v>1.169</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7170,28 +7178,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E149" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.53</v>
+      </c>
+      <c r="E149" s="17" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>505800</v>
+        <v>1037600</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="H149" t="n">
-        <v>35.22</v>
+        <v>34.14</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -7199,16 +7207,1636 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>1.106</v>
+        <v>0.555</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>1.146</v>
+        <v>0.586</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>1028000</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H150" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>1.889</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>1.956</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>1005700</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H151" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>1.146</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E152" s="17" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>1000400</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H152" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E153" s="17" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>974500</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H153" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>969400</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H154" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E155" s="17" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>956000</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H155" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>2.068</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>952900</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H156" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2488</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ABMB</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>919300</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H157" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>4.834</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E158" s="17" t="n">
+        <v>-0.0305</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>916400</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H158" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0388</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SEMICO</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E159" s="17" t="n">
+        <v>-0.008100000000000001</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>911200</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H159" t="n">
+        <v>61.04</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>5139</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AEONCR</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="E160" s="17" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>884100</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H160" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>5.365</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>5.548</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>7095</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>PIE</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E161" s="15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>862300</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H161" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="I161" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>1.713</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>1.627</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E162" s="15" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>823500</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H162" t="n">
+        <v>43.28</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>756900</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H163" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>1.662</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>756900</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H164" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E165" s="17" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>728700</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H165" t="n">
+        <v>33.37</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>2.776</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>720500</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H166" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>DRBHCOM</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E167" s="17" t="n">
+        <v>-0.0107</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>716700</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H167" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E168" s="17" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>710000</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H168" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E169" s="15" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>707700</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H169" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="I169" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>1.521</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>686000</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H170" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="I170" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>1.472</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>1.472</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="E171" s="15" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>676300</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H171" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>6.277</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>6.472</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>666300</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H172" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>1.178</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>657300</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H173" t="n">
+        <v>56.03</v>
+      </c>
+      <c r="I173" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>6.618</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>6.534</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E174" s="17" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>653900</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H174" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="I174" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E175" s="17" t="n">
+        <v>-0.0201</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H175" t="n">
+        <v>85.09</v>
+      </c>
+      <c r="I175" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E176" s="17" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>611500</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H176" t="n">
+        <v>44.22</v>
+      </c>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>1.628</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>1.686</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>6599</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>AEON</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E177" s="17" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>589600</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H177" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="I177" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="E178" s="17" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>580800</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H178" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>5.255</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>5.279</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E179" s="17" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>577800</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H179" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="I179" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="E180" s="17" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>547300</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H180" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="I180" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>9.606</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>9.148</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E181" s="17" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>544800</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H181" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="I181" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>2.796</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>2.706</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="E182" s="17" t="n">
+        <v>-0.004699999999999999</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>543500</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H182" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>6.674</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>6.873</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>MCEMENT</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E183" s="15" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>538900</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H183" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="I183" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>5.632</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>6.047</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E184" s="17" t="n">
+        <v>-0.0362</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>515700</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H184" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="I184" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>506200</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H185" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="I185" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M149"/>
+  <autoFilter ref="A1:M185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
+++ b/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-30'!$A$1:$M$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.45略高于50日均线0.436，RSI 53.82处中性区间，无超买迹象，EMA信号可靠性偏中性。</t>
+          <t>现价0.45略高于50日均线0.436，RSI 53.82处中性区间，无超买迹象，EMA信号技术面偏温和。</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>148015600</v>
+        <v>148050300</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>0.26</v>
@@ -776,10 +776,10 @@
         <v>0.0851</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>102619500</v>
+        <v>103321400</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>5.27</v>
+        <v>5.31</v>
       </c>
       <c r="H6" t="n">
         <v>63.19</v>
@@ -821,10 +821,10 @@
         <v>0.04019999999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>37215700</v>
+        <v>37561800</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H7" t="n">
         <v>75.89</v>
@@ -866,7 +866,7 @@
         <v>0.0625</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>30341600</v>
+        <v>30366000</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>1.3</v>
@@ -911,10 +911,10 @@
         <v>0.0263</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>27915100</v>
+        <v>29415100</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="H9" t="n">
         <v>80.31999999999999</v>
@@ -1001,10 +1001,10 @@
         <v>-0.008399999999999999</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>22408300</v>
+        <v>22510300</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="H11" t="n">
         <v>69.39</v>
@@ -1040,19 +1040,19 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.0068</v>
+        <v>0.735</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14634800</v>
+        <v>15581600</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H12" t="n">
-        <v>53.23</v>
+        <v>52.16</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         <v>-0.004</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>14531300</v>
+        <v>14562500</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="H13" t="n">
         <v>59.66</v>
@@ -1130,19 +1130,19 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>-0.1521</v>
+        <v>-0.1475</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>12821200</v>
+        <v>12858100</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>1.06</v>
       </c>
       <c r="H14" t="n">
-        <v>56.82</v>
+        <v>57.27</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>3.609</v>
+        <v>3.611</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>2.46</v>
@@ -1175,19 +1175,19 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.51</v>
+        <v>0.515</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>-0.08109999999999999</v>
+        <v>-0.0721</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>12716100</v>
+        <v>12722100</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>45.42</v>
+        <v>46.92</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.523</v>
+        <v>0.524</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0.532</v>
@@ -1226,10 +1226,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>12346800</v>
+        <v>12579800</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="H16" t="n">
         <v>45.92</v>
@@ -1406,10 +1406,10 @@
         <v>-0.0319</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>10673200</v>
+        <v>10809000</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H20" t="n">
         <v>53.57</v>
@@ -1481,28 +1481,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.215</v>
+        <v>0.53</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>0.0488</v>
+        <v>0.0392</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>9603700</v>
+        <v>9734300</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
       <c r="H22" t="n">
-        <v>35.23</v>
+        <v>29.77</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.233</v>
+        <v>0.613</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.247</v>
+        <v>0.827</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1526,28 +1526,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>-0.1</v>
+        <v>0.215</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.0488</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9460800</v>
+        <v>9618400</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.95</v>
+        <v>0.39</v>
       </c>
       <c r="H23" t="n">
-        <v>42.47</v>
+        <v>35.23</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.052</v>
+        <v>0.233</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.044</v>
+        <v>0.247</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1571,39 +1571,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.77</v>
+        <v>0.045</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>9164600</v>
+        <v>9460800</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="H24" t="n">
-        <v>48.13</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.47</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.773</v>
+        <v>0.052</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.774</v>
+        <v>0.044</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         <v>-0.005699999999999999</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>9028400</v>
+        <v>9388300</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="H25" t="n">
         <v>46.81</v>
@@ -1661,39 +1661,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>8984000</v>
+        <v>9164600</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.38</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>55.27</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.13</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.203</v>
+        <v>0.773</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.186</v>
+        <v>0.774</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1706,28 +1706,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.78</v>
+        <v>0.385</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>-0.0127</v>
+        <v>-0.0128</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>8922000</v>
+        <v>9023500</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>2.06</v>
+        <v>0.19</v>
       </c>
       <c r="H27" t="n">
-        <v>42.88</v>
+        <v>75.87</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.8</v>
+        <v>0.332</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.806</v>
+        <v>0.197</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1751,39 +1751,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.0208</v>
+        <v>0.205</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>8899300</v>
+        <v>8984000</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="H28" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.27</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.27</v>
+        <v>0.203</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.322</v>
+        <v>0.186</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1796,39 +1796,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.0392</v>
+        <v>0.78</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8465100</v>
+        <v>8942300</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.22</v>
+        <v>2.07</v>
       </c>
       <c r="H29" t="n">
-        <v>29.77</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.88</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.613</v>
+        <v>0.8</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.827</v>
+        <v>0.806</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1841,39 +1841,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
+        <v>0.245</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>8025000</v>
+        <v>8919300</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="H30" t="n">
-        <v>50.19</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.57</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1886,39 +1886,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.0106</v>
+        <v>0.39</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7888000</v>
+        <v>8123100</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H31" t="n">
-        <v>52.83</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.3</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.469</v>
+        <v>0.383</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.472</v>
+        <v>0.325</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1931,28 +1931,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>-0.012</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>7435800</v>
+        <v>8025000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>44.57</v>
+        <v>50.19</v>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.57</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>2.451</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1976,39 +1976,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.395</v>
+        <v>0.475</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>0.0128</v>
+        <v>0.0106</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7391400</v>
+        <v>7888000</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0.33</v>
       </c>
       <c r="H33" t="n">
-        <v>56.49</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.83</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.383</v>
+        <v>0.469</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.325</v>
+        <v>0.472</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2021,28 +2021,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.4</v>
+        <v>2.48</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>-0.0244</v>
+        <v>-0.012</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>7091500</v>
+        <v>7472400</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.63</v>
+        <v>0.37</v>
       </c>
       <c r="H34" t="n">
-        <v>42.46</v>
+        <v>44.57</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.408</v>
+        <v>2.57</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.411</v>
+        <v>2.451</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2066,28 +2066,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>-0.0435</v>
+        <v>-0.0244</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>7012600</v>
+        <v>7207300</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.84</v>
+        <v>0.64</v>
       </c>
       <c r="H35" t="n">
-        <v>37.36</v>
+        <v>42.46</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.121</v>
+        <v>0.408</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.124</v>
+        <v>0.411</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2111,39 +2111,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0</v>
+        <v>0.11</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6649200</v>
+        <v>7012600</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.14</v>
+        <v>0.84</v>
       </c>
       <c r="H36" t="n">
-        <v>78.19</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.36</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.332</v>
+        <v>0.121</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.197</v>
+        <v>0.124</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         <v>0.011</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>6516300</v>
+        <v>6519300</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>0.88</v>
@@ -2246,33 +2246,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.0192</v>
+        <v>1.76</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>6455800</v>
+        <v>6489400</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.43</v>
+        <v>0.27</v>
+      </c>
+      <c r="H39" t="n">
+        <v>55.26</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
+      <c r="J39" s="9" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>1.55</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
     </row>
@@ -2284,40 +2291,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>-0.0135</v>
+        <v>0.265</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>6281000</v>
+        <v>6455800</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H40" t="n">
-        <v>64.36</v>
+        <v>0.43</v>
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J40" s="9" t="n">
-        <v>2.683</v>
-      </c>
-      <c r="K40" s="9" t="n">
-        <v>2.522</v>
-      </c>
+      <c r="J40" s="9" t="n"/>
+      <c r="K40" s="9" t="n"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
     </row>
@@ -2329,28 +2329,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1.75</v>
+        <v>2.93</v>
       </c>
       <c r="E41" s="17" t="n">
-        <v>-0.0223</v>
+        <v>-0.0135</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>6102100</v>
+        <v>6319500</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.25</v>
+        <v>0.72</v>
       </c>
       <c r="H41" t="n">
-        <v>54.37</v>
+        <v>64.36</v>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1.741</v>
+        <v>2.683</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1.55</v>
+        <v>2.522</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2592,28 +2592,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>0.0076</v>
+        <v>0.15</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5078900</v>
+        <v>5119900</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.53</v>
+        <v>0.12</v>
       </c>
       <c r="H47" t="n">
-        <v>58.87</v>
+        <v>47.65</v>
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.636</v>
+        <v>0.157</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.58</v>
+        <v>0.148</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2637,39 +2637,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>-0.0172</v>
+        <v>10.04</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.005</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>5069900</v>
+        <v>5086900</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="H48" t="n">
-        <v>61.57</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.82</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.533</v>
+        <v>10.147</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.485</v>
+        <v>10.294</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2682,39 +2682,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>10.04</v>
+        <v>0.66</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>0.005</v>
+        <v>0.0076</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5038100</v>
+        <v>5086200</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="H49" t="n">
-        <v>40.82</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.87</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>10.147</v>
+        <v>0.636</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>10.294</v>
+        <v>0.58</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2727,28 +2727,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>-0.0164</v>
+        <v>-0.0172</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>5000300</v>
+        <v>5069900</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="H50" t="n">
-        <v>46.01</v>
+        <v>61.57</v>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.607</v>
+        <v>0.533</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.606</v>
+        <v>0.485</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2772,28 +2772,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>0.0333</v>
+        <v>0.6</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4944300</v>
+        <v>5000300</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.12</v>
+        <v>0.48</v>
       </c>
       <c r="H51" t="n">
-        <v>50.05</v>
+        <v>46.01</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
@@ -2801,10 +2801,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.157</v>
+        <v>0.607</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.148</v>
+        <v>0.606</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2826,19 +2826,19 @@
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="E52" s="17" t="n">
-        <v>-0.0444</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4613100</v>
+        <v>4614100</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0.37</v>
       </c>
       <c r="H52" t="n">
-        <v>43.26</v>
+        <v>44.18</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>1.361</v>
+        <v>1.362</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>1.296</v>
@@ -2877,7 +2877,7 @@
         <v>0.0026</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4545400</v>
+        <v>4563700</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0.35</v>
@@ -2967,7 +2967,7 @@
         <v>-0.0196</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4473000</v>
+        <v>4511300</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>0.71</v>
@@ -3012,7 +3012,7 @@
         <v>-0.019</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4376800</v>
+        <v>4386900</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>0.39</v>
@@ -3057,7 +3057,7 @@
         <v>-0.0058</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4318900</v>
+        <v>4323900</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0.77</v>
@@ -3132,28 +3132,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0</v>
+        <v>0.795</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3696300</v>
+        <v>3854400</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="H59" t="n">
-        <v>66.27</v>
+        <v>62.67</v>
       </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.278</v>
+        <v>0.727</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.271</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3177,28 +3177,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.0806</v>
+        <v>0.295</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3609700</v>
+        <v>3696300</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>1.31</v>
+        <v>0.57</v>
       </c>
       <c r="H60" t="n">
-        <v>84.04000000000001</v>
+        <v>66.27</v>
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>1.09</v>
+        <v>0.278</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.913</v>
+        <v>0.271</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3222,28 +3222,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>-0.0247</v>
+        <v>1.34</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0.0806</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3434200</v>
+        <v>3614700</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.31</v>
+        <v>1.32</v>
       </c>
       <c r="H61" t="n">
-        <v>61.74</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.727</v>
+        <v>1.09</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.913</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3267,39 +3267,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.55</v>
+        <v>4.43</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>-0.0064</v>
+        <v>-0.0134</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3431800</v>
+        <v>3560400</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.99</v>
+        <v>0.59</v>
       </c>
       <c r="H62" t="n">
-        <v>40.52</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.89</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.578</v>
+        <v>3.71</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.642</v>
+        <v>3.283</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3312,39 +3312,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.25</v>
+        <v>1.55</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>-0.0196</v>
+        <v>-0.0064</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3383600</v>
+        <v>3442300</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>37.16</v>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.52</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.268</v>
+        <v>1.578</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.311</v>
+        <v>1.642</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3357,39 +3357,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>-0.0156</v>
+        <v>1.23</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0.025</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3363500</v>
+        <v>3417800</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H64" t="n">
-        <v>80.33</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.8</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>3.709</v>
+        <v>1.263</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>3.283</v>
+        <v>1.3</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3402,39 +3402,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E65" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.25</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3359600</v>
+        <v>3383600</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.63</v>
+        <v>0.29</v>
       </c>
       <c r="H65" t="n">
-        <v>38.27</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.16</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.262</v>
+        <v>0.268</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.3</v>
+        <v>0.311</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3447,39 +3447,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>4.71</v>
+        <v>0.88</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>-0.0021</v>
+        <v>-0.0638</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3293700</v>
+        <v>3344800</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.18</v>
+        <v>0.7</v>
       </c>
       <c r="H66" t="n">
-        <v>32.42</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.9</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>4.822</v>
+        <v>0.888</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>4.945</v>
+        <v>0.852</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3492,39 +3492,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.885</v>
+        <v>4.71</v>
       </c>
       <c r="E67" s="17" t="n">
-        <v>-0.0585</v>
+        <v>-0.0021</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3272000</v>
+        <v>3301300</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.68</v>
+        <v>0.18</v>
       </c>
       <c r="H67" t="n">
-        <v>51.27</v>
-      </c>
-      <c r="I67" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.42</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.889</v>
+        <v>4.822</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.852</v>
+        <v>4.945</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3552,7 +3552,7 @@
         <v>0.0309</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3237600</v>
+        <v>3241600</v>
       </c>
       <c r="G68" s="12" t="n">
         <v>0.49</v>
@@ -3591,19 +3591,19 @@
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="E69" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0044</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3214100</v>
+        <v>3221200</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>0.19</v>
       </c>
       <c r="H69" t="n">
-        <v>48.57</v>
+        <v>47.79</v>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>2.339</v>
+        <v>2.338</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>2.251</v>
+        <v>2.25</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3627,28 +3627,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0.0183</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3107200</v>
+        <v>3180900</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="H70" t="n">
-        <v>43.06</v>
+        <v>76.28</v>
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>1.17</v>
+        <v>1.021</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1.148</v>
+        <v>0.861</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3672,28 +3672,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>0.0092</v>
+        <v>0.0089</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3080900</v>
+        <v>3107800</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="H71" t="n">
-        <v>75.29000000000001</v>
+        <v>44.53</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>1.02</v>
+        <v>1.171</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.861</v>
+        <v>1.148</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3717,39 +3717,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>7.56</v>
+        <v>13.06</v>
       </c>
       <c r="E72" s="15" t="n">
-        <v>0.0027</v>
+        <v>0.0267</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2971000</v>
+        <v>3049900</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="H72" t="n">
-        <v>28.35</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.58</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>7.899</v>
+        <v>13.154</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>8.231999999999999</v>
+        <v>13.741</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3762,28 +3762,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>-0.0217</v>
+        <v>2.93</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.0103</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2954500</v>
+        <v>2987000</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.78</v>
+        <v>0.2</v>
       </c>
       <c r="H73" t="n">
-        <v>65.48999999999999</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.206</v>
+        <v>2.793</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.181</v>
+        <v>2.649</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3807,39 +3807,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2.92</v>
+        <v>7.56</v>
       </c>
       <c r="E74" s="15" t="n">
-        <v>0.0069</v>
+        <v>0.0027</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2950300</v>
+        <v>2984400</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="H74" t="n">
-        <v>68.58</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.35</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>2.792</v>
+        <v>7.899</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>2.649</v>
+        <v>8.231999999999999</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3852,28 +3852,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.225</v>
       </c>
       <c r="E75" s="17" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0217</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2878100</v>
+        <v>2954500</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.19</v>
+        <v>0.78</v>
       </c>
       <c r="H75" t="n">
-        <v>70.89</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="I75" s="16" t="inlineStr">
         <is>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.492</v>
+        <v>0.206</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.41</v>
+        <v>0.181</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3897,39 +3897,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2789500</v>
+        <v>2878100</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.88</v>
+        <v>0.19</v>
       </c>
       <c r="H76" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.89</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>3.273</v>
+        <v>0.492</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>3.465</v>
+        <v>0.41</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3942,39 +3942,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>0.0252</v>
+        <v>3.15</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2775200</v>
+        <v>2818100</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.33</v>
+        <v>0.89</v>
       </c>
       <c r="H77" t="n">
-        <v>41.84</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.3</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>13.152</v>
+        <v>3.273</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>13.74</v>
+        <v>3.465</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -4002,7 +4002,7 @@
         <v>0.0054</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2725500</v>
+        <v>2726700</v>
       </c>
       <c r="G78" s="12" t="n">
         <v>0.8100000000000001</v>
@@ -4122,28 +4122,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0.0036</v>
+        <v>0.675</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2600300</v>
+        <v>2602300</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.54</v>
+        <v>0.33</v>
       </c>
       <c r="H81" t="n">
-        <v>83.48999999999999</v>
+        <v>49.14</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>2.516</v>
+        <v>0.681</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>2.161</v>
+        <v>0.665</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4167,28 +4167,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>YXPM</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E82" s="17" t="n">
-        <v>-0.0444</v>
+        <v>2.77</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2574500</v>
+        <v>2600300</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>4.98</v>
+        <v>0.54</v>
       </c>
       <c r="H82" t="n">
-        <v>49.65</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.216</v>
+        <v>2.516</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.214</v>
+        <v>2.161</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4212,28 +4212,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>YXPM</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>3.06</v>
+        <v>0.215</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>-0.0377</v>
+        <v>-0.0444</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2566700</v>
+        <v>2574500</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.87</v>
+        <v>4.98</v>
       </c>
       <c r="H83" t="n">
-        <v>83.58</v>
+        <v>49.65</v>
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>2.356</v>
+        <v>0.216</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.835</v>
+        <v>0.214</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4257,28 +4257,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>0.0201</v>
+        <v>3.06</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>-0.0377</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2525600</v>
+        <v>2570500</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.7</v>
+        <v>0.87</v>
       </c>
       <c r="H84" t="n">
-        <v>59.37</v>
+        <v>83.58</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>2.89</v>
+        <v>2.356</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>2.7</v>
+        <v>1.835</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4311,19 +4311,19 @@
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>-0.009399999999999999</v>
+        <v>1.07</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2524800</v>
+        <v>2554300</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>0.31</v>
       </c>
       <c r="H85" t="n">
-        <v>75.19</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.921</v>
+        <v>0.923</v>
       </c>
       <c r="K85" s="9" t="n">
         <v>0.775</v>
@@ -4347,28 +4347,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>-0.0217</v>
+        <v>3.05</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>0.0201</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2514300</v>
+        <v>2529900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.32</v>
+        <v>0.7</v>
       </c>
       <c r="H86" t="n">
-        <v>49.14</v>
+        <v>59.37</v>
       </c>
       <c r="I86" s="16" t="inlineStr">
         <is>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.681</v>
+        <v>2.89</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.665</v>
+        <v>2.7</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4482,28 +4482,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>0.0049</v>
+        <v>0.29</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2211300</v>
+        <v>2232300</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="H89" t="n">
-        <v>47.99</v>
+        <v>39.08</v>
       </c>
       <c r="I89" s="16" t="inlineStr">
         <is>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>2.062</v>
+        <v>0.296</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>2.102</v>
+        <v>0.311</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4527,28 +4527,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.29</v>
+        <v>2.05</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2199300</v>
+        <v>2211600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H90" t="n">
-        <v>39.08</v>
+        <v>45.9</v>
       </c>
       <c r="I90" s="16" t="inlineStr">
         <is>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.296</v>
+        <v>2.061</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.311</v>
+        <v>2.101</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4581,19 +4581,19 @@
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>0.0251</v>
+        <v>0.0228</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2178300</v>
+        <v>2187200</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>0.44</v>
       </c>
       <c r="H91" t="n">
-        <v>36.64</v>
+        <v>35.96</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>4.672</v>
+        <v>4.671</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>4.96</v>
@@ -4632,10 +4632,10 @@
         <v>0.0238</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2148000</v>
+        <v>2165500</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H92" t="n">
         <v>58.16</v>
@@ -4662,28 +4662,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>-0.0178</v>
+        <v>7.91</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2141100</v>
+        <v>2150500</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="H93" t="n">
-        <v>59.93</v>
+        <v>49.03</v>
       </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>7.894</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.729</v>
+        <v>8.074</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4707,28 +4707,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>0.0051</v>
+        <v>0.83</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>-0.0178</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2119500</v>
+        <v>2141100</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H94" t="n">
-        <v>49.03</v>
+        <v>59.93</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>7.894</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>8.074</v>
+        <v>0.729</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4761,19 +4761,19 @@
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E95" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>1.15</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2074300</v>
+        <v>2075500</v>
       </c>
       <c r="G95" s="12" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>61.75</v>
+        <v>60.43</v>
       </c>
       <c r="I95" s="16" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.116</v>
+        <v>1.115</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>1.021</v>
@@ -4812,7 +4812,7 @@
         <v>-0.005699999999999999</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2022300</v>
+        <v>2027600</v>
       </c>
       <c r="G96" s="12" t="n">
         <v>0.65</v>
@@ -4851,19 +4851,19 @@
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0</v>
+        <v>1.94</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1946200</v>
+        <v>1962400</v>
       </c>
       <c r="G97" s="12" t="n">
         <v>0.26</v>
       </c>
       <c r="H97" t="n">
-        <v>45.43</v>
+        <v>44.03</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.977</v>
+        <v>1.976</v>
       </c>
       <c r="K97" s="9" t="n">
         <v>1.972</v>
@@ -4887,28 +4887,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>-0.0128</v>
+        <v>1.3</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1907000</v>
+        <v>1950900</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="H98" t="n">
-        <v>72.39</v>
+        <v>40.64</v>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.323</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.625</v>
+        <v>1.43</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4932,39 +4932,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="E99" s="15" t="n">
-        <v>0.0156</v>
+        <v>0.0159</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1902300</v>
+        <v>1913100</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.16</v>
+        <v>0.66</v>
       </c>
       <c r="H99" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.98</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.323</v>
+        <v>1.376</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.43</v>
+        <v>1.318</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4977,39 +4977,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>-0.0163</v>
+        <v>0.78</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1833300</v>
+        <v>1907100</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H100" t="n">
-        <v>35.81</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.67</v>
+      </c>
+      <c r="I100" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.928</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.947</v>
+        <v>0.625</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5022,28 +5022,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E101" s="15" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.905</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>-0.0163</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1819100</v>
+        <v>1833500</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.63</v>
+        <v>0.8</v>
       </c>
       <c r="H101" t="n">
-        <v>36.42</v>
+        <v>35.81</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.375</v>
+        <v>0.928</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1.317</v>
+        <v>0.947</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5082,7 +5082,7 @@
         <v>-0.0086</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1810600</v>
+        <v>1823100</v>
       </c>
       <c r="G102" s="12" t="n">
         <v>0.12</v>
@@ -5172,7 +5172,7 @@
         <v>-0.0092</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1737200</v>
+        <v>1746000</v>
       </c>
       <c r="G104" s="12" t="n">
         <v>0.35</v>
@@ -5202,28 +5202,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.585</v>
+        <v>0.34</v>
       </c>
       <c r="E105" s="17" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0145</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1674200</v>
+        <v>1713100</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="H105" t="n">
-        <v>32.29</v>
+        <v>38.45</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.628</v>
+        <v>0.35</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.656</v>
+        <v>0.35</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5247,28 +5247,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.25</v>
+        <v>0.585</v>
       </c>
       <c r="E106" s="17" t="n">
-        <v>-0.1228</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1666000</v>
+        <v>1674200</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="H106" t="n">
-        <v>48.47</v>
+        <v>32.29</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.264</v>
+        <v>0.628</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.223</v>
+        <v>0.656</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5292,28 +5292,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="E107" s="17" t="n">
-        <v>-0.0145</v>
+        <v>-0.1228</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1654600</v>
+        <v>1666000</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="H107" t="n">
-        <v>38.45</v>
+        <v>48.47</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.35</v>
+        <v>0.264</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.35</v>
+        <v>0.223</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         <v>-0.0167</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1613900</v>
+        <v>1629700</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="H108" t="n">
         <v>38.37</v>
@@ -5382,39 +5382,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.45</v>
+        <v>4.74</v>
       </c>
       <c r="E109" s="15" t="n">
-        <v>0.0227</v>
+        <v>0.0064</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1603600</v>
+        <v>1616300</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.51</v>
+        <v>0.18</v>
       </c>
       <c r="H109" t="n">
-        <v>54.28</v>
-      </c>
-      <c r="I109" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.79</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.437</v>
+        <v>4.738</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.452</v>
+        <v>4.597</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5427,39 +5427,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E110" s="17" t="n">
-        <v>-0.014</v>
+        <v>0.45</v>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1602900</v>
+        <v>1603600</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.2</v>
+        <v>0.51</v>
       </c>
       <c r="H110" t="n">
-        <v>39.78</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.28</v>
+      </c>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>4.524</v>
+        <v>0.437</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>4.521</v>
+        <v>0.452</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5472,28 +5472,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="E111" s="15" t="n">
-        <v>0.0064</v>
+        <v>4.23</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>-0.014</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1587900</v>
+        <v>1603600</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="H111" t="n">
-        <v>52.79</v>
+        <v>39.78</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>4.738</v>
+        <v>4.524</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>4.597</v>
+        <v>4.521</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5517,39 +5517,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.57</v>
+        <v>7.5</v>
       </c>
       <c r="E112" s="15" t="n">
-        <v>0.0364</v>
+        <v>0.0067</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1585100</v>
+        <v>1586500</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>2.44</v>
+        <v>0.22</v>
       </c>
       <c r="H112" t="n">
-        <v>75.72</v>
-      </c>
-      <c r="I112" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.52</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.535</v>
+        <v>7.651</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.528</v>
+        <v>7.828</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5562,39 +5562,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>7.5</v>
+        <v>0.57</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>0.0067</v>
+        <v>0.0364</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1580900</v>
+        <v>1585100</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.22</v>
+        <v>2.44</v>
       </c>
       <c r="H113" t="n">
-        <v>40.52</v>
-      </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.72</v>
+      </c>
+      <c r="I113" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>7.651</v>
+        <v>0.535</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>7.828</v>
+        <v>0.528</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         <v>-0.026</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1563300</v>
+        <v>1577000</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H114" t="n">
         <v>41.59</v>
@@ -5667,7 +5667,7 @@
         <v>-0.0089</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1551300</v>
+        <v>1559800</v>
       </c>
       <c r="G115" s="12" t="n">
         <v>0.17</v>
@@ -5802,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1508200</v>
+        <v>1508400</v>
       </c>
       <c r="G118" s="12" t="n">
         <v>0.18</v>
@@ -5847,7 +5847,7 @@
         <v>-0.0233</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1501200</v>
+        <v>1506200</v>
       </c>
       <c r="G119" s="12" t="n">
         <v>0.24</v>
@@ -5886,19 +5886,19 @@
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E120" s="17" t="n">
-        <v>-0.0102</v>
+        <v>0.49</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1475600</v>
+        <v>1478600</v>
       </c>
       <c r="G120" s="12" t="n">
         <v>0.48</v>
       </c>
       <c r="H120" t="n">
-        <v>68.22</v>
+        <v>71.12</v>
       </c>
       <c r="I120" s="16" t="inlineStr">
         <is>
@@ -5937,10 +5937,10 @@
         <v>0.0059</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1426400</v>
+        <v>1442200</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H121" t="n">
         <v>34.72</v>
@@ -5967,39 +5967,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>2.9</v>
+        <v>0.735</v>
       </c>
       <c r="E122" s="17" t="n">
-        <v>-0.0102</v>
+        <v>-0.0068</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1422400</v>
+        <v>1441100</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="H122" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.32</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>2.989</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>3.039</v>
+        <v>0.62</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6012,28 +6012,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.83</v>
+        <v>2.91</v>
       </c>
       <c r="E123" s="17" t="n">
-        <v>-0.006</v>
+        <v>-0.0068</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1404200</v>
+        <v>1433700</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.92</v>
+        <v>0.46</v>
       </c>
       <c r="H123" t="n">
-        <v>29.7</v>
+        <v>41.15</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.875</v>
+        <v>2.99</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.9429999999999999</v>
+        <v>3.039</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6057,39 +6057,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v>0.0068</v>
+        <v>0.83</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1401900</v>
+        <v>1404200</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.23</v>
+        <v>0.92</v>
       </c>
       <c r="H124" t="n">
-        <v>64.18000000000001</v>
-      </c>
-      <c r="I124" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.7</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.875</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.62</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6117,7 +6117,7 @@
         <v>-0.0053</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1400200</v>
+        <v>1401900</v>
       </c>
       <c r="G125" s="12" t="n">
         <v>0.31</v>
@@ -6207,7 +6207,7 @@
         <v>-0.0054</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1384700</v>
+        <v>1385700</v>
       </c>
       <c r="G127" s="12" t="n">
         <v>0.38</v>
@@ -6372,28 +6372,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E131" s="15" t="n">
-        <v>0.0297</v>
+        <v>0.3</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1259500</v>
+        <v>1317000</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.8</v>
+        <v>6.89</v>
       </c>
       <c r="H131" t="n">
-        <v>52.53</v>
+        <v>38.76</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>1.029</v>
+        <v>0.308</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.013</v>
+        <v>0.319</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6432,10 +6432,10 @@
         <v>0.0149</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1254700</v>
+        <v>1280500</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="H132" t="n">
         <v>79.84999999999999</v>
@@ -6462,28 +6462,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E133" s="17" t="n">
-        <v>-0.02</v>
+        <v>1.04</v>
+      </c>
+      <c r="E133" s="15" t="n">
+        <v>0.0297</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1251900</v>
+        <v>1259500</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>1.14</v>
+        <v>0.8</v>
       </c>
       <c r="H133" t="n">
-        <v>43.9</v>
+        <v>52.53</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.254</v>
+        <v>1.029</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.252</v>
+        <v>1.013</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6507,28 +6507,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0263</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.245</v>
       </c>
       <c r="E134" s="17" t="n">
-        <v>-0.0115</v>
+        <v>-0.02</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1247800</v>
+        <v>1251900</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>2.33</v>
+        <v>1.14</v>
       </c>
       <c r="H134" t="n">
-        <v>48.3</v>
+        <v>43.9</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.694</v>
+        <v>0.254</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.711</v>
+        <v>0.252</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6567,7 +6567,7 @@
         <v>-0.0228</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1246100</v>
+        <v>1250200</v>
       </c>
       <c r="G135" s="12" t="n">
         <v>0.16</v>
@@ -6597,28 +6597,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>0263</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.3</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E136" s="17" t="n">
-        <v>-0.0164</v>
+        <v>-0.0115</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1236800</v>
+        <v>1247800</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>6.47</v>
+        <v>2.33</v>
       </c>
       <c r="H136" t="n">
-        <v>38.76</v>
+        <v>48.3</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.308</v>
+        <v>0.694</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.319</v>
+        <v>0.711</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6698,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1209600</v>
+        <v>1212800</v>
       </c>
       <c r="G138" s="12" t="n">
         <v>0.27</v>
@@ -6827,19 +6827,19 @@
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>0</v>
+        <v>0.915</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1171300</v>
+        <v>1175500</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H141" t="n">
-        <v>55.71</v>
+        <v>54.82</v>
       </c>
       <c r="I141" s="16" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.909</v>
+        <v>0.908</v>
       </c>
       <c r="K141" s="9" t="n">
         <v>0.795</v>
@@ -6962,19 +6962,19 @@
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>23.4</v>
+        <v>23.38</v>
       </c>
       <c r="E144" s="15" t="n">
-        <v>0.0052</v>
+        <v>0.0043</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1119200</v>
+        <v>1119500</v>
       </c>
       <c r="G144" s="12" t="n">
         <v>1.67</v>
       </c>
       <c r="H144" t="n">
-        <v>54.45</v>
+        <v>54.1</v>
       </c>
       <c r="I144" s="16" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>23.234</v>
+        <v>23.232</v>
       </c>
       <c r="K144" s="9" t="n">
         <v>22.902</v>
@@ -7013,7 +7013,7 @@
         <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1101600</v>
+        <v>1102700</v>
       </c>
       <c r="G145" s="12" t="n">
         <v>0.95</v>
@@ -7103,7 +7103,7 @@
         <v>-0.0175</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1079900</v>
+        <v>1080200</v>
       </c>
       <c r="G147" s="12" t="n">
         <v>0.29</v>
@@ -7142,19 +7142,19 @@
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="E148" s="17" t="n">
-        <v>-0.0357</v>
+        <v>-0.0286</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1040200</v>
+        <v>1055600</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H148" t="n">
-        <v>53.57</v>
+        <v>54.62</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>1.348</v>
+        <v>1.349</v>
       </c>
       <c r="K148" s="9" t="n">
         <v>1.169</v>
@@ -7193,7 +7193,7 @@
         <v>-0.009300000000000001</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>1037600</v>
+        <v>1053200</v>
       </c>
       <c r="G149" s="12" t="n">
         <v>0.16</v>
@@ -7238,7 +7238,7 @@
         <v>0</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1028000</v>
+        <v>1028100</v>
       </c>
       <c r="G150" s="12" t="n">
         <v>0.8</v>
@@ -7418,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>969400</v>
+        <v>972200</v>
       </c>
       <c r="G154" s="12" t="n">
         <v>0.52</v>
@@ -7463,7 +7463,7 @@
         <v>-0.014</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>956000</v>
+        <v>956100</v>
       </c>
       <c r="G155" s="12" t="n">
         <v>0.3</v>
@@ -7508,7 +7508,7 @@
         <v>0</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>952900</v>
+        <v>953000</v>
       </c>
       <c r="G156" s="12" t="n">
         <v>0.15</v>
@@ -7598,7 +7598,7 @@
         <v>-0.0305</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>916400</v>
+        <v>918500</v>
       </c>
       <c r="G158" s="12" t="n">
         <v>0.23</v>
@@ -7688,10 +7688,10 @@
         <v>-0.025</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>884100</v>
+        <v>891000</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="H160" t="n">
         <v>25.97</v>
@@ -7763,28 +7763,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E162" s="15" t="n">
-        <v>0.0213</v>
+        <v>1.09</v>
+      </c>
+      <c r="E162" s="17" t="n">
+        <v>-0.0091</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>823500</v>
+        <v>857700</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.49</v>
+        <v>0.74</v>
       </c>
       <c r="H162" t="n">
-        <v>43.28</v>
+        <v>30.54</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -7792,10 +7792,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>0.732</v>
+        <v>1.14</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>0.751</v>
+        <v>1.178</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7808,28 +7808,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>0</v>
+        <v>0.72</v>
+      </c>
+      <c r="E163" s="15" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>756900</v>
+        <v>825500</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.32</v>
+        <v>0.49</v>
       </c>
       <c r="H163" t="n">
-        <v>30.4</v>
+        <v>43.28</v>
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>1.548</v>
+        <v>0.732</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>1.662</v>
+        <v>0.751</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7853,28 +7853,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>0.975</v>
+        <v>1.49</v>
       </c>
       <c r="E164" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>756900</v>
+        <v>758800</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="H164" t="n">
-        <v>30.66</v>
+        <v>30.4</v>
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>1.036</v>
+        <v>1.548</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>1.075</v>
+        <v>1.662</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7898,28 +7898,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E165" s="17" t="n">
-        <v>-0.0115</v>
+        <v>0.975</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>728700</v>
+        <v>757400</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="H165" t="n">
-        <v>33.37</v>
+        <v>30.66</v>
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
@@ -7927,10 +7927,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>2.656</v>
+        <v>1.036</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>2.776</v>
+        <v>1.075</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7943,39 +7943,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>0</v>
+        <v>2.57</v>
+      </c>
+      <c r="E166" s="17" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>720500</v>
+        <v>728700</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.52</v>
+        <v>0.22</v>
       </c>
       <c r="H166" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="I166" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.37</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>0.634</v>
+        <v>2.656</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>0.629</v>
+        <v>2.776</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7988,39 +7988,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>DRBHCOM</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E167" s="17" t="n">
-        <v>-0.0107</v>
+        <v>0.635</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>716700</v>
+        <v>720500</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>1.44</v>
+        <v>0.52</v>
       </c>
       <c r="H167" t="n">
-        <v>37.45</v>
-      </c>
-      <c r="I167" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.65</v>
+      </c>
+      <c r="I167" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>0.951</v>
+        <v>0.634</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>0.962</v>
+        <v>0.629</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8033,28 +8033,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>DRBHCOM</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>0.62</v>
+        <v>0.925</v>
       </c>
       <c r="E168" s="17" t="n">
-        <v>-0.0159</v>
+        <v>-0.0107</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>710000</v>
+        <v>717400</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.7</v>
+        <v>1.45</v>
       </c>
       <c r="H168" t="n">
-        <v>36.72</v>
+        <v>37.45</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8062,10 +8062,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>0.63</v>
+        <v>0.951</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>0.636</v>
+        <v>0.962</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8078,28 +8078,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E169" s="15" t="n">
-        <v>0.0069</v>
+        <v>2.91</v>
+      </c>
+      <c r="E169" s="17" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>707700</v>
+        <v>713700</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="H169" t="n">
-        <v>44.92</v>
+        <v>84.23</v>
       </c>
       <c r="I169" s="16" t="inlineStr">
         <is>
@@ -8107,10 +8107,10 @@
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>1.474</v>
+        <v>2.377</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>1.521</v>
+        <v>1.997</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8123,39 +8123,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E170" s="10" t="n">
-        <v>0</v>
+        <v>0.62</v>
+      </c>
+      <c r="E170" s="17" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>686000</v>
+        <v>710000</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.13</v>
+        <v>0.7</v>
       </c>
       <c r="H170" t="n">
-        <v>50.09</v>
-      </c>
-      <c r="I170" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.72</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.472</v>
+        <v>0.63</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>1.472</v>
+        <v>0.636</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8168,39 +8168,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>6.18</v>
+        <v>1.46</v>
       </c>
       <c r="E171" s="15" t="n">
-        <v>0.0032</v>
+        <v>0.0069</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>676300</v>
+        <v>707700</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.04</v>
+        <v>0.27</v>
       </c>
       <c r="H171" t="n">
-        <v>39.97</v>
-      </c>
-      <c r="I171" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.92</v>
+      </c>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>6.277</v>
+        <v>1.474</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>6.472</v>
+        <v>1.521</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8213,39 +8213,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E172" s="17" t="n">
-        <v>-0.0091</v>
+        <v>1.47</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>666300</v>
+        <v>686200</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.57</v>
+        <v>0.13</v>
       </c>
       <c r="H172" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.09</v>
+      </c>
+      <c r="I172" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>1.14</v>
+        <v>1.472</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>1.178</v>
+        <v>1.472</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8258,39 +8258,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E173" s="10" t="n">
-        <v>0</v>
+        <v>6.18</v>
+      </c>
+      <c r="E173" s="15" t="n">
+        <v>0.0032</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>657300</v>
+        <v>677800</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="H173" t="n">
-        <v>56.03</v>
-      </c>
-      <c r="I173" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.97</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>6.618</v>
+        <v>6.277</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>6.534</v>
+        <v>6.472</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8303,28 +8303,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E174" s="17" t="n">
-        <v>-0.0192</v>
+        <v>6.8</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>653900</v>
+        <v>671900</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="H174" t="n">
-        <v>52.38</v>
+        <v>56.03</v>
       </c>
       <c r="I174" s="16" t="inlineStr">
         <is>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>0.758</v>
+        <v>6.618</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>0.741</v>
+        <v>6.534</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8348,28 +8348,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>2.92</v>
+        <v>0.765</v>
       </c>
       <c r="E175" s="17" t="n">
-        <v>-0.0201</v>
+        <v>-0.0192</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>650000</v>
+        <v>653900</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="H175" t="n">
-        <v>85.09</v>
+        <v>52.38</v>
       </c>
       <c r="I175" s="16" t="inlineStr">
         <is>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>2.378</v>
+        <v>0.758</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>1.997</v>
+        <v>0.741</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8393,28 +8393,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="E176" s="17" t="n">
-        <v>-0.0062</v>
+        <v>-0.0155</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>611500</v>
+        <v>611700</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="H176" t="n">
-        <v>44.22</v>
+        <v>46.38</v>
       </c>
       <c r="I176" s="16" t="inlineStr">
         <is>
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>1.628</v>
+        <v>1.28</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>1.686</v>
+        <v>1.337</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8438,39 +8438,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>0.95</v>
+        <v>1.6</v>
       </c>
       <c r="E177" s="17" t="n">
-        <v>-0.0052</v>
+        <v>-0.0062</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>589600</v>
+        <v>611500</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.65</v>
+        <v>0.37</v>
       </c>
       <c r="H177" t="n">
-        <v>29.04</v>
-      </c>
-      <c r="I177" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.22</v>
+      </c>
+      <c r="I177" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>0.973</v>
+        <v>1.628</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>1.007</v>
+        <v>1.686</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8483,28 +8483,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>5.12</v>
+        <v>0.95</v>
       </c>
       <c r="E178" s="17" t="n">
-        <v>-0.0116</v>
+        <v>-0.0052</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>580800</v>
+        <v>589600</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.23</v>
+        <v>0.65</v>
       </c>
       <c r="H178" t="n">
-        <v>45.16</v>
+        <v>29.04</v>
       </c>
       <c r="I178" s="13" t="inlineStr">
         <is>
@@ -8512,10 +8512,10 @@
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>5.255</v>
+        <v>0.973</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>5.279</v>
+        <v>1.007</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8528,39 +8528,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>1.27</v>
+        <v>5.12</v>
       </c>
       <c r="E179" s="17" t="n">
-        <v>-0.0155</v>
+        <v>-0.0116</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>577800</v>
+        <v>583000</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.36</v>
+        <v>0.23</v>
       </c>
       <c r="H179" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="I179" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.16</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>1.28</v>
+        <v>5.255</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>1.337</v>
+        <v>5.279</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8588,7 +8588,7 @@
         <v>-0.013</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>547300</v>
+        <v>548900</v>
       </c>
       <c r="G180" s="12" t="n">
         <v>0.16</v>
@@ -8627,19 +8627,19 @@
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="E181" s="17" t="n">
-        <v>-0.0105</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>544800</v>
+        <v>547000</v>
       </c>
       <c r="G181" s="12" t="n">
         <v>0.18</v>
       </c>
       <c r="H181" t="n">
-        <v>53.75</v>
+        <v>54.36</v>
       </c>
       <c r="I181" s="16" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>-0.004699999999999999</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>543500</v>
+        <v>543900</v>
       </c>
       <c r="G182" s="12" t="n">
         <v>0.12</v>
@@ -8723,10 +8723,10 @@
         <v>0.009300000000000001</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>538900</v>
+        <v>541100</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H183" t="n">
         <v>35.35</v>
@@ -8753,39 +8753,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E184" s="17" t="n">
-        <v>-0.0362</v>
+        <v>6.7</v>
+      </c>
+      <c r="E184" s="15" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>515700</v>
+        <v>539800</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="H184" t="n">
-        <v>48.34</v>
-      </c>
-      <c r="I184" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.14</v>
+      </c>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>0.673</v>
+        <v>6.76</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>0.675</v>
+        <v>6.822</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8798,28 +8798,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E185" s="10" t="n">
-        <v>0</v>
+        <v>0.665</v>
+      </c>
+      <c r="E185" s="17" t="n">
+        <v>-0.0362</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>506200</v>
+        <v>515700</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.89</v>
+        <v>0.45</v>
       </c>
       <c r="H185" t="n">
-        <v>60.52</v>
+        <v>48.34</v>
       </c>
       <c r="I185" s="16" t="inlineStr">
         <is>
@@ -8827,16 +8827,106 @@
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>0.985</v>
+        <v>0.673</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>0.976</v>
+        <v>0.675</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E186" s="15" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>510100</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H186" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>506200</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H187" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="I187" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M185"/>
+  <autoFilter ref="A1:M187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
+++ b/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
@@ -557,28 +557,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0118</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>TRIVE</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.02</v>
+        <v>0.345</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.3333</v>
+        <v>0.0455</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5612400</v>
+        <v>10315600</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>57.37</v>
+        <v>1.36</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>58.93</v>
+        <v>59.18</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.016</v>
+        <v>0.331</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.017</v>
+        <v>0.314</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,62 +598,54 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.02高于50日均线0.017，EMA信号偏多；RSI 58.93处中性偏强区间，未超买，信号可靠性中等。</t>
+          <t>现价0.345高于50日均线0.314，EMA信号偏多；RSI 59.18处中性偏强区间，未超买，信号可靠性中等。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>0457</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>PENTECH</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0.0455</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>10315600</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>🎯 EMA</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>现价0.345高于50日均线0.314，EMA信号偏多；RSI 59.18处中性偏强区间，未超买，信号可靠性中等。</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>190165500</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H3" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -663,39 +655,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0.0638</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>190165500</v>
+        <v>104040500</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.33</v>
+        <v>5.34</v>
       </c>
       <c r="H4" t="n">
-        <v>20.46</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.02</v>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.255</v>
+        <v>0.234</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.47</v>
+        <v>0.233</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -708,28 +700,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.25</v>
+        <v>5.18</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0638</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>104040500</v>
+        <v>39630600</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>5.34</v>
+        <v>2.09</v>
       </c>
       <c r="H5" t="n">
-        <v>61.02</v>
+        <v>75.89</v>
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
@@ -737,10 +729,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.234</v>
+        <v>4.807</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.233</v>
+        <v>4.546</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -753,28 +745,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>5.18</v>
+        <v>0.195</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.0263</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>39630600</v>
+        <v>31611600</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>2.09</v>
+        <v>0.63</v>
       </c>
       <c r="H6" t="n">
-        <v>75.89</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
@@ -782,10 +774,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>4.807</v>
+        <v>0.155</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>4.546</v>
+        <v>0.12</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -798,39 +790,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.195</v>
+        <v>0.165</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.0263</v>
+        <v>0.0313</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>31611600</v>
+        <v>30766900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.63</v>
+        <v>1.32</v>
       </c>
       <c r="H7" t="n">
-        <v>80.31999999999999</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.06</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.155</v>
+        <v>0.178</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.12</v>
+        <v>0.215</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -843,39 +835,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.165</v>
+        <v>0.51</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0.0313</v>
+        <v>0.2143</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>30766900</v>
+        <v>26239100</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1.32</v>
+        <v>18.1</v>
       </c>
       <c r="H8" t="n">
-        <v>36.06</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.29000000000001</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.178</v>
+        <v>0.417</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.215</v>
+        <v>0.412</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -888,28 +880,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.2143</v>
+        <v>0.59</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>26239100</v>
+        <v>23557400</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>18.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>76.29000000000001</v>
+        <v>69.39</v>
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
@@ -917,10 +909,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.417</v>
+        <v>0.555</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.412</v>
+        <v>0.495</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -933,39 +925,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.74</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>23557400</v>
+        <v>18117900</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>69.39</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.23</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.555</v>
+        <v>0.736</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.495</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -978,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.0068</v>
+        <v>0.155</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>18117900</v>
+        <v>15691300</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.4</v>
+        <v>0.66</v>
       </c>
       <c r="H11" t="n">
-        <v>53.23</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.736</v>
+        <v>0.156</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.159</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1023,28 +1015,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>2.49</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-0.004</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>15691300</v>
+        <v>14958800</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.66</v>
+        <v>0.93</v>
       </c>
       <c r="H12" t="n">
-        <v>44.73</v>
+        <v>59.66</v>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
@@ -1052,10 +1044,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.156</v>
+        <v>2.45</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.159</v>
+        <v>2.295</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1068,39 +1060,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2.49</v>
+        <v>3.77</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>-0.004</v>
+        <v>-0.1313</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>14958800</v>
+        <v>14695100</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="H13" t="n">
-        <v>59.66</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.88</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>2.45</v>
+        <v>3.618</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>2.295</v>
+        <v>2.462</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1113,28 +1105,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>-0.1313</v>
+        <v>0.21</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>14695100</v>
+        <v>14057000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.21</v>
+        <v>0.59</v>
       </c>
       <c r="H14" t="n">
-        <v>58.88</v>
+        <v>58.61</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1142,10 +1134,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>3.618</v>
+        <v>0.203</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>2.462</v>
+        <v>0.186</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1158,28 +1150,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.0244</v>
+        <v>0.51</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>-0.08109999999999999</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>14057000</v>
+        <v>13043300</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.59</v>
+        <v>2.05</v>
       </c>
       <c r="H15" t="n">
-        <v>58.61</v>
+        <v>45.42</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1187,10 +1179,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.203</v>
+        <v>0.523</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.186</v>
+        <v>0.532</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1203,28 +1195,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>-0.08109999999999999</v>
+        <v>2.09</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>13043300</v>
+        <v>13041200</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2.05</v>
+        <v>0.77</v>
       </c>
       <c r="H16" t="n">
-        <v>45.42</v>
+        <v>47.29</v>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
@@ -1232,10 +1224,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.523</v>
+        <v>2.119</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.532</v>
+        <v>2.067</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1248,39 +1240,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0.0048</v>
+        <v>0.38</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>13041200</v>
+        <v>12966600</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.77</v>
+        <v>0.27</v>
       </c>
       <c r="H17" t="n">
-        <v>47.29</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.68000000000001</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2.119</v>
+        <v>0.332</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2.067</v>
+        <v>0.196</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1293,28 +1285,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.38</v>
+        <v>0.865</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>-0.0256</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>12966600</v>
+        <v>12863600</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.27</v>
+        <v>0.68</v>
       </c>
       <c r="H18" t="n">
-        <v>73.68000000000001</v>
+        <v>46.81</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
@@ -1322,10 +1314,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.332</v>
+        <v>0.868</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.196</v>
+        <v>0.87</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1338,39 +1330,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.305</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>12863600</v>
+        <v>12223300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H19" t="n">
-        <v>46.81</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.62</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.868</v>
+        <v>0.303</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.87</v>
+        <v>0.291</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1383,28 +1375,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.05</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>12223300</v>
+        <v>12093400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="H20" t="n">
-        <v>53.62</v>
+        <v>35.15</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1412,10 +1404,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.303</v>
+        <v>0.058</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.291</v>
+        <v>0.076</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1428,28 +1420,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0051</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CUSCAPI</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>0.455</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>-0.0319</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>12093400</v>
+        <v>11403800</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.47</v>
+        <v>1.15</v>
       </c>
       <c r="H21" t="n">
-        <v>35.15</v>
+        <v>53.57</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1457,10 +1449,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.058</v>
+        <v>0.45</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.076</v>
+        <v>0.413</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1473,39 +1465,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0152</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>DGB</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>-0.0319</v>
+        <v>0.04</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>11403800</v>
+        <v>11113900</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1.15</v>
+        <v>160.02</v>
       </c>
       <c r="H22" t="n">
-        <v>53.57</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.06</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.45</v>
+        <v>0.035</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.413</v>
+        <v>0.035</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1518,39 +1510,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0152</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DGB</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>0.53</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>11113900</v>
+        <v>11073900</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>160.02</v>
+        <v>0.28</v>
       </c>
       <c r="H23" t="n">
-        <v>60.06</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.77</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.035</v>
+        <v>0.613</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.035</v>
+        <v>0.827</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1563,28 +1555,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.53</v>
+        <v>0.055</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.0392</v>
+        <v>0.1</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>11073900</v>
+        <v>10372300</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.28</v>
+        <v>1.04</v>
       </c>
       <c r="H24" t="n">
-        <v>29.77</v>
+        <v>55.65</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1592,10 +1584,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.613</v>
+        <v>0.053</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.827</v>
+        <v>0.044</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1608,28 +1600,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.055</v>
+        <v>0.215</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.1</v>
+        <v>0.0488</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>10372300</v>
+        <v>9926200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.04</v>
+        <v>0.4</v>
       </c>
       <c r="H25" t="n">
-        <v>55.65</v>
+        <v>35.23</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1637,10 +1629,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.053</v>
+        <v>0.233</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.044</v>
+        <v>0.247</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1653,39 +1645,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0.0488</v>
+        <v>0.765</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>9926200</v>
+        <v>9588000</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.4</v>
+        <v>0.72</v>
       </c>
       <c r="H26" t="n">
-        <v>35.23</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.233</v>
+        <v>0.773</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.247</v>
+        <v>0.774</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1698,28 +1690,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>-0.0129</v>
+        <v>0.245</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>9588000</v>
+        <v>9293400</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.72</v>
+        <v>0.32</v>
       </c>
       <c r="H27" t="n">
-        <v>46</v>
+        <v>33.57</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1727,10 +1719,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.773</v>
+        <v>0.27</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.774</v>
+        <v>0.322</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1743,39 +1735,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.0208</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>9293400</v>
+        <v>9185700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.32</v>
+        <v>0.64</v>
       </c>
       <c r="H28" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.19</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.27</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.322</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1788,28 +1780,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
+        <v>2.48</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>9185700</v>
+        <v>9180100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="H29" t="n">
-        <v>50.19</v>
+        <v>44.57</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1817,10 +1809,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.57</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>2.451</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1833,39 +1825,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2.48</v>
+        <v>0.78</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>-0.012</v>
+        <v>-0.0127</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>9180100</v>
+        <v>9144600</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.46</v>
+        <v>2.12</v>
       </c>
       <c r="H30" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.88</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>2.57</v>
+        <v>0.8</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>2.451</v>
+        <v>0.806</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1878,39 +1870,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>-0.0127</v>
+        <v>0.39</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>9144600</v>
+        <v>8391800</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>2.12</v>
+        <v>0.37</v>
       </c>
       <c r="H31" t="n">
-        <v>42.88</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.3</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.8</v>
+        <v>0.383</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.806</v>
+        <v>0.325</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1923,39 +1915,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>8391800</v>
+        <v>7937600</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="H32" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.68</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.383</v>
+        <v>0.469</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.325</v>
+        <v>0.472</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1968,39 +1960,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>0.0213</v>
+        <v>0.11</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7937600</v>
+        <v>7697700</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.33</v>
+        <v>0.93</v>
       </c>
       <c r="H33" t="n">
-        <v>54.68</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.36</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.469</v>
+        <v>0.121</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.472</v>
+        <v>0.124</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2013,39 +2005,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.11</v>
+        <v>0.385</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>-0.0435</v>
+        <v>-0.0253</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>7697700</v>
+        <v>7470400</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="H34" t="n">
-        <v>37.36</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.01</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.121</v>
+        <v>0.376</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.124</v>
+        <v>0.372</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2058,39 +2050,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.385</v>
+        <v>0.4</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>-0.0253</v>
+        <v>-0.0244</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>7470400</v>
+        <v>7313000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="H35" t="n">
-        <v>59.01</v>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.46</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.376</v>
+        <v>0.408</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.372</v>
+        <v>0.411</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2103,39 +2095,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.4</v>
+        <v>1.75</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>-0.0244</v>
+        <v>-0.0223</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7313000</v>
+        <v>7123800</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
       <c r="H36" t="n">
-        <v>42.46</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.37</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.408</v>
+        <v>1.741</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.411</v>
+        <v>1.55</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2148,28 +2140,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>1.75</v>
+        <v>2.92</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>-0.0223</v>
+        <v>-0.0168</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>7123800</v>
+        <v>6876100</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.3</v>
+        <v>0.79</v>
       </c>
       <c r="H37" t="n">
-        <v>54.37</v>
+        <v>63.76</v>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
@@ -2177,10 +2169,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.741</v>
+        <v>2.682</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.55</v>
+        <v>2.522</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2193,39 +2185,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>-0.0168</v>
+        <v>1.85</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.0165</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>6876100</v>
+        <v>6787400</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="H38" t="n">
-        <v>63.76</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.86</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>2.682</v>
+        <v>1.888</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>2.522</v>
+        <v>1.959</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2238,40 +2230,33 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.0165</v>
+        <v>0.26</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>6787400</v>
+        <v>6517700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H39" t="n">
-        <v>43.86</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>1.888</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>1.959</v>
-      </c>
+        <v>0.44</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
     </row>
@@ -2283,33 +2268,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.26</v>
+        <v>0.01</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>6517700</v>
+        <v>6452200</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
+        <v>8.99</v>
+      </c>
+      <c r="H40" t="n">
+        <v>53.43</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>0.007</v>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
     </row>
@@ -2321,39 +2313,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.01</v>
+        <v>0.655</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>6452200</v>
+        <v>6145100</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>8.99</v>
+        <v>0.64</v>
       </c>
       <c r="H41" t="n">
-        <v>53.43</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.9</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.636</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.007</v>
+        <v>0.58</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2366,28 +2358,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.655</v>
+        <v>0.035</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>6145100</v>
+        <v>6100700</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H42" t="n">
-        <v>57.9</v>
+        <v>53.89</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
@@ -2395,10 +2387,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.636</v>
+        <v>0.033</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.58</v>
+        <v>0.032</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2411,28 +2403,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0007</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PUC</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0</v>
+        <v>4.38</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>-0.0245</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>6100700</v>
+        <v>5974400</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.73</v>
+        <v>0.99</v>
       </c>
       <c r="H43" t="n">
-        <v>53.89</v>
+        <v>78.19</v>
       </c>
       <c r="I43" s="16" t="inlineStr">
         <is>
@@ -2440,10 +2432,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.033</v>
+        <v>3.706</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.032</v>
+        <v>3.282</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2456,39 +2448,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>-0.0245</v>
+        <v>10.04</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.005</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>5974400</v>
+        <v>5839500</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.99</v>
+        <v>0.47</v>
       </c>
       <c r="H44" t="n">
-        <v>78.19</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.82</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>3.706</v>
+        <v>10.147</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>3.282</v>
+        <v>10.294</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2501,40 +2493,33 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0.005</v>
+        <v>0.12</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>5839500</v>
+        <v>5795200</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H45" t="n">
-        <v>40.82</v>
+        <v>0.14</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J45" s="9" t="n">
-        <v>10.147</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>10.294</v>
-      </c>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
     </row>
@@ -2546,33 +2531,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>-0.04</v>
+        <v>0.44</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5795200</v>
+        <v>5672000</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J46" s="9" t="n"/>
-      <c r="K46" s="9" t="n"/>
+        <v>2.84</v>
+      </c>
+      <c r="H46" t="n">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>0.346</v>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
     </row>
@@ -2584,28 +2576,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0118</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>TRIVE</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.44</v>
+        <v>0.02</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.0476</v>
+        <v>0.3333</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5672000</v>
+        <v>5612400</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>2.84</v>
+        <v>57.37</v>
       </c>
       <c r="H47" t="n">
-        <v>75.29000000000001</v>
+        <v>58.93</v>
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
@@ -2613,10 +2605,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.381</v>
+        <v>0.016</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.346</v>
+        <v>0.017</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>

--- a/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
+++ b/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.345高于50日均线0.314，EMA信号偏多；RSI 59.18处中性偏强区间，未超买，信号可靠性中等。</t>
+          <t>现价0.345高于50日均线0.314，EMA信号偏多；RSI 59.18处中性偏强，未超买，信号可靠性中等。</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
+++ b/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.345高于50日均线0.314，EMA信号偏多；RSI 59.18处中性偏强，未超买，信号可靠性中等。</t>
+          <t>现价0.345高于50日均线0.314，EMA信号偏多；RSI 59.18处中性偏上，未超买，信号可靠性中等。</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
+++ b/docs/downloads/2026-09-30/bursa-report-2026-09-30.xlsx
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="4">
@@ -92,7 +92,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -572,10 +572,10 @@
         <v>0.0168</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>30866400</v>
+        <v>30987300</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>74.03</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，但RSI达74.03已超买，现价高于50日均线约22%，信号可靠性偏弱。</t>
+          <t>SAR转多，但RSI达74已超买，现价高于50日均线约22%，信号可靠性偏弱。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.165</v>
+        <v>0.16</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0</v>
+        <v>-0.0303</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>243276300</v>
+        <v>243512000</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>0.42</v>
       </c>
       <c r="H3" t="n">
-        <v>20.46</v>
+        <v>20.05</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -670,10 +670,10 @@
         <v>0.0851</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>114039500</v>
+        <v>114480200</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>5.86</v>
+        <v>5.88</v>
       </c>
       <c r="H4" t="n">
         <v>63.19</v>
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>5.15</v>
+        <v>5.16</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0341</v>
+        <v>0.0361</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>63187400</v>
+        <v>63439700</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="H5" t="n">
-        <v>75.06</v>
+        <v>75.34</v>
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>4.804</v>
+        <v>4.805</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>4.546</v>
@@ -760,10 +760,10 @@
         <v>0.0263</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>40303500</v>
+        <v>40403500</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>80.31999999999999</v>
@@ -805,7 +805,7 @@
         <v>0.0625</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>31399900</v>
+        <v>31410000</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>1.35</v>
@@ -835,40 +835,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>0.1905</v>
+        <v>0.005</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>28318100</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>19.54</v>
-      </c>
-      <c r="H8" t="n">
-        <v>75.03</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>0.412</v>
-      </c>
+        <v>28384600</v>
+      </c>
+      <c r="G8" s="12" t="n"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
     </row>
@@ -880,31 +871,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.1905</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>27784600</v>
-      </c>
-      <c r="G9" s="12" t="n"/>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
+        <v>28328100</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="H9" t="n">
+        <v>75.03</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.412</v>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
     </row>
@@ -927,14 +927,14 @@
       <c r="D10" s="9" t="n">
         <v>0.205</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>25352500</v>
+        <v>25502500</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H10" t="n">
         <v>55.27</v>
@@ -972,7 +972,7 @@
       <c r="D11" s="9" t="n">
         <v>0.025</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
@@ -1017,7 +1017,7 @@
       <c r="D12" s="9" t="n">
         <v>0.01</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="10" t="n">
         <v>-0.3333</v>
       </c>
       <c r="F12" s="11" t="n">
@@ -1062,14 +1062,14 @@
       <c r="D13" s="9" t="n">
         <v>0.735</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>21032800</v>
+        <v>21367100</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H13" t="n">
         <v>52.16</v>
@@ -1111,10 +1111,10 @@
         <v>0.0167</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>19533300</v>
+        <v>20176300</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="H14" t="n">
         <v>53.62</v>
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>-0.182</v>
+        <v>3.48</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>-0.1982</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>18925200</v>
+        <v>20075600</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="H15" t="n">
-        <v>54.09</v>
+        <v>52.73</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>3.597</v>
+        <v>3.59</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>2.457</v>
+        <v>2.456</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       <c r="D16" s="9" t="n">
         <v>0.385</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="10" t="n">
         <v>-0.0128</v>
       </c>
       <c r="F16" s="11" t="n">
@@ -1246,7 +1246,7 @@
         <v>0.0319</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>18332600</v>
+        <v>18387100</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0.76</v>
@@ -1287,14 +1287,14 @@
       <c r="D18" s="9" t="n">
         <v>0.865</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="10" t="n">
         <v>-0.005699999999999999</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>17389000</v>
+        <v>17849000</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H18" t="n">
         <v>46.81</v>
@@ -1332,14 +1332,14 @@
       <c r="D19" s="9" t="n">
         <v>0.155</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>17211300</v>
+        <v>17711300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="H19" t="n">
         <v>44.73</v>
@@ -1366,28 +1366,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>-0.0048</v>
+        <v>0.53</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>15663200</v>
+        <v>16008400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.92</v>
+        <v>0.41</v>
       </c>
       <c r="H20" t="n">
-        <v>44.75</v>
+        <v>29.77</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2.117</v>
+        <v>0.613</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>2.066</v>
+        <v>0.827</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1411,39 +1411,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.53</v>
+        <v>0.355</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>0.0392</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>15622200</v>
+        <v>15707100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.4</v>
+        <v>2.07</v>
       </c>
       <c r="H21" t="n">
-        <v>29.77</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.52</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.613</v>
+        <v>0.332</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.827</v>
+        <v>0.314</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,39 +1456,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>15471100</v>
+        <v>15698500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="H22" t="n">
-        <v>59.66</v>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.92</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>2.45</v>
+        <v>2.118</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2.295</v>
+        <v>2.067</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1501,28 +1501,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>0.07580000000000001</v>
+        <v>2.5</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>15464100</v>
+        <v>15493300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>2.04</v>
+        <v>0.96</v>
       </c>
       <c r="H23" t="n">
-        <v>62.52</v>
+        <v>61.27</v>
       </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.332</v>
+        <v>2.451</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.314</v>
+        <v>2.296</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1557,14 +1557,14 @@
       <c r="D24" s="9" t="n">
         <v>0.515</v>
       </c>
-      <c r="E24" s="17" t="n">
+      <c r="E24" s="10" t="n">
         <v>-0.0721</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>14245100</v>
+        <v>14278900</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="H24" t="n">
         <v>46.92</v>
@@ -1591,28 +1591,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>0.0488</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>13057800</v>
+        <v>13278700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.52</v>
+        <v>0.92</v>
       </c>
       <c r="H25" t="n">
-        <v>35.23</v>
+        <v>50.19</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.233</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.247</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1636,28 +1636,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>-0.0426</v>
+        <v>0.215</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0.0488</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>12965300</v>
+        <v>13136800</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1.31</v>
+        <v>0.53</v>
       </c>
       <c r="H26" t="n">
-        <v>52.18</v>
+        <v>35.23</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.45</v>
+        <v>0.233</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.413</v>
+        <v>0.247</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1692,14 +1692,14 @@
       <c r="D27" s="9" t="n">
         <v>0.77</v>
       </c>
-      <c r="E27" s="17" t="n">
+      <c r="E27" s="10" t="n">
         <v>-0.006500000000000001</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>12900400</v>
+        <v>13095300</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H27" t="n">
         <v>48.13</v>
@@ -1726,28 +1726,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v>-0.0532</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>12875700</v>
+        <v>13000300</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.89</v>
+        <v>1.32</v>
       </c>
       <c r="H28" t="n">
-        <v>50.19</v>
+        <v>50.86</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.449</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.412</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1782,7 +1782,7 @@
       <c r="D29" s="9" t="n">
         <v>0.05</v>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E29" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
@@ -1816,39 +1816,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>11125900</v>
+        <v>11282400</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.12</v>
+        <v>0.39</v>
       </c>
       <c r="H30" t="n">
-        <v>48.92</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.22</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.052</v>
+        <v>0.271</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.044</v>
+        <v>0.322</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1872,14 +1872,14 @@
       <c r="D31" s="9" t="n">
         <v>2.48</v>
       </c>
-      <c r="E31" s="17" t="n">
+      <c r="E31" s="10" t="n">
         <v>-0.012</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>11122400</v>
+        <v>11198800</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H31" t="n">
         <v>44.57</v>
@@ -1906,39 +1906,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0152</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DGB</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E32" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E32" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>11113900</v>
+        <v>11130900</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>160.02</v>
+        <v>1.12</v>
       </c>
       <c r="H32" t="n">
-        <v>60.06</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.92</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.035</v>
+        <v>0.052</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.035</v>
+        <v>0.044</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1951,28 +1951,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0152</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>DGB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.57</v>
+        <v>0.04</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>-0.0172</v>
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>10869400</v>
+        <v>11113900</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.72</v>
+        <v>160.02</v>
       </c>
       <c r="H33" t="n">
-        <v>61.57</v>
+        <v>60.06</v>
       </c>
       <c r="I33" s="16" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.533</v>
+        <v>0.035</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.485</v>
+        <v>0.035</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1996,28 +1996,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>0.0208</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-0.0259</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>10772400</v>
+        <v>10918800</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.37</v>
+        <v>0.72</v>
       </c>
       <c r="H34" t="n">
-        <v>33.57</v>
+        <v>60.2</v>
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.27</v>
+        <v>0.532</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.322</v>
+        <v>0.485</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>-0.0127</v>
+        <v>0.785</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>9918700</v>
+        <v>10022900</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="H35" t="n">
-        <v>42.88</v>
+        <v>44.17</v>
       </c>
       <c r="I35" s="16" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.8</v>
+        <v>0.801</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0.806</v>
@@ -2086,28 +2086,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.335</v>
+        <v>0.01</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>-0.029</v>
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>9756700</v>
+        <v>9952700</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1.43</v>
+        <v>13.86</v>
       </c>
       <c r="H36" t="n">
-        <v>34.86</v>
+        <v>53.43</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.35</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.35</v>
+        <v>0.007</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2131,39 +2131,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>-0.0168</v>
+        <v>0.335</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.029</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>9045600</v>
+        <v>9890500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.38</v>
+        <v>1.44</v>
       </c>
       <c r="H37" t="n">
-        <v>55.26</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.86</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.742</v>
+        <v>0.35</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.55</v>
+        <v>0.35</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2176,39 +2176,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.39</v>
+        <v>1.76</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0</v>
+        <v>-0.0168</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>9042000</v>
+        <v>9060600</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="H38" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.26</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.383</v>
+        <v>1.742</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.325</v>
+        <v>1.55</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2221,28 +2221,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E39" s="10" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E39" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>8952700</v>
+        <v>9053100</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>12.47</v>
+        <v>0.4</v>
       </c>
       <c r="H39" t="n">
-        <v>53.43</v>
+        <v>55.3</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.383</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.007</v>
+        <v>0.325</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2277,11 +2277,11 @@
       <c r="D40" s="9" t="n">
         <v>0.38</v>
       </c>
-      <c r="E40" s="17" t="n">
+      <c r="E40" s="10" t="n">
         <v>-0.038</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>8876800</v>
+        <v>8926800</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0.83</v>
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>10.04</v>
+        <v>10.02</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>8738500</v>
+        <v>8836500</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H41" t="n">
-        <v>40.82</v>
+        <v>39.33</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>10.147</v>
+        <v>10.145</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>10.294</v>
+        <v>10.293</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2356,39 +2356,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>-0.0435</v>
+        <v>0.8</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>8566100</v>
+        <v>8755600</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1.03</v>
+        <v>0.79</v>
       </c>
       <c r="H42" t="n">
-        <v>37.36</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.64</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.121</v>
+        <v>0.727</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.124</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2401,39 +2401,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>-0.0312</v>
+        <v>0.11</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>8025700</v>
+        <v>8666100</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="H43" t="n">
-        <v>76.66</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.36</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>3.703</v>
+        <v>0.121</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>3.281</v>
+        <v>0.124</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2446,28 +2446,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>-0.0168</v>
+        <v>4.39</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>-0.0223</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>7982300</v>
+        <v>8167300</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.91</v>
+        <v>1.35</v>
       </c>
       <c r="H44" t="n">
-        <v>63.76</v>
+        <v>78.72</v>
       </c>
       <c r="I44" s="16" t="inlineStr">
         <is>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>2.682</v>
+        <v>3.707</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>2.522</v>
+        <v>3.282</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2491,28 +2491,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>-0.0062</v>
+        <v>2.93</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>7970300</v>
+        <v>8068700</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.72</v>
+        <v>0.92</v>
       </c>
       <c r="H45" t="n">
-        <v>64.63</v>
+        <v>64.36</v>
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.728</v>
+        <v>2.683</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>2.522</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2547,7 +2547,7 @@
       <c r="D46" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E46" s="17" t="n">
+      <c r="E46" s="10" t="n">
         <v>-0.0476</v>
       </c>
       <c r="F46" s="11" t="n">
@@ -2596,7 +2596,7 @@
         <v>0.033</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>7692400</v>
+        <v>7712200</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>1.04</v>
@@ -2637,7 +2637,7 @@
       <c r="D48" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="E48" s="17" t="n">
+      <c r="E48" s="10" t="n">
         <v>-0.04</v>
       </c>
       <c r="F48" s="11" t="n">
@@ -2675,7 +2675,7 @@
       <c r="D49" s="9" t="n">
         <v>0.29</v>
       </c>
-      <c r="E49" s="17" t="n">
+      <c r="E49" s="10" t="n">
         <v>-0.0333</v>
       </c>
       <c r="F49" s="11" t="n">
@@ -2720,7 +2720,7 @@
       <c r="D50" s="9" t="n">
         <v>0.035</v>
       </c>
-      <c r="E50" s="10" t="n">
+      <c r="E50" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
@@ -2763,19 +2763,19 @@
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>-0.0366</v>
+        <v>0.4</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>7417700</v>
+        <v>7420600</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>0.66</v>
       </c>
       <c r="H51" t="n">
-        <v>39.14</v>
+        <v>42.46</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>0.0034</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>7294400</v>
+        <v>7378000</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0.5</v>
@@ -2855,14 +2855,14 @@
       <c r="D53" s="9" t="n">
         <v>0.255</v>
       </c>
-      <c r="E53" s="17" t="n">
+      <c r="E53" s="10" t="n">
         <v>-0.0192</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>7204400</v>
+        <v>7224400</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
@@ -2882,39 +2882,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>-0.0064</v>
+        <v>7.8</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0026</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>6934800</v>
+        <v>7019000</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>2.01</v>
+        <v>0.54</v>
       </c>
       <c r="H54" t="n">
-        <v>40.52</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.83</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.578</v>
+        <v>7.803</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.642</v>
+        <v>7.741</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,39 +2927,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0.0013</v>
+        <v>1.55</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>6860600</v>
+        <v>6973900</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.52</v>
+        <v>2.02</v>
       </c>
       <c r="H55" t="n">
-        <v>50.34</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.52</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>7.802</v>
+        <v>1.578</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>7.741</v>
+        <v>1.642</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2981,19 +2981,19 @@
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="E56" s="17" t="n">
-        <v>-0.008500000000000001</v>
+        <v>4.69</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>6740700</v>
+        <v>6807600</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>0.37</v>
       </c>
       <c r="H56" t="n">
-        <v>30.19</v>
+        <v>30.9</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>4.819</v>
+        <v>4.82</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>4.944</v>
+        <v>4.945</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3028,14 +3028,14 @@
       <c r="D57" s="9" t="n">
         <v>1.31</v>
       </c>
-      <c r="E57" s="17" t="n">
+      <c r="E57" s="10" t="n">
         <v>-0.0296</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>6717900</v>
+        <v>6776100</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="H57" t="n">
         <v>45.15</v>
@@ -3073,11 +3073,11 @@
       <c r="D58" s="9" t="n">
         <v>0.655</v>
       </c>
-      <c r="E58" s="10" t="n">
+      <c r="E58" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>6526700</v>
+        <v>6545900</v>
       </c>
       <c r="G58" s="12" t="n">
         <v>0.68</v>
@@ -3116,19 +3116,19 @@
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>0.0333</v>
+        <v>0.15</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>6386900</v>
+        <v>6424600</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>0.15</v>
       </c>
       <c r="H59" t="n">
-        <v>50.05</v>
+        <v>47.65</v>
       </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
@@ -3161,19 +3161,19 @@
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>-0.0095</v>
+        <v>1.03</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>6224000</v>
+        <v>6358200</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H60" t="n">
-        <v>45.77</v>
+        <v>44.39</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>1.075</v>
+        <v>1.074</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>1.025</v>
@@ -3197,39 +3197,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SINARAN</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>-0.0131</v>
+        <v>0.12</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0.1429</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>6199200</v>
+        <v>6212400</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.98</v>
+        <v>2.49</v>
       </c>
       <c r="H61" t="n">
-        <v>41.15</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.04000000000001</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.771</v>
+        <v>0.106</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.772</v>
+        <v>0.102</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3242,39 +3242,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>0.0476</v>
+        <v>0.755</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.0131</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>5991000</v>
+        <v>6209200</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>3</v>
+        <v>0.98</v>
       </c>
       <c r="H62" t="n">
-        <v>75.29000000000001</v>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.15</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.381</v>
+        <v>0.771</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.346</v>
+        <v>0.772</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3287,28 +3287,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PERMAJU</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>5970700</v>
+        <v>5991000</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>9.49</v>
+        <v>3</v>
       </c>
       <c r="H63" t="n">
-        <v>58.67</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.008</v>
+        <v>0.381</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.008</v>
+        <v>0.346</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3332,28 +3332,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SINARAN</t>
+          <t>PERMAJU</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>0.1429</v>
+        <v>0.01</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>5964900</v>
+        <v>5980700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>2.39</v>
+        <v>9.5</v>
       </c>
       <c r="H64" t="n">
-        <v>64.04000000000001</v>
+        <v>58.67</v>
       </c>
       <c r="I64" s="16" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.106</v>
+        <v>0.008</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.102</v>
+        <v>0.008</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3377,28 +3377,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0118</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TRIVE</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E65" s="15" t="n">
-        <v>0.3333</v>
+        <v>2.05</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>5692700</v>
+        <v>5900000</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>58.19</v>
+        <v>2.17</v>
       </c>
       <c r="H65" t="n">
-        <v>58.93</v>
+        <v>45.9</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.016</v>
+        <v>2.061</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.017</v>
+        <v>2.101</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3422,39 +3422,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>0.0049</v>
+        <v>7.53</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>5679400</v>
+        <v>5843500</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>2.09</v>
+        <v>0.52</v>
       </c>
       <c r="H66" t="n">
-        <v>47.99</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.65</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.062</v>
+        <v>7.896</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.102</v>
+        <v>8.231</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3467,28 +3467,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0118</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>TRIVE</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.36</v>
+        <v>0.02</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>0.0141</v>
+        <v>0.3333</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>5565500</v>
+        <v>5692700</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.78</v>
+        <v>58.19</v>
       </c>
       <c r="H67" t="n">
-        <v>64.29000000000001</v>
+        <v>58.93</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.34</v>
+        <v>0.016</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.321</v>
+        <v>0.017</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3512,28 +3512,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0055</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SERSOL</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.05</v>
+        <v>0.36</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>0.4286</v>
+        <v>0.0141</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>5475300</v>
+        <v>5593400</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>1.49</v>
+        <v>0.79</v>
       </c>
       <c r="H68" t="n">
-        <v>63.38</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.039</v>
+        <v>0.34</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.035</v>
+        <v>0.321</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3557,39 +3557,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0055</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SERSOL</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>-0.0027</v>
+        <v>0.05</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.4286</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>5442400</v>
+        <v>5475300</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.48</v>
+        <v>1.49</v>
       </c>
       <c r="H69" t="n">
-        <v>26.39</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.38</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>7.895</v>
+        <v>0.039</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>8.231</v>
+        <v>0.035</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3602,39 +3602,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0145</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TFP</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.055</v>
+        <v>0.595</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>0</v>
+        <v>-0.0246</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>5321200</v>
+        <v>5428200</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1.43</v>
+        <v>0.52</v>
       </c>
       <c r="H70" t="n">
-        <v>38.54</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.82</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.062</v>
+        <v>0.606</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.606</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3658,14 +3658,14 @@
       <c r="D71" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E71" s="17" t="n">
+      <c r="E71" s="10" t="n">
         <v>-0.0173</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>5280300</v>
+        <v>5351200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="H71" t="n">
         <v>41.33</v>
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>TFP</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>0.0625</v>
+        <v>0.055</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>5265100</v>
+        <v>5321200</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="H72" t="n">
-        <v>67</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.54</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.151</v>
+        <v>0.062</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.14</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3737,28 +3737,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>-0.0246</v>
+        <v>0.17</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>5001400</v>
+        <v>5268900</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.48</v>
+        <v>1.79</v>
       </c>
       <c r="H73" t="n">
-        <v>43.82</v>
+        <v>67</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.606</v>
+        <v>0.151</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.606</v>
+        <v>0.14</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3782,28 +3782,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E74" s="10" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="E74" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>4966100</v>
+        <v>5069900</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>1.56</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>31.3</v>
+        <v>37.74</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>3.273</v>
+        <v>7.647</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>3.465</v>
+        <v>7.827</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3827,28 +3827,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>0.0013</v>
+        <v>3.14</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.0032</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>4903700</v>
+        <v>4966800</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.67</v>
+        <v>1.56</v>
       </c>
       <c r="H75" t="n">
-        <v>38.32</v>
+        <v>30.64</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>7.648</v>
+        <v>3.272</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>7.827</v>
+        <v>3.465</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3872,39 +3872,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>0</v>
+        <v>2.33</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>4779100</v>
+        <v>4817200</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.58</v>
+        <v>0.28</v>
       </c>
       <c r="H76" t="n">
-        <v>41.13</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.06</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.194</v>
+        <v>2.341</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.197</v>
+        <v>2.251</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3917,39 +3917,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E77" s="10" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="E77" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>4744800</v>
+        <v>4779100</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="H77" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.13</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.367</v>
+        <v>0.194</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.367</v>
+        <v>0.197</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3962,39 +3962,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E78" s="10" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E78" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>4727000</v>
+        <v>4744800</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H78" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.25</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.306</v>
+        <v>0.367</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.296</v>
+        <v>0.367</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4007,28 +4007,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>0.0185</v>
+        <v>0.3</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>4675300</v>
+        <v>4727000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="H79" t="n">
-        <v>37.36</v>
+        <v>44.88</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>1.715</v>
+        <v>0.306</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1.831</v>
+        <v>0.296</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4052,39 +4052,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="E80" s="15" t="n">
-        <v>0.08869999999999999</v>
+        <v>0.0247</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>4593100</v>
+        <v>4718600</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>1.67</v>
+        <v>0.72</v>
       </c>
       <c r="H80" t="n">
-        <v>84.38</v>
-      </c>
-      <c r="I80" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.93</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>1.091</v>
+        <v>1.716</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.914</v>
+        <v>1.832</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4097,28 +4097,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E81" s="17" t="n">
-        <v>-0.0196</v>
+        <v>0.91</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>-0.0319</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>4571000</v>
+        <v>4705200</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.39</v>
+        <v>0.98</v>
       </c>
       <c r="H81" t="n">
-        <v>37.16</v>
+        <v>59.42</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.268</v>
+        <v>0.891</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.311</v>
+        <v>0.853</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4142,28 +4142,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E82" s="17" t="n">
-        <v>-0.029</v>
+        <v>1.35</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.08869999999999999</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>4518200</v>
+        <v>4659100</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.58</v>
+        <v>1.7</v>
       </c>
       <c r="H82" t="n">
-        <v>48.24</v>
+        <v>84.38</v>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.681</v>
+        <v>1.091</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.665</v>
+        <v>0.914</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4187,28 +4187,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.09</v>
+        <v>0.25</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>0</v>
+        <v>-0.0196</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>4516800</v>
+        <v>4572000</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="H83" t="n">
-        <v>74.22</v>
+        <v>37.16</v>
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.019</v>
+        <v>0.268</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.861</v>
+        <v>0.311</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4232,28 +4232,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>1.09</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>4483000</v>
+        <v>4535800</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="H84" t="n">
-        <v>48.57</v>
+        <v>74.22</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>2.339</v>
+        <v>1.019</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>2.251</v>
+        <v>0.861</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4277,28 +4277,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>0.0089</v>
+        <v>0.67</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>-0.029</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>4463100</v>
+        <v>4518200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="H85" t="n">
-        <v>44.53</v>
+        <v>48.24</v>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.171</v>
+        <v>0.681</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.148</v>
+        <v>0.665</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4322,28 +4322,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>-0.0426</v>
+        <v>5.82</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>0.0017</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>4373600</v>
+        <v>4485500</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.91</v>
+        <v>0.31</v>
       </c>
       <c r="H86" t="n">
-        <v>55.87</v>
+        <v>59.45</v>
       </c>
       <c r="I86" s="16" t="inlineStr">
         <is>
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.89</v>
+        <v>5.708</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.852</v>
+        <v>5.192</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4367,28 +4367,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>13.06</v>
+        <v>1.13</v>
       </c>
       <c r="E87" s="15" t="n">
-        <v>0.0267</v>
+        <v>0.0089</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>4320700</v>
+        <v>4471500</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="H87" t="n">
-        <v>42.58</v>
+        <v>44.53</v>
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>13.154</v>
+        <v>1.171</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>13.741</v>
+        <v>1.148</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4412,28 +4412,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="E88" s="17" t="n">
-        <v>-0.0034</v>
+        <v>13.06</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0.0267</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>4279500</v>
+        <v>4340700</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.29</v>
+        <v>0.52</v>
       </c>
       <c r="H88" t="n">
-        <v>58.09</v>
+        <v>42.58</v>
       </c>
       <c r="I88" s="16" t="inlineStr">
         <is>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>5.705</v>
+        <v>13.154</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>5.192</v>
+        <v>13.741</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4457,39 +4457,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>0.025</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>4207500</v>
+        <v>4332100</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.78</v>
+        <v>0.28</v>
       </c>
       <c r="H89" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.42</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.263</v>
+        <v>0.491</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.3</v>
+        <v>0.41</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4502,28 +4502,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>-0.028</v>
+        <v>1.22</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>4128800</v>
+        <v>4272200</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
       <c r="H90" t="n">
-        <v>38.3</v>
+        <v>38.27</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>4.518</v>
+        <v>1.262</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>4.52</v>
+        <v>1.3</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4547,39 +4547,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>4269400</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H91" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n">
         <v>0.555</v>
       </c>
-      <c r="E91" s="17" t="n">
-        <v>-0.0263</v>
-      </c>
-      <c r="F91" s="11" t="n">
-        <v>4101900</v>
-      </c>
-      <c r="G91" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H91" t="n">
-        <v>68.02</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J91" s="9" t="n">
-        <v>0.491</v>
-      </c>
       <c r="K91" s="9" t="n">
-        <v>0.41</v>
+        <v>0.586</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4592,39 +4592,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1.28</v>
+        <v>4.15</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>0</v>
+        <v>-0.0326</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>4022100</v>
+        <v>4238200</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.34</v>
+        <v>0.54</v>
       </c>
       <c r="H92" t="n">
-        <v>35.67</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.84</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>1.322</v>
+        <v>4.516</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1.43</v>
+        <v>4.52</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4637,39 +4637,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>-0.0409</v>
+        <v>5.23</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>-0.0297</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>3967500</v>
+        <v>4092400</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="H93" t="n">
-        <v>82.97</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.03</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.355</v>
+        <v>5.705</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.834</v>
+        <v>5.752</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4682,39 +4682,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.525</v>
+        <v>1.28</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>-0.0187</v>
+        <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>3943200</v>
+        <v>4049600</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.61</v>
+        <v>0.34</v>
       </c>
       <c r="H94" t="n">
-        <v>32.66</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>35.67</v>
+      </c>
+      <c r="I94" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.555</v>
+        <v>1.322</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.586</v>
+        <v>1.43</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4727,39 +4727,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="E95" s="17" t="n">
-        <v>-0.0334</v>
+        <v>3.05</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.0409</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>3887900</v>
+        <v>4037000</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="H95" t="n">
-        <v>36.66</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.97</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>5.703</v>
+        <v>2.355</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>5.751</v>
+        <v>1.834</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4772,28 +4772,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>-0.031</v>
+        <v>0.335</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>-0.0429</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>3871300</v>
+        <v>3936400</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.63</v>
+        <v>0.83</v>
       </c>
       <c r="H96" t="n">
-        <v>87.81999999999999</v>
+        <v>48.04</v>
       </c>
       <c r="I96" s="16" t="inlineStr">
         <is>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.949</v>
+        <v>0.339</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.757</v>
+        <v>0.333</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4817,28 +4817,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="E97" s="10" t="n">
-        <v>0</v>
+        <v>-0.031</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>3858300</v>
+        <v>3871800</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="H97" t="n">
-        <v>77.37</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.922</v>
+        <v>0.949</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.775</v>
+        <v>0.757</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4862,28 +4862,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>0</v>
+        <v>1.07</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>3766200</v>
+        <v>3863200</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="H98" t="n">
-        <v>66.27</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.278</v>
+        <v>0.923</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.271</v>
+        <v>0.775</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         <v>0.0038</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>3755900</v>
+        <v>3857800</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="H99" t="n">
         <v>48.51</v>
@@ -4952,28 +4952,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>0.0064</v>
+        <v>0.295</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>3708300</v>
+        <v>3766200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="H100" t="n">
-        <v>64.37</v>
+        <v>66.27</v>
       </c>
       <c r="I100" s="16" t="inlineStr">
         <is>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.768</v>
+        <v>0.278</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.754</v>
+        <v>0.271</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4997,28 +4997,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E101" s="17" t="n">
-        <v>-0.0429</v>
+        <v>0.79</v>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>3628300</v>
+        <v>3708300</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.76</v>
+        <v>0.6</v>
       </c>
       <c r="H101" t="n">
-        <v>48.04</v>
+        <v>64.37</v>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.339</v>
+        <v>0.768</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.333</v>
+        <v>0.754</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5057,10 +5057,10 @@
         <v>0.0114</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3489800</v>
+        <v>3699200</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="H102" t="n">
         <v>32.36</v>
@@ -5098,7 +5098,7 @@
       <c r="D103" s="9" t="n">
         <v>0.835</v>
       </c>
-      <c r="E103" s="17" t="n">
+      <c r="E103" s="10" t="n">
         <v>-0.0118</v>
       </c>
       <c r="F103" s="11" t="n">
@@ -5132,39 +5132,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.75</v>
+        <v>1.47</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>-0.0132</v>
+        <v>0</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>3310700</v>
+        <v>3324000</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.75</v>
+        <v>0.61</v>
       </c>
       <c r="H104" t="n">
-        <v>34.02</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.09</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.788</v>
+        <v>1.472</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.842</v>
+        <v>1.472</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5177,39 +5177,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>-0.0068</v>
+        <v>0.75</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>3247200</v>
+        <v>3317000</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H105" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="I105" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.02</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.471</v>
+        <v>0.788</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>1.472</v>
+        <v>0.842</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5237,7 +5237,7 @@
         <v>0.0172</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>3200400</v>
+        <v>3200500</v>
       </c>
       <c r="G106" s="12" t="n">
         <v>0.44</v>
@@ -5278,11 +5278,11 @@
       <c r="D107" s="9" t="n">
         <v>0.65</v>
       </c>
-      <c r="E107" s="17" t="n">
+      <c r="E107" s="10" t="n">
         <v>-0.0152</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>3183700</v>
+        <v>3192100</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>1.07</v>
@@ -5312,28 +5312,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>-0.0217</v>
+        <v>0.645</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>3147700</v>
+        <v>3148200</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H108" t="n">
-        <v>65.48999999999999</v>
+        <v>58.16</v>
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.206</v>
+        <v>0.622</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.181</v>
+        <v>0.586</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5357,28 +5357,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>0.0134</v>
+        <v>0.225</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>3146500</v>
+        <v>3147700</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="H109" t="n">
-        <v>58.56</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="I109" s="16" t="inlineStr">
         <is>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>2.888</v>
+        <v>0.206</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>2.7</v>
+        <v>0.181</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5402,28 +5402,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>3.71</v>
+        <v>3.03</v>
       </c>
       <c r="E110" s="15" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0134</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>3116400</v>
+        <v>3147400</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H110" t="n">
-        <v>77.59999999999999</v>
+        <v>58.56</v>
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>3.382</v>
+        <v>2.888</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>2.938</v>
+        <v>2.7</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5447,28 +5447,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>-0.0185</v>
+        <v>3.7</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>0.0054</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>3103500</v>
+        <v>3117100</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>1.1</v>
+        <v>0.92</v>
       </c>
       <c r="H111" t="n">
-        <v>71.53</v>
+        <v>77.33</v>
       </c>
       <c r="I111" s="16" t="inlineStr">
         <is>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.232</v>
+        <v>3.381</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.211</v>
+        <v>2.938</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5492,28 +5492,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v>0.0317</v>
+        <v>0.265</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>3101000</v>
+        <v>3113500</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="H112" t="n">
-        <v>59.19</v>
+        <v>71.53</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.623</v>
+        <v>0.232</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.586</v>
+        <v>0.211</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5548,7 +5548,7 @@
       <c r="D113" s="9" t="n">
         <v>2.73</v>
       </c>
-      <c r="E113" s="17" t="n">
+      <c r="E113" s="10" t="n">
         <v>-0.0109</v>
       </c>
       <c r="F113" s="11" t="n">
@@ -5582,28 +5582,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>-0.0443</v>
+        <v>0.58</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>3037500</v>
+        <v>3040100</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>4.78</v>
+        <v>0.58</v>
       </c>
       <c r="H114" t="n">
-        <v>39.84</v>
+        <v>31.26</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.577</v>
+        <v>0.628</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1.507</v>
+        <v>0.656</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5627,28 +5627,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>-0.0307</v>
+        <v>1.51</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>-0.0443</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>3000500</v>
+        <v>3037500</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>1.19</v>
+        <v>4.78</v>
       </c>
       <c r="H115" t="n">
-        <v>41.08</v>
+        <v>39.84</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>4.364</v>
+        <v>1.577</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>4.41</v>
+        <v>1.507</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5672,28 +5672,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E116" s="17" t="n">
-        <v>-0.008500000000000001</v>
+        <v>4.1</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>-0.0307</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>2707100</v>
+        <v>3020400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.52</v>
+        <v>1.2</v>
       </c>
       <c r="H116" t="n">
-        <v>32.29</v>
+        <v>41.08</v>
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.628</v>
+        <v>4.364</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.656</v>
+        <v>4.41</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5726,19 +5726,19 @@
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E117" s="15" t="n">
-        <v>0.0068</v>
+        <v>0.74</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>2665200</v>
+        <v>2871500</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="H117" t="n">
-        <v>64.18000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="I117" s="16" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0.62</v>
@@ -5771,19 +5771,19 @@
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="E118" s="15" t="n">
-        <v>0.0176</v>
+        <v>0.0235</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>2605900</v>
+        <v>2863200</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="H118" t="n">
-        <v>38.54</v>
+        <v>40.29</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>3.584</v>
+        <v>3.586</v>
       </c>
       <c r="K118" s="9" t="n">
         <v>3.694</v>
@@ -5807,39 +5807,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <v>-0.0051</v>
+        <v>1.16</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>2603500</v>
+        <v>2712300</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.35</v>
+        <v>0.73</v>
       </c>
       <c r="H119" t="n">
-        <v>44.03</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.75</v>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.976</v>
+        <v>1.116</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.972</v>
+        <v>1.021</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5852,39 +5852,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0250</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>YXPM</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.215</v>
+        <v>1.26</v>
       </c>
       <c r="E120" s="17" t="n">
-        <v>-0.0444</v>
+        <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>2594500</v>
+        <v>2665900</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>5.02</v>
+        <v>0.93</v>
       </c>
       <c r="H120" t="n">
-        <v>49.65</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.77</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.216</v>
+        <v>1.374</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.214</v>
+        <v>1.317</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5897,33 +5897,40 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>-0.0104</v>
+        <v>1.94</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>2594200</v>
+        <v>2641700</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I121" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J121" s="9" t="n"/>
-      <c r="K121" s="9" t="n"/>
+        <v>0.35</v>
+      </c>
+      <c r="H121" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>1.976</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>1.972</v>
+      </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
     </row>
@@ -5935,28 +5942,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.295</v>
+        <v>1.05</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>0</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>2592000</v>
+        <v>2631200</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="H122" t="n">
-        <v>49.23</v>
+        <v>29.35</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5964,10 +5971,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.295</v>
+        <v>1.105</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.296</v>
+        <v>1.146</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5995,10 +6002,10 @@
         <v>0.0227</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>2550500</v>
+        <v>2620500</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="H123" t="n">
         <v>53.82</v>
@@ -6025,39 +6032,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0250</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>YXPM</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1.26</v>
+        <v>0.215</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>0</v>
+        <v>-0.0444</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>2549000</v>
+        <v>2594500</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.89</v>
+        <v>5.02</v>
       </c>
       <c r="H124" t="n">
-        <v>34.77</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.65</v>
+      </c>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.374</v>
+        <v>0.216</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.317</v>
+        <v>0.214</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6070,40 +6077,33 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E125" s="15" t="n">
-        <v>0.0089</v>
+        <v>0.475</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>-0.0104</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>2547400</v>
+        <v>2594200</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H125" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J125" s="9" t="n">
-        <v>1.157</v>
-      </c>
-      <c r="K125" s="9" t="n">
-        <v>1.103</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n"/>
+      <c r="K125" s="9" t="n"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
     </row>
@@ -6115,39 +6115,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="E126" s="10" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E126" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>2523300</v>
+        <v>2592000</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="H126" t="n">
-        <v>69.06</v>
-      </c>
-      <c r="I126" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>1.956</v>
+        <v>0.295</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>1.898</v>
+        <v>0.296</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6160,39 +6160,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E127" s="17" t="n">
-        <v>-0.0064</v>
+        <v>1.13</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>2446800</v>
+        <v>2577000</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="H127" t="n">
-        <v>73.98999999999999</v>
-      </c>
-      <c r="I127" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.49</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.157</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.625</v>
+        <v>1.103</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6205,28 +6205,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>0.0122</v>
+        <v>2.18</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>2436900</v>
+        <v>2523300</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.42</v>
+        <v>1.25</v>
       </c>
       <c r="H128" t="n">
-        <v>54.53</v>
+        <v>69.06</v>
       </c>
       <c r="I128" s="16" t="inlineStr">
         <is>
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.403</v>
+        <v>1.956</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.403</v>
+        <v>1.898</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6250,39 +6250,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E129" s="17" t="n">
-        <v>-0.0115</v>
+        <v>0.775</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>2385900</v>
+        <v>2521800</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.76</v>
+        <v>0.4</v>
       </c>
       <c r="H129" t="n">
-        <v>50.97</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.98999999999999</v>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.856</v>
+        <v>0.625</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6295,28 +6295,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>0</v>
+        <v>-0.0183</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>2344400</v>
+        <v>2510300</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.63</v>
+        <v>0.51</v>
       </c>
       <c r="H130" t="n">
-        <v>60.43</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="I130" s="16" t="inlineStr">
         <is>
@@ -6324,10 +6324,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>1.115</v>
+        <v>0.993</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1.021</v>
+        <v>0.821</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6340,39 +6340,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
         <v>0.415</v>
       </c>
-      <c r="E131" s="17" t="n">
-        <v>-0.0235</v>
+      <c r="E131" s="15" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>2293600</v>
+        <v>2456900</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>1.98</v>
+        <v>0.42</v>
       </c>
       <c r="H131" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.53</v>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.429</v>
+        <v>0.403</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.45</v>
+        <v>0.403</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6385,39 +6385,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>0.0182</v>
+        <v>0.86</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>2282300</v>
+        <v>2385900</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>3.52</v>
+        <v>0.76</v>
       </c>
       <c r="H132" t="n">
-        <v>72.13</v>
-      </c>
-      <c r="I132" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.97</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.534</v>
+        <v>0.86</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.528</v>
+        <v>0.856</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6430,28 +6430,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1.06</v>
+        <v>0.415</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>0</v>
+        <v>-0.0235</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>2210900</v>
+        <v>2294000</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>1</v>
+        <v>1.98</v>
       </c>
       <c r="H133" t="n">
-        <v>31.18</v>
+        <v>35.3</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>1.105</v>
+        <v>0.429</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>1.146</v>
+        <v>0.45</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6475,28 +6475,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E134" s="17" t="n">
-        <v>-0.0163</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>2202400</v>
+        <v>2282300</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.6</v>
+        <v>3.52</v>
       </c>
       <c r="H134" t="n">
-        <v>39.42</v>
+        <v>72.13</v>
       </c>
       <c r="I134" s="16" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.925</v>
+        <v>0.534</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.969</v>
+        <v>0.528</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6520,39 +6520,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
         <v>0.91</v>
       </c>
-      <c r="E135" s="17" t="n">
+      <c r="E135" s="10" t="n">
         <v>-0.0109</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>2188000</v>
+        <v>2223000</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.96</v>
+        <v>0.61</v>
       </c>
       <c r="H135" t="n">
-        <v>37.66</v>
-      </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.8</v>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.929</v>
+        <v>0.925</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.947</v>
+        <v>0.969</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6565,39 +6565,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>2.7</v>
+        <v>6.21</v>
       </c>
       <c r="E136" s="15" t="n">
-        <v>0.0037</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>2164500</v>
+        <v>2222100</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="H136" t="n">
-        <v>49.21</v>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.46</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>2.676</v>
+        <v>6.28</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>2.853</v>
+        <v>6.472</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6610,28 +6610,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E137" s="15" t="n">
-        <v>0.0139</v>
+        <v>0.91</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>2154400</v>
+        <v>2197300</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="H137" t="n">
-        <v>40.95</v>
+        <v>37.66</v>
       </c>
       <c r="I137" s="13" t="inlineStr">
         <is>
@@ -6639,10 +6639,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.375</v>
+        <v>0.929</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.389</v>
+        <v>0.947</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6655,39 +6655,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="E138" s="15" t="n">
-        <v>0.0064</v>
+        <v>2.69</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>2142900</v>
+        <v>2180400</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H138" t="n">
-        <v>52.79</v>
-      </c>
-      <c r="I138" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.27</v>
+      </c>
+      <c r="I138" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>4.738</v>
+        <v>2.675</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>4.597</v>
+        <v>2.853</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6700,39 +6700,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E139" s="15" t="n">
-        <v>0.0114</v>
+        <v>0.36</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>2102700</v>
+        <v>2174400</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.67</v>
+        <v>0.48</v>
       </c>
       <c r="H139" t="n">
-        <v>52.52</v>
-      </c>
-      <c r="I139" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.91</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.436</v>
+        <v>0.374</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.452</v>
+        <v>0.389</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6745,39 +6745,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>-0.0183</v>
+        <v>4.74</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>2096300</v>
+        <v>2167000</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="H140" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="I140" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.79</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.993</v>
+        <v>4.738</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.821</v>
+        <v>4.597</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6790,39 +6790,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>1.89</v>
+        <v>0.445</v>
       </c>
       <c r="E141" s="15" t="n">
-        <v>0.0053</v>
+        <v>0.0114</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>2090000</v>
+        <v>2102700</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.46</v>
+        <v>0.67</v>
       </c>
       <c r="H141" t="n">
-        <v>37.69</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.52</v>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>1.944</v>
+        <v>0.436</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>2.067</v>
+        <v>0.452</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6835,28 +6835,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>0.008100000000000001</v>
+        <v>1.88</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>2048700</v>
+        <v>2101800</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.13</v>
+        <v>0.46</v>
       </c>
       <c r="H142" t="n">
-        <v>42.46</v>
+        <v>35.9</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>6.28</v>
+        <v>1.943</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>6.472</v>
+        <v>2.067</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6880,40 +6880,36 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>0.0256</v>
+        <v>0.27</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1969800</v>
+        <v>2041100</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>1.81</v>
+        <v>0.11</v>
       </c>
       <c r="H143" t="n">
-        <v>40.98</v>
+        <v>16.24</v>
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J143" s="9" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="K143" s="9" t="n">
-        <v>0.213</v>
-      </c>
+      <c r="J143" s="9" t="n"/>
+      <c r="K143" s="9" t="n"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
     </row>
@@ -6925,36 +6921,40 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E144" s="17" t="n">
-        <v>-0.0182</v>
+        <v>0.2</v>
+      </c>
+      <c r="E144" s="15" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1961100</v>
+        <v>1969800</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.1</v>
+        <v>1.81</v>
       </c>
       <c r="H144" t="n">
-        <v>16.24</v>
+        <v>40.98</v>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J144" s="9" t="n"/>
-      <c r="K144" s="9" t="n"/>
+      <c r="J144" s="9" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>0.213</v>
+      </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
     </row>
@@ -6977,7 +6977,7 @@
       <c r="D145" s="9" t="n">
         <v>0.46</v>
       </c>
-      <c r="E145" s="10" t="n">
+      <c r="E145" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
@@ -7011,28 +7011,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.42</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>0</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1923200</v>
+        <v>1926700</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.84</v>
+        <v>0.63</v>
       </c>
       <c r="H146" t="n">
-        <v>65.7</v>
+        <v>48.95</v>
       </c>
       <c r="I146" s="16" t="inlineStr">
         <is>
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.398</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.382</v>
+        <v>0.575</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7056,28 +7056,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>-0.0175</v>
+        <v>0</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1910500</v>
+        <v>1923200</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="H147" t="n">
-        <v>47.63</v>
+        <v>65.7</v>
       </c>
       <c r="I147" s="16" t="inlineStr">
         <is>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.398</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.575</v>
+        <v>0.382</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7101,28 +7101,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E148" s="17" t="n">
-        <v>-0.0278</v>
+        <v>0.68</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1867500</v>
+        <v>1876700</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="H148" t="n">
-        <v>57.63</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="I148" s="16" t="inlineStr">
         <is>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.504</v>
+        <v>0.581</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.412</v>
+        <v>0.501</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7157,11 +7157,11 @@
       <c r="D149" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="E149" s="17" t="n">
+      <c r="E149" s="10" t="n">
         <v>-0.0102</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>1865100</v>
+        <v>1869100</v>
       </c>
       <c r="G149" s="12" t="n">
         <v>0.6</v>
@@ -7191,39 +7191,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E150" s="17" t="n">
-        <v>-0.1053</v>
+        <v>0.525</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1842400</v>
+        <v>1867500</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.21</v>
+        <v>0.98</v>
       </c>
       <c r="H150" t="n">
-        <v>50.13</v>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.63</v>
+      </c>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.265</v>
+        <v>0.504</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.223</v>
+        <v>0.412</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7236,39 +7236,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E151" s="15" t="n">
-        <v>0.0075</v>
+        <v>0.255</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>-0.1053</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>1801500</v>
+        <v>1842400</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>1.04</v>
+        <v>0.21</v>
       </c>
       <c r="H151" t="n">
-        <v>79.36</v>
-      </c>
-      <c r="I151" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.13</v>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.58</v>
+        <v>0.265</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.5</v>
+        <v>0.223</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7281,39 +7281,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TEKSENG</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E152" s="17" t="n">
-        <v>-0.0357</v>
+        <v>1.04</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>0.0297</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>1799500</v>
+        <v>1809600</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>2.38</v>
+        <v>1.15</v>
       </c>
       <c r="H152" t="n">
-        <v>56.39</v>
-      </c>
-      <c r="I152" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.53</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.262</v>
+        <v>1.029</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.243</v>
+        <v>1.013</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7326,28 +7326,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E153" s="17" t="n">
-        <v>-0.0357</v>
+        <v>0.325</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1783900</v>
+        <v>1806000</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.55</v>
+        <v>0.93</v>
       </c>
       <c r="H153" t="n">
-        <v>53.57</v>
+        <v>39.72</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -7355,10 +7355,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>1.348</v>
+        <v>0.349</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>1.169</v>
+        <v>0.321</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7371,28 +7371,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>TEKSENG</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>0</v>
+        <v>-0.0357</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1776100</v>
+        <v>1799500</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="H154" t="n">
-        <v>43.6</v>
+        <v>56.39</v>
       </c>
       <c r="I154" s="16" t="inlineStr">
         <is>
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.318</v>
+        <v>0.262</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.337</v>
+        <v>0.243</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7416,39 +7416,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E155" s="17" t="n">
-        <v>-0.0299</v>
+        <v>0.305</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>1776000</v>
+        <v>1791100</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.91</v>
+        <v>0.3</v>
       </c>
       <c r="H155" t="n">
-        <v>39.72</v>
-      </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.46</v>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>0.349</v>
+        <v>0.318</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>0.321</v>
+        <v>0.337</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7461,28 +7461,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E156" s="15" t="n">
-        <v>0.0396</v>
+        <v>1.35</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>1757500</v>
+        <v>1790900</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H156" t="n">
-        <v>54.01</v>
+        <v>53.57</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -7490,10 +7490,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>1.03</v>
+        <v>1.348</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>1.013</v>
+        <v>1.169</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7517,11 +7517,11 @@
       <c r="D157" s="9" t="n">
         <v>2.12</v>
       </c>
-      <c r="E157" s="17" t="n">
+      <c r="E157" s="10" t="n">
         <v>-0.032</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>1756900</v>
+        <v>1766400</v>
       </c>
       <c r="G157" s="12" t="n">
         <v>0.23</v>
@@ -7562,7 +7562,7 @@
       <c r="D158" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E158" s="17" t="n">
+      <c r="E158" s="10" t="n">
         <v>-0.0164</v>
       </c>
       <c r="F158" s="11" t="n">
@@ -7607,11 +7607,11 @@
       <c r="D159" s="9" t="n">
         <v>0.48</v>
       </c>
-      <c r="E159" s="17" t="n">
+      <c r="E159" s="10" t="n">
         <v>-0.0204</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>1678700</v>
+        <v>1688700</v>
       </c>
       <c r="G159" s="12" t="n">
         <v>0.55</v>
@@ -7652,11 +7652,11 @@
       <c r="D160" s="9" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E160" s="17" t="n">
+      <c r="E160" s="10" t="n">
         <v>-0.0175</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>1676000</v>
+        <v>1680700</v>
       </c>
       <c r="G160" s="12" t="n">
         <v>0.45</v>
@@ -7695,19 +7695,19 @@
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="E161" s="17" t="n">
-        <v>-0.0067</v>
+        <v>1.47</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>-0.0134</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1618100</v>
+        <v>1628500</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H161" t="n">
-        <v>29.13</v>
+        <v>27.96</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>1.547</v>
+        <v>1.546</v>
       </c>
       <c r="K161" s="9" t="n">
         <v>1.662</v>
@@ -7731,28 +7731,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>PIE</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E162" s="17" t="n">
-        <v>-0.02</v>
+        <v>1.64</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>1580300</v>
+        <v>1589500</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="H162" t="n">
-        <v>43.9</v>
+        <v>45.07</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>0.254</v>
+        <v>1.709</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>0.252</v>
+        <v>1.626</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7776,28 +7776,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E163" s="17" t="n">
-        <v>-0.0179</v>
+        <v>0.245</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>1566400</v>
+        <v>1580300</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="H163" t="n">
-        <v>45.85</v>
+        <v>43.9</v>
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
@@ -7805,10 +7805,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>1.709</v>
+        <v>0.254</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>1.626</v>
+        <v>0.252</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7832,14 +7832,14 @@
       <c r="D164" s="9" t="n">
         <v>0.83</v>
       </c>
-      <c r="E164" s="17" t="n">
+      <c r="E164" s="10" t="n">
         <v>-0.006</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>1563500</v>
+        <v>1564600</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="H164" t="n">
         <v>29.7</v>
@@ -7911,39 +7911,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="E166" s="17" t="n">
-        <v>-0.004699999999999999</v>
+        <v>2.35</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>-0.0249</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>1451700</v>
+        <v>1479200</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.31</v>
+        <v>0.99</v>
       </c>
       <c r="H166" t="n">
-        <v>26.42</v>
-      </c>
-      <c r="I166" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.94</v>
+      </c>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>6.674</v>
+        <v>2.244</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>6.873</v>
+        <v>2.047</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7956,39 +7956,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E167" s="17" t="n">
-        <v>-0.0109</v>
+        <v>6.42</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>-0.0031</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>1448000</v>
+        <v>1463600</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.78</v>
+        <v>0.32</v>
       </c>
       <c r="H167" t="n">
-        <v>53.95</v>
-      </c>
-      <c r="I167" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.8</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>0.908</v>
+        <v>6.675</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>0.795</v>
+        <v>6.873</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8001,39 +8001,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ABMB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="E168" s="17" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.91</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>1446400</v>
+        <v>1454400</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>1.1</v>
+        <v>0.79</v>
       </c>
       <c r="H168" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="I168" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.95</v>
+      </c>
+      <c r="I168" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>4.83</v>
+        <v>0.908</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>4.834</v>
+        <v>0.795</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8046,39 +8046,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>ABMB</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E169" s="17" t="n">
-        <v>-0.029</v>
+        <v>4.7</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>1441100</v>
+        <v>1452400</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="H169" t="n">
-        <v>61.08</v>
-      </c>
-      <c r="I169" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.7</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>2.243</v>
+        <v>4.832</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>2.047</v>
+        <v>4.835</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8106,7 +8106,7 @@
         <v>0.0089</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>1415700</v>
+        <v>1445200</v>
       </c>
       <c r="G170" s="12" t="n">
         <v>0.38</v>
@@ -8145,19 +8145,19 @@
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="E171" s="17" t="n">
-        <v>-0.0308</v>
+        <v>5.02</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>1411800</v>
+        <v>1413600</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="H171" t="n">
-        <v>25.01</v>
+        <v>24.7</v>
       </c>
       <c r="I171" s="13" t="inlineStr">
         <is>
@@ -8165,10 +8165,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>5.362</v>
+        <v>5.361</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>5.548</v>
+        <v>5.547</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8181,39 +8181,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>HLBANK</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>23.34</v>
-      </c>
-      <c r="E172" s="15" t="n">
-        <v>0.0026</v>
+        <v>1.38</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>1336000</v>
+        <v>1400000</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>1.99</v>
+        <v>0.71</v>
       </c>
       <c r="H172" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="I172" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.46</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>23.228</v>
+        <v>1.361</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>22.901</v>
+        <v>1.328</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8226,39 +8226,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>0.635</v>
+        <v>2.57</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>0</v>
+        <v>-0.0115</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>1326000</v>
+        <v>1374200</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.95</v>
+        <v>0.42</v>
       </c>
       <c r="H173" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="I173" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.37</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>0.634</v>
+        <v>2.656</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>0.629</v>
+        <v>2.776</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8271,28 +8271,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>HLBANK</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E174" s="17" t="n">
-        <v>-0.0235</v>
+        <v>23.34</v>
+      </c>
+      <c r="E174" s="15" t="n">
+        <v>0.0026</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>1304500</v>
+        <v>1361100</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.52</v>
+        <v>2.03</v>
       </c>
       <c r="H174" t="n">
-        <v>84.23</v>
+        <v>53.4</v>
       </c>
       <c r="I174" s="16" t="inlineStr">
         <is>
@@ -8300,10 +8300,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>2.377</v>
+        <v>23.228</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>1.997</v>
+        <v>22.901</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8316,39 +8316,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E175" s="10" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E175" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>1289300</v>
+        <v>1326000</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
       <c r="H175" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="I175" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.65</v>
+      </c>
+      <c r="I175" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>0.239</v>
+        <v>0.634</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>0.243</v>
+        <v>0.629</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8361,39 +8361,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0263</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E176" s="17" t="n">
-        <v>-0.0115</v>
+        <v>2.92</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>-0.0201</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>1255600</v>
+        <v>1312100</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2.34</v>
+        <v>0.52</v>
       </c>
       <c r="H176" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="I176" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.09</v>
+      </c>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>0.694</v>
+        <v>2.378</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>0.711</v>
+        <v>1.997</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8406,28 +8406,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="E177" s="17" t="n">
-        <v>-0.0305</v>
+        <v>0</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>1250300</v>
+        <v>1296100</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.31</v>
+        <v>1.01</v>
       </c>
       <c r="H177" t="n">
-        <v>54.74</v>
+        <v>31.93</v>
       </c>
       <c r="I177" s="13" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>1.247</v>
+        <v>1.889</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>1.15</v>
+        <v>1.956</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8451,39 +8451,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E178" s="10" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E178" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>1243500</v>
+        <v>1294300</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.63</v>
+        <v>0.74</v>
       </c>
       <c r="H178" t="n">
-        <v>70.84</v>
-      </c>
-      <c r="I178" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.61</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>1.363</v>
+        <v>0.239</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>1.328</v>
+        <v>0.243</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8496,28 +8496,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0263</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>0.97</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>0</v>
+        <v>-0.0115</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>1219300</v>
+        <v>1255600</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.26</v>
+        <v>2.34</v>
       </c>
       <c r="H179" t="n">
-        <v>39.58</v>
+        <v>48.3</v>
       </c>
       <c r="I179" s="13" t="inlineStr">
         <is>
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>0.993</v>
+        <v>0.694</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>1.042</v>
+        <v>0.711</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8541,28 +8541,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E180" s="15" t="n">
-        <v>0.0213</v>
+        <v>1.27</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>-0.0305</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>1205100</v>
+        <v>1254000</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.71</v>
+        <v>0.31</v>
       </c>
       <c r="H180" t="n">
-        <v>43.28</v>
+        <v>54.74</v>
       </c>
       <c r="I180" s="13" t="inlineStr">
         <is>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>0.732</v>
+        <v>1.247</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>0.751</v>
+        <v>1.15</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8586,28 +8586,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E181" s="10" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E181" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>1177600</v>
+        <v>1219300</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.92</v>
+        <v>0.26</v>
       </c>
       <c r="H181" t="n">
-        <v>31.93</v>
+        <v>39.58</v>
       </c>
       <c r="I181" s="13" t="inlineStr">
         <is>
@@ -8615,10 +8615,10 @@
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>1.889</v>
+        <v>0.993</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>1.956</v>
+        <v>1.042</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8631,28 +8631,28 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E182" s="17" t="n">
-        <v>-0.0052</v>
+        <v>0.72</v>
+      </c>
+      <c r="E182" s="15" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>1173100</v>
+        <v>1205100</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H182" t="n">
-        <v>39.69</v>
+        <v>43.28</v>
       </c>
       <c r="I182" s="13" t="inlineStr">
         <is>
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>0.99</v>
+        <v>0.732</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>1.008</v>
+        <v>0.751</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8676,39 +8676,39 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E183" s="17" t="n">
-        <v>-0.0154</v>
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>1166300</v>
+        <v>1202100</v>
       </c>
       <c r="G183" s="12" t="n">
         <v>0.35</v>
       </c>
       <c r="H183" t="n">
-        <v>32.47</v>
-      </c>
-      <c r="I183" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.67</v>
+      </c>
+      <c r="I183" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>2.655</v>
+        <v>9.613</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>2.776</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8721,28 +8721,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E184" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.965</v>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>1165300</v>
+        <v>1178100</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.35</v>
+        <v>0.63</v>
       </c>
       <c r="H184" t="n">
-        <v>56.82</v>
+        <v>39.69</v>
       </c>
       <c r="I184" s="13" t="inlineStr">
         <is>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>0.634</v>
+        <v>0.99</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>0.596</v>
+        <v>1.008</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8766,39 +8766,39 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E185" s="17" t="n">
-        <v>-0.0385</v>
+        <v>0.635</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>1153200</v>
+        <v>1165300</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.83</v>
+        <v>0.35</v>
       </c>
       <c r="H185" t="n">
-        <v>66.98</v>
-      </c>
-      <c r="I185" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.82</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>0.22</v>
+        <v>0.634</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>0.201</v>
+        <v>0.596</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
@@ -8811,39 +8811,39 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>IWCITY</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D186" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E186" s="15" t="n">
-        <v>0.0244</v>
+        <v>0.245</v>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>-0.05769999999999999</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>1138200</v>
+        <v>1163200</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1.36</v>
+        <v>0.84</v>
       </c>
       <c r="H186" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="I186" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.11</v>
+      </c>
+      <c r="I186" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J186" s="9" t="n">
-        <v>0.213</v>
+        <v>0.22</v>
       </c>
       <c r="K186" s="9" t="n">
-        <v>0.224</v>
+        <v>0.201</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="14" t="inlineStr"/>
@@ -8871,7 +8871,7 @@
         <v>0.0121</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>1136000</v>
+        <v>1138400</v>
       </c>
       <c r="G187" s="12" t="n">
         <v>0.26</v>
@@ -8901,39 +8901,39 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>IWCITY</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E188" s="10" t="n">
-        <v>0</v>
+        <v>0.21</v>
+      </c>
+      <c r="E188" s="15" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>1123500</v>
+        <v>1138200</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>0.18</v>
+        <v>1.36</v>
       </c>
       <c r="H188" t="n">
-        <v>48.43</v>
-      </c>
-      <c r="I188" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.7</v>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>2.565</v>
+        <v>0.213</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>2.544</v>
+        <v>0.224</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8955,19 +8955,19 @@
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E189" s="17" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>-0.0174</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>1118500</v>
+        <v>1133200</v>
       </c>
       <c r="G189" s="12" t="n">
         <v>0.28</v>
       </c>
       <c r="H189" t="n">
-        <v>36.2</v>
+        <v>33.35</v>
       </c>
       <c r="I189" s="13" t="inlineStr">
         <is>
@@ -8991,28 +8991,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D190" s="9" t="n">
-        <v>9.93</v>
+        <v>2.55</v>
       </c>
       <c r="E190" s="17" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>1113300</v>
+        <v>1124900</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="H190" t="n">
-        <v>63.91</v>
+        <v>48.43</v>
       </c>
       <c r="I190" s="16" t="inlineStr">
         <is>
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="J190" s="9" t="n">
-        <v>9.611000000000001</v>
+        <v>2.565</v>
       </c>
       <c r="K190" s="9" t="n">
-        <v>9.148999999999999</v>
+        <v>2.544</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="14" t="inlineStr"/>
@@ -9047,11 +9047,11 @@
       <c r="D191" s="9" t="n">
         <v>2.12</v>
       </c>
-      <c r="E191" s="17" t="n">
+      <c r="E191" s="10" t="n">
         <v>-0.014</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>1101600</v>
+        <v>1101800</v>
       </c>
       <c r="G191" s="12" t="n">
         <v>0.35</v>
@@ -9092,7 +9092,7 @@
       <c r="D192" s="9" t="n">
         <v>0.21</v>
       </c>
-      <c r="E192" s="17" t="n">
+      <c r="E192" s="10" t="n">
         <v>-0.0233</v>
       </c>
       <c r="F192" s="11" t="n">
@@ -9137,14 +9137,14 @@
       <c r="D193" s="9" t="n">
         <v>1.08</v>
       </c>
-      <c r="E193" s="17" t="n">
+      <c r="E193" s="10" t="n">
         <v>-0.0182</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>1076200</v>
+        <v>1087600</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H193" t="n">
         <v>28.79</v>
@@ -9182,14 +9182,14 @@
       <c r="D194" s="9" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E194" s="17" t="n">
+      <c r="E194" s="10" t="n">
         <v>-0.0157</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>1070200</v>
+        <v>1081900</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="H194" t="n">
         <v>25.81</v>
@@ -9216,39 +9216,39 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D195" s="9" t="n">
-        <v>0.27</v>
+        <v>3.53</v>
       </c>
       <c r="E195" s="10" t="n">
-        <v>0</v>
+        <v>-0.0028</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>1048900</v>
+        <v>1067500</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>1.09</v>
+        <v>0.51</v>
       </c>
       <c r="H195" t="n">
-        <v>36.39</v>
-      </c>
-      <c r="I195" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.66</v>
+      </c>
+      <c r="I195" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J195" s="9" t="n">
-        <v>0.277</v>
+        <v>3.566</v>
       </c>
       <c r="K195" s="9" t="n">
-        <v>0.275</v>
+        <v>3.605</v>
       </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" s="14" t="inlineStr"/>
@@ -9261,39 +9261,39 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D196" s="9" t="n">
-        <v>3.53</v>
+        <v>0.27</v>
       </c>
       <c r="E196" s="17" t="n">
-        <v>-0.0028</v>
+        <v>0</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>1038600</v>
+        <v>1048900</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>0.5</v>
+        <v>1.09</v>
       </c>
       <c r="H196" t="n">
-        <v>44.66</v>
-      </c>
-      <c r="I196" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.39</v>
+      </c>
+      <c r="I196" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J196" s="9" t="n">
-        <v>3.566</v>
+        <v>0.277</v>
       </c>
       <c r="K196" s="9" t="n">
-        <v>3.605</v>
+        <v>0.275</v>
       </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" s="14" t="inlineStr"/>
@@ -9306,39 +9306,39 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D197" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E197" s="17" t="n">
-        <v>-0.0155</v>
+        <v>5.11</v>
+      </c>
+      <c r="E197" s="10" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>1028100</v>
+        <v>1041300</v>
       </c>
       <c r="G197" s="12" t="n">
-        <v>0.64</v>
+        <v>0.41</v>
       </c>
       <c r="H197" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="I197" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.85</v>
+      </c>
+      <c r="I197" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J197" s="9" t="n">
-        <v>1.28</v>
+        <v>5.254</v>
       </c>
       <c r="K197" s="9" t="n">
-        <v>1.337</v>
+        <v>5.279</v>
       </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" s="14" t="inlineStr"/>
@@ -9360,19 +9360,19 @@
         </is>
       </c>
       <c r="D198" s="9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E198" s="17" t="n">
-        <v>-0.0105</v>
+        <v>2.84</v>
+      </c>
+      <c r="E198" s="10" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>1024200</v>
+        <v>1029500</v>
       </c>
       <c r="G198" s="12" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="H198" t="n">
-        <v>53.75</v>
+        <v>54.36</v>
       </c>
       <c r="I198" s="16" t="inlineStr">
         <is>
@@ -9396,39 +9396,39 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D199" s="9" t="n">
-        <v>0.335</v>
+        <v>1.27</v>
       </c>
       <c r="E199" s="10" t="n">
-        <v>0</v>
+        <v>-0.0155</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>1018300</v>
+        <v>1028100</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>0.29</v>
+        <v>0.64</v>
       </c>
       <c r="H199" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="I199" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.38</v>
+      </c>
+      <c r="I199" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J199" s="9" t="n">
-        <v>0.38</v>
+        <v>1.28</v>
       </c>
       <c r="K199" s="9" t="n">
-        <v>0.372</v>
+        <v>1.337</v>
       </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" s="14" t="inlineStr"/>
@@ -9441,28 +9441,28 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D200" s="9" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E200" s="10" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E200" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>1008400</v>
+        <v>1018300</v>
       </c>
       <c r="G200" s="12" t="n">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="H200" t="n">
-        <v>30.66</v>
+        <v>38.24</v>
       </c>
       <c r="I200" s="13" t="inlineStr">
         <is>
@@ -9470,10 +9470,10 @@
         </is>
       </c>
       <c r="J200" s="9" t="n">
-        <v>1.036</v>
+        <v>0.38</v>
       </c>
       <c r="K200" s="9" t="n">
-        <v>1.075</v>
+        <v>0.372</v>
       </c>
       <c r="L200" t="inlineStr"/>
       <c r="M200" s="14" t="inlineStr"/>
@@ -9486,28 +9486,28 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D201" s="9" t="n">
-        <v>5.12</v>
+        <v>0.975</v>
       </c>
       <c r="E201" s="17" t="n">
-        <v>-0.0116</v>
+        <v>0</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>998500</v>
+        <v>1010000</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="H201" t="n">
-        <v>45.16</v>
+        <v>30.66</v>
       </c>
       <c r="I201" s="13" t="inlineStr">
         <is>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="J201" s="9" t="n">
-        <v>5.255</v>
+        <v>1.036</v>
       </c>
       <c r="K201" s="9" t="n">
-        <v>5.279</v>
+        <v>1.075</v>
       </c>
       <c r="L201" t="inlineStr"/>
       <c r="M201" s="14" t="inlineStr"/>
@@ -9531,39 +9531,39 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D202" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E202" s="17" t="n">
-        <v>-0.008100000000000001</v>
+        <v>6.84</v>
+      </c>
+      <c r="E202" s="15" t="n">
+        <v>0.0059</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>979200</v>
+        <v>980900</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="H202" t="n">
-        <v>61.04</v>
-      </c>
-      <c r="I202" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.96</v>
+      </c>
+      <c r="I202" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J202" s="9" t="n">
-        <v>0.61</v>
+        <v>6.621</v>
       </c>
       <c r="K202" s="9" t="n">
-        <v>0.591</v>
+        <v>6.535</v>
       </c>
       <c r="L202" t="inlineStr"/>
       <c r="M202" s="14" t="inlineStr"/>
@@ -9576,28 +9576,28 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D203" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E203" s="15" t="n">
-        <v>0.0107</v>
+        <v>0.615</v>
+      </c>
+      <c r="E203" s="10" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>964800</v>
+        <v>979200</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="H203" t="n">
-        <v>35.45</v>
+        <v>61.04</v>
       </c>
       <c r="I203" s="13" t="inlineStr">
         <is>
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="J203" s="9" t="n">
-        <v>1.024</v>
+        <v>0.61</v>
       </c>
       <c r="K203" s="9" t="n">
-        <v>1.019</v>
+        <v>0.591</v>
       </c>
       <c r="L203" t="inlineStr"/>
       <c r="M203" s="14" t="inlineStr"/>
@@ -9632,14 +9632,14 @@
       <c r="D204" s="9" t="n">
         <v>0.65</v>
       </c>
-      <c r="E204" s="17" t="n">
+      <c r="E204" s="10" t="n">
         <v>-0.0076</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>963000</v>
+        <v>979000</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H204" t="n">
         <v>39.06</v>
@@ -9666,39 +9666,39 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D205" s="9" t="n">
-        <v>6.84</v>
+        <v>0.945</v>
       </c>
       <c r="E205" s="15" t="n">
-        <v>0.0059</v>
+        <v>0.0107</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>960700</v>
+        <v>964800</v>
       </c>
       <c r="G205" s="12" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="H205" t="n">
-        <v>56.96</v>
-      </c>
-      <c r="I205" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.45</v>
+      </c>
+      <c r="I205" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J205" s="9" t="n">
-        <v>6.621</v>
+        <v>1.024</v>
       </c>
       <c r="K205" s="9" t="n">
-        <v>6.535</v>
+        <v>1.019</v>
       </c>
       <c r="L205" t="inlineStr"/>
       <c r="M205" s="14" t="inlineStr"/>
@@ -9722,11 +9722,11 @@
       <c r="D206" s="9" t="n">
         <v>0.765</v>
       </c>
-      <c r="E206" s="17" t="n">
+      <c r="E206" s="10" t="n">
         <v>-0.0192</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>956600</v>
+        <v>957600</v>
       </c>
       <c r="G206" s="12" t="n">
         <v>0.35</v>
@@ -9767,7 +9767,7 @@
       <c r="D207" s="9" t="n">
         <v>3.36</v>
       </c>
-      <c r="E207" s="17" t="n">
+      <c r="E207" s="10" t="n">
         <v>-0.0562</v>
       </c>
       <c r="F207" s="11" t="n">
@@ -9801,39 +9801,39 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D208" s="9" t="n">
-        <v>0.61</v>
+        <v>1.82</v>
       </c>
       <c r="E208" s="10" t="n">
-        <v>0</v>
+        <v>-0.0215</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>924400</v>
+        <v>946700</v>
       </c>
       <c r="G208" s="12" t="n">
-        <v>0.36</v>
+        <v>1.05</v>
       </c>
       <c r="H208" t="n">
-        <v>39.14</v>
-      </c>
-      <c r="I208" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.72</v>
+      </c>
+      <c r="I208" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J208" s="9" t="n">
-        <v>0.632</v>
+        <v>1.831</v>
       </c>
       <c r="K208" s="9" t="n">
-        <v>0.635</v>
+        <v>1.864</v>
       </c>
       <c r="L208" t="inlineStr"/>
       <c r="M208" s="14" t="inlineStr"/>
@@ -9846,39 +9846,39 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>HEXTECH</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D209" s="9" t="n">
-        <v>1.13</v>
+        <v>0.61</v>
       </c>
       <c r="E209" s="17" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>893000</v>
+        <v>924400</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>16.23</v>
+        <v>0.36</v>
       </c>
       <c r="H209" t="n">
-        <v>40.79</v>
-      </c>
-      <c r="I209" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.14</v>
+      </c>
+      <c r="I209" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J209" s="9" t="n">
-        <v>1.143</v>
+        <v>0.632</v>
       </c>
       <c r="K209" s="9" t="n">
-        <v>1.137</v>
+        <v>0.635</v>
       </c>
       <c r="L209" t="inlineStr"/>
       <c r="M209" s="14" t="inlineStr"/>
@@ -9891,28 +9891,28 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>HEXTECH</t>
         </is>
       </c>
       <c r="D210" s="9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E210" s="15" t="n">
-        <v>0.0138</v>
+        <v>1.13</v>
+      </c>
+      <c r="E210" s="10" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>891700</v>
+        <v>893000</v>
       </c>
       <c r="G210" s="12" t="n">
-        <v>0.34</v>
+        <v>16.23</v>
       </c>
       <c r="H210" t="n">
-        <v>47.11</v>
+        <v>40.79</v>
       </c>
       <c r="I210" s="16" t="inlineStr">
         <is>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="J210" s="9" t="n">
-        <v>1.475</v>
+        <v>1.143</v>
       </c>
       <c r="K210" s="9" t="n">
-        <v>1.521</v>
+        <v>1.137</v>
       </c>
       <c r="L210" t="inlineStr"/>
       <c r="M210" s="14" t="inlineStr"/>
@@ -9936,28 +9936,28 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D211" s="9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="E211" s="17" t="n">
-        <v>-0.0269</v>
+        <v>1.46</v>
+      </c>
+      <c r="E211" s="15" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>872400</v>
+        <v>892800</v>
       </c>
       <c r="G211" s="12" t="n">
-        <v>0.97</v>
+        <v>0.34</v>
       </c>
       <c r="H211" t="n">
-        <v>45.07</v>
+        <v>44.92</v>
       </c>
       <c r="I211" s="16" t="inlineStr">
         <is>
@@ -9965,10 +9965,10 @@
         </is>
       </c>
       <c r="J211" s="9" t="n">
-        <v>1.83</v>
+        <v>1.474</v>
       </c>
       <c r="K211" s="9" t="n">
-        <v>1.864</v>
+        <v>1.521</v>
       </c>
       <c r="L211" t="inlineStr"/>
       <c r="M211" s="14" t="inlineStr"/>
@@ -9996,7 +9996,7 @@
         <v>0.009300000000000001</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>864300</v>
+        <v>878600</v>
       </c>
       <c r="G212" s="12" t="n">
         <v>0.46</v>
@@ -10037,14 +10037,14 @@
       <c r="D213" s="9" t="n">
         <v>0.925</v>
       </c>
-      <c r="E213" s="17" t="n">
+      <c r="E213" s="10" t="n">
         <v>-0.0107</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>858300</v>
+        <v>877900</v>
       </c>
       <c r="G213" s="12" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="H213" t="n">
         <v>37.45</v>
@@ -10082,14 +10082,14 @@
       <c r="D214" s="9" t="n">
         <v>2.98</v>
       </c>
-      <c r="E214" s="17" t="n">
+      <c r="E214" s="10" t="n">
         <v>-0.0067</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>836600</v>
+        <v>841900</v>
       </c>
       <c r="G214" s="12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="H214" t="n">
         <v>54.07</v>
@@ -10127,14 +10127,14 @@
       <c r="D215" s="9" t="n">
         <v>0.98</v>
       </c>
-      <c r="E215" s="17" t="n">
+      <c r="E215" s="10" t="n">
         <v>-0.0101</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>794700</v>
+        <v>812200</v>
       </c>
       <c r="G215" s="12" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="H215" t="n">
         <v>30.91</v>
@@ -10161,39 +10161,39 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D216" s="9" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="E216" s="15" t="n">
-        <v>0.0105</v>
+        <v>0.625</v>
+      </c>
+      <c r="E216" s="10" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>763600</v>
+        <v>810000</v>
       </c>
       <c r="G216" s="12" t="n">
-        <v>0.19</v>
+        <v>0.79</v>
       </c>
       <c r="H216" t="n">
-        <v>50.84</v>
-      </c>
-      <c r="I216" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.61</v>
+      </c>
+      <c r="I216" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J216" s="9" t="n">
-        <v>7.674</v>
+        <v>0.63</v>
       </c>
       <c r="K216" s="9" t="n">
-        <v>7.82</v>
+        <v>0.636</v>
       </c>
       <c r="L216" t="inlineStr"/>
       <c r="M216" s="14" t="inlineStr"/>
@@ -10206,39 +10206,39 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D217" s="9" t="n">
-        <v>0.525</v>
+        <v>7.77</v>
       </c>
       <c r="E217" s="15" t="n">
-        <v>0.0294</v>
+        <v>0.0157</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>741100</v>
+        <v>781300</v>
       </c>
       <c r="G217" s="12" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H217" t="n">
-        <v>56.43</v>
-      </c>
-      <c r="I217" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.75</v>
+      </c>
+      <c r="I217" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J217" s="9" t="n">
-        <v>0.513</v>
+        <v>7.678</v>
       </c>
       <c r="K217" s="9" t="n">
-        <v>0.469</v>
+        <v>7.821</v>
       </c>
       <c r="L217" t="inlineStr"/>
       <c r="M217" s="14" t="inlineStr"/>
@@ -10251,39 +10251,39 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>KIPREIT</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D218" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E218" s="17" t="n">
-        <v>-0.0058</v>
+        <v>0.525</v>
+      </c>
+      <c r="E218" s="15" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>734400</v>
+        <v>765300</v>
       </c>
       <c r="G218" s="12" t="n">
-        <v>1.18</v>
+        <v>0.19</v>
       </c>
       <c r="H218" t="n">
-        <v>49.11</v>
-      </c>
-      <c r="I218" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.43</v>
+      </c>
+      <c r="I218" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J218" s="9" t="n">
-        <v>0.852</v>
+        <v>0.513</v>
       </c>
       <c r="K218" s="9" t="n">
-        <v>0.847</v>
+        <v>0.469</v>
       </c>
       <c r="L218" t="inlineStr"/>
       <c r="M218" s="14" t="inlineStr"/>
@@ -10296,28 +10296,28 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>KIPREIT</t>
         </is>
       </c>
       <c r="D219" s="9" t="n">
-        <v>0.67</v>
+        <v>0.855</v>
       </c>
       <c r="E219" s="17" t="n">
-        <v>-0.029</v>
+        <v>0</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>732900</v>
+        <v>745400</v>
       </c>
       <c r="G219" s="12" t="n">
-        <v>0.64</v>
+        <v>1.19</v>
       </c>
       <c r="H219" t="n">
-        <v>49.44</v>
+        <v>54.19</v>
       </c>
       <c r="I219" s="16" t="inlineStr">
         <is>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="J219" s="9" t="n">
-        <v>0.673</v>
+        <v>0.853</v>
       </c>
       <c r="K219" s="9" t="n">
-        <v>0.675</v>
+        <v>0.847</v>
       </c>
       <c r="L219" t="inlineStr"/>
       <c r="M219" s="14" t="inlineStr"/>
@@ -10341,39 +10341,39 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>AFFIN</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D220" s="9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E220" s="17" t="n">
-        <v>-0.005</v>
+        <v>0.67</v>
+      </c>
+      <c r="E220" s="10" t="n">
+        <v>-0.029</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>724300</v>
+        <v>737200</v>
       </c>
       <c r="G220" s="12" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="H220" t="n">
-        <v>35.94</v>
-      </c>
-      <c r="I220" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.44</v>
+      </c>
+      <c r="I220" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J220" s="9" t="n">
-        <v>2.039</v>
+        <v>0.673</v>
       </c>
       <c r="K220" s="9" t="n">
-        <v>2.112</v>
+        <v>0.675</v>
       </c>
       <c r="L220" t="inlineStr"/>
       <c r="M220" s="14" t="inlineStr"/>
@@ -10386,39 +10386,39 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D221" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E221" s="15" t="n">
-        <v>0.004</v>
+        <v>2.94</v>
+      </c>
+      <c r="E221" s="10" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>715100</v>
+        <v>734200</v>
       </c>
       <c r="G221" s="12" t="n">
-        <v>0.13</v>
+        <v>0.59</v>
       </c>
       <c r="H221" t="n">
-        <v>50.77</v>
-      </c>
-      <c r="I221" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.03</v>
+      </c>
+      <c r="I221" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J221" s="9" t="n">
-        <v>4.982</v>
+        <v>3.049</v>
       </c>
       <c r="K221" s="9" t="n">
-        <v>5.045</v>
+        <v>3.142</v>
       </c>
       <c r="L221" t="inlineStr"/>
       <c r="M221" s="14" t="inlineStr"/>
@@ -10431,39 +10431,39 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D222" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E222" s="17" t="n">
-        <v>-0.0159</v>
+        <v>5</v>
+      </c>
+      <c r="E222" s="15" t="n">
+        <v>0.004</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>710000</v>
+        <v>728900</v>
       </c>
       <c r="G222" s="12" t="n">
-        <v>0.7</v>
+        <v>0.14</v>
       </c>
       <c r="H222" t="n">
-        <v>36.72</v>
-      </c>
-      <c r="I222" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.77</v>
+      </c>
+      <c r="I222" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J222" s="9" t="n">
-        <v>0.63</v>
+        <v>4.982</v>
       </c>
       <c r="K222" s="9" t="n">
-        <v>0.636</v>
+        <v>5.045</v>
       </c>
       <c r="L222" t="inlineStr"/>
       <c r="M222" s="14" t="inlineStr"/>
@@ -10476,39 +10476,39 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>AFFIN</t>
         </is>
       </c>
       <c r="D223" s="9" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="E223" s="17" t="n">
-        <v>-0.0247</v>
+        <v>0</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>685200</v>
+        <v>724400</v>
       </c>
       <c r="G223" s="12" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="H223" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="I223" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.31</v>
+      </c>
+      <c r="I223" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J223" s="9" t="n">
-        <v>1.64</v>
+        <v>2.039</v>
       </c>
       <c r="K223" s="9" t="n">
-        <v>1.712</v>
+        <v>2.112</v>
       </c>
       <c r="L223" t="inlineStr"/>
       <c r="M223" s="14" t="inlineStr"/>
@@ -10521,28 +10521,28 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D224" s="9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E224" s="17" t="n">
-        <v>-0.0124</v>
+        <v>3.96</v>
+      </c>
+      <c r="E224" s="10" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>674700</v>
+        <v>722200</v>
       </c>
       <c r="G224" s="12" t="n">
-        <v>0.41</v>
+        <v>0.22</v>
       </c>
       <c r="H224" t="n">
-        <v>43.09</v>
+        <v>63.53</v>
       </c>
       <c r="I224" s="16" t="inlineStr">
         <is>
@@ -10550,10 +10550,10 @@
         </is>
       </c>
       <c r="J224" s="9" t="n">
-        <v>1.627</v>
+        <v>3.79</v>
       </c>
       <c r="K224" s="9" t="n">
-        <v>1.686</v>
+        <v>3.44</v>
       </c>
       <c r="L224" t="inlineStr"/>
       <c r="M224" s="14" t="inlineStr"/>
@@ -10566,28 +10566,28 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D225" s="9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="E225" s="17" t="n">
-        <v>-0.015</v>
+        <v>1.58</v>
+      </c>
+      <c r="E225" s="10" t="n">
+        <v>-0.0247</v>
       </c>
       <c r="F225" s="11" t="n">
-        <v>666900</v>
+        <v>685200</v>
       </c>
       <c r="G225" s="12" t="n">
-        <v>0.2</v>
+        <v>0.77</v>
       </c>
       <c r="H225" t="n">
-        <v>62.88</v>
+        <v>41.7</v>
       </c>
       <c r="I225" s="16" t="inlineStr">
         <is>
@@ -10595,10 +10595,10 @@
         </is>
       </c>
       <c r="J225" s="9" t="n">
-        <v>3.789</v>
+        <v>1.64</v>
       </c>
       <c r="K225" s="9" t="n">
-        <v>3.44</v>
+        <v>1.712</v>
       </c>
       <c r="L225" t="inlineStr"/>
       <c r="M225" s="14" t="inlineStr"/>
@@ -10611,39 +10611,39 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>KLK</t>
         </is>
       </c>
       <c r="D226" s="9" t="n">
-        <v>2.95</v>
+        <v>22.28</v>
       </c>
       <c r="E226" s="10" t="n">
-        <v>0</v>
+        <v>-0.0098</v>
       </c>
       <c r="F226" s="11" t="n">
-        <v>646300</v>
+        <v>678800</v>
       </c>
       <c r="G226" s="12" t="n">
-        <v>0.52</v>
+        <v>0.85</v>
       </c>
       <c r="H226" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="I226" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.62</v>
+      </c>
+      <c r="I226" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J226" s="9" t="n">
-        <v>3.05</v>
+        <v>22.425</v>
       </c>
       <c r="K226" s="9" t="n">
-        <v>3.142</v>
+        <v>21.914</v>
       </c>
       <c r="L226" t="inlineStr"/>
       <c r="M226" s="14" t="inlineStr"/>
@@ -10656,39 +10656,39 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D227" s="9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E227" s="15" t="n">
-        <v>0.006</v>
+        <v>1.59</v>
+      </c>
+      <c r="E227" s="10" t="n">
+        <v>-0.0124</v>
       </c>
       <c r="F227" s="11" t="n">
-        <v>634600</v>
+        <v>674700</v>
       </c>
       <c r="G227" s="12" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="H227" t="n">
-        <v>38.52</v>
-      </c>
-      <c r="I227" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.09</v>
+      </c>
+      <c r="I227" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J227" s="9" t="n">
-        <v>1.742</v>
+        <v>1.627</v>
       </c>
       <c r="K227" s="9" t="n">
-        <v>1.849</v>
+        <v>1.686</v>
       </c>
       <c r="L227" t="inlineStr"/>
       <c r="M227" s="14" t="inlineStr"/>
@@ -10701,39 +10701,39 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>KLK</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="D228" s="9" t="n">
-        <v>22.24</v>
-      </c>
-      <c r="E228" s="17" t="n">
-        <v>-0.0116</v>
+        <v>7.69</v>
+      </c>
+      <c r="E228" s="15" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>609200</v>
+        <v>649000</v>
       </c>
       <c r="G228" s="12" t="n">
-        <v>0.76</v>
+        <v>0.36</v>
       </c>
       <c r="H228" t="n">
-        <v>47.74</v>
-      </c>
-      <c r="I228" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.01</v>
+      </c>
+      <c r="I228" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J228" s="9" t="n">
-        <v>22.421</v>
+        <v>7.842</v>
       </c>
       <c r="K228" s="9" t="n">
-        <v>21.914</v>
+        <v>7.952</v>
       </c>
       <c r="L228" t="inlineStr"/>
       <c r="M228" s="14" t="inlineStr"/>
@@ -10746,28 +10746,28 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D229" s="9" t="n">
-        <v>7.69</v>
+        <v>1.68</v>
       </c>
       <c r="E229" s="15" t="n">
-        <v>0.0118</v>
+        <v>0.006</v>
       </c>
       <c r="F229" s="11" t="n">
-        <v>604000</v>
+        <v>644800</v>
       </c>
       <c r="G229" s="12" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="H229" t="n">
-        <v>43.01</v>
+        <v>38.52</v>
       </c>
       <c r="I229" s="13" t="inlineStr">
         <is>
@@ -10775,10 +10775,10 @@
         </is>
       </c>
       <c r="J229" s="9" t="n">
-        <v>7.842</v>
+        <v>1.742</v>
       </c>
       <c r="K229" s="9" t="n">
-        <v>7.952</v>
+        <v>1.849</v>
       </c>
       <c r="L229" t="inlineStr"/>
       <c r="M229" s="14" t="inlineStr"/>
@@ -10802,14 +10802,14 @@
       <c r="D230" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="E230" s="17" t="n">
+      <c r="E230" s="10" t="n">
         <v>-0.0152</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>597600</v>
+        <v>615200</v>
       </c>
       <c r="G230" s="12" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="H230" t="n">
         <v>59.12</v>
@@ -10847,11 +10847,11 @@
       <c r="D231" s="9" t="n">
         <v>3.91</v>
       </c>
-      <c r="E231" s="17" t="n">
+      <c r="E231" s="10" t="n">
         <v>-0.0201</v>
       </c>
       <c r="F231" s="11" t="n">
-        <v>585100</v>
+        <v>589600</v>
       </c>
       <c r="G231" s="12" t="n">
         <v>0.31</v>
@@ -10890,19 +10890,19 @@
         </is>
       </c>
       <c r="D232" s="9" t="n">
-        <v>0.86</v>
+        <v>0.855</v>
       </c>
       <c r="E232" s="10" t="n">
-        <v>0</v>
+        <v>-0.0058</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>575600</v>
+        <v>585900</v>
       </c>
       <c r="G232" s="12" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="H232" t="n">
-        <v>44.68</v>
+        <v>41.59</v>
       </c>
       <c r="I232" s="16" t="inlineStr">
         <is>
@@ -10935,19 +10935,19 @@
         </is>
       </c>
       <c r="D233" s="9" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="E233" s="17" t="n">
-        <v>-0.0034</v>
+        <v>5.78</v>
+      </c>
+      <c r="E233" s="10" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F233" s="11" t="n">
-        <v>572300</v>
+        <v>576900</v>
       </c>
       <c r="G233" s="12" t="n">
         <v>0.34</v>
       </c>
       <c r="H233" t="n">
-        <v>44.52</v>
+        <v>44.06</v>
       </c>
       <c r="I233" s="13" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         </is>
       </c>
       <c r="J233" s="9" t="n">
-        <v>5.877</v>
+        <v>5.876</v>
       </c>
       <c r="K233" s="9" t="n">
         <v>5.915</v>
@@ -10980,19 +10980,19 @@
         </is>
       </c>
       <c r="D234" s="9" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="E234" s="17" t="n">
-        <v>-0.021</v>
+        <v>3.28</v>
+      </c>
+      <c r="E234" s="10" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>567900</v>
+        <v>575300</v>
       </c>
       <c r="G234" s="12" t="n">
         <v>0.22</v>
       </c>
       <c r="H234" t="n">
-        <v>68.27</v>
+        <v>68.91</v>
       </c>
       <c r="I234" s="16" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="J234" s="9" t="n">
-        <v>3</v>
+        <v>3.001</v>
       </c>
       <c r="K234" s="9" t="n">
         <v>2.574</v>
@@ -11072,7 +11072,7 @@
       <c r="D236" s="9" t="n">
         <v>1.05</v>
       </c>
-      <c r="E236" s="17" t="n">
+      <c r="E236" s="10" t="n">
         <v>-0.0187</v>
       </c>
       <c r="F236" s="11" t="n">
@@ -11151,39 +11151,39 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D238" s="9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E238" s="17" t="n">
-        <v>-0.0241</v>
+        <v>8.640000000000001</v>
+      </c>
+      <c r="E238" s="10" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>526400</v>
+        <v>527600</v>
       </c>
       <c r="G238" s="12" t="n">
-        <v>0.39</v>
+        <v>0.18</v>
       </c>
       <c r="H238" t="n">
-        <v>42.58</v>
-      </c>
-      <c r="I238" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.69</v>
+      </c>
+      <c r="I238" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J238" s="9" t="n">
-        <v>2.954</v>
+        <v>8.677</v>
       </c>
       <c r="K238" s="9" t="n">
-        <v>2.819</v>
+        <v>8.584</v>
       </c>
       <c r="L238" t="inlineStr"/>
       <c r="M238" s="14" t="inlineStr"/>
@@ -11196,39 +11196,39 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D239" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E239" s="15" t="n">
-        <v>0.027</v>
+        <v>2.83</v>
+      </c>
+      <c r="E239" s="10" t="n">
+        <v>-0.0241</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>517400</v>
+        <v>526400</v>
       </c>
       <c r="G239" s="12" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="H239" t="n">
-        <v>49.67</v>
-      </c>
-      <c r="I239" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.58</v>
+      </c>
+      <c r="I239" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J239" s="9" t="n">
-        <v>0.762</v>
+        <v>2.954</v>
       </c>
       <c r="K239" s="9" t="n">
-        <v>0.755</v>
+        <v>2.819</v>
       </c>
       <c r="L239" t="inlineStr"/>
       <c r="M239" s="14" t="inlineStr"/>
@@ -11252,14 +11252,14 @@
       <c r="D240" s="9" t="n">
         <v>0.775</v>
       </c>
-      <c r="E240" s="17" t="n">
+      <c r="E240" s="10" t="n">
         <v>-0.0313</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>516300</v>
+        <v>517800</v>
       </c>
       <c r="G240" s="12" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H240" t="n">
         <v>30.29</v>
@@ -11286,39 +11286,39 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>CCK</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D241" s="9" t="n">
-        <v>0.875</v>
+        <v>0.76</v>
       </c>
       <c r="E241" s="15" t="n">
-        <v>0.0116</v>
+        <v>0.027</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>509600</v>
+        <v>517400</v>
       </c>
       <c r="G241" s="12" t="n">
-        <v>0.91</v>
+        <v>0.32</v>
       </c>
       <c r="H241" t="n">
-        <v>28.41</v>
-      </c>
-      <c r="I241" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.67</v>
+      </c>
+      <c r="I241" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J241" s="9" t="n">
-        <v>0.911</v>
+        <v>0.762</v>
       </c>
       <c r="K241" s="9" t="n">
-        <v>0.994</v>
+        <v>0.755</v>
       </c>
       <c r="L241" t="inlineStr"/>
       <c r="M241" s="14" t="inlineStr"/>
@@ -11331,39 +11331,39 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>CCK</t>
         </is>
       </c>
       <c r="D242" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E242" s="10" t="n">
-        <v>0</v>
+        <v>0.875</v>
+      </c>
+      <c r="E242" s="15" t="n">
+        <v>0.0116</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>506200</v>
+        <v>509600</v>
       </c>
       <c r="G242" s="12" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="H242" t="n">
-        <v>60.52</v>
-      </c>
-      <c r="I242" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.41</v>
+      </c>
+      <c r="I242" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J242" s="9" t="n">
-        <v>0.985</v>
+        <v>0.911</v>
       </c>
       <c r="K242" s="9" t="n">
-        <v>0.976</v>
+        <v>0.994</v>
       </c>
       <c r="L242" t="inlineStr"/>
       <c r="M242" s="14" t="inlineStr"/>
@@ -11376,28 +11376,28 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D243" s="9" t="n">
-        <v>8.630000000000001</v>
+        <v>1</v>
       </c>
       <c r="E243" s="17" t="n">
-        <v>-0.0115</v>
+        <v>0</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>505000</v>
+        <v>506200</v>
       </c>
       <c r="G243" s="12" t="n">
-        <v>0.17</v>
+        <v>0.89</v>
       </c>
       <c r="H243" t="n">
-        <v>49.43</v>
+        <v>60.52</v>
       </c>
       <c r="I243" s="16" t="inlineStr">
         <is>
@@ -11405,10 +11405,10 @@
         </is>
       </c>
       <c r="J243" s="9" t="n">
-        <v>8.676</v>
+        <v>0.985</v>
       </c>
       <c r="K243" s="9" t="n">
-        <v>8.583</v>
+        <v>0.976</v>
       </c>
       <c r="L243" t="inlineStr"/>
       <c r="M243" s="14" t="inlineStr"/>
